--- a/iridescent/src/main/resources/IridescentAlchemy3-TraceOfBattle/ReadMe.xlsx
+++ b/iridescent/src/main/resources/IridescentAlchemy3-TraceOfBattle/ReadMe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace-idea\7daystodie\IridescentAlchemy3-TraceOfBattle\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Program Files (x86)\Steam\steamapps\common\7 Days To Die\Mods\IridescentAlchemy3-TraceOfBattle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D577180-152A-4175-833C-98FDDA660F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D05918-19BD-42F8-9486-998525167056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2160" yWindow="2190" windowWidth="34300" windowHeight="17350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="首页" sheetId="15" r:id="rId1"/>
@@ -3541,6 +3541,66 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
+    <t>战斧</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>流血异常</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>40</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>小石斧</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>150</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>210</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>240</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>110</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>130</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/20/30/40</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>90</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>180</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>280</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>320</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">虹彩炼金3-战痕
 </t>
@@ -3555,70 +3615,10 @@
       </rPr>
       <t xml:space="preserve">
 作者：整洁的魔理沙
-文档版本：V2.6.26.667
-七日杀游戏版本：V2.5</t>
+文档版本：V3.0.26.816
+七日杀游戏版本：V3.0</t>
     </r>
     <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斧</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>流血异常</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>40</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>小石斧</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>150</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>210</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>240</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>110</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>130</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>10/20/30/40</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>90</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>180</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>280</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>320</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4636,6 +4636,18 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="12" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4647,15 +4659,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="62" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="60" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="31" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="62" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4684,6 +4687,12 @@
     <xf numFmtId="49" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="31" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="62" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="60" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4691,6 +4700,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="60" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="60" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -4703,9 +4715,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4741,6 +4750,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4748,18 +4769,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -4795,24 +4804,6 @@
     <xf numFmtId="49" fontId="0" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4840,16 +4831,25 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5137,771 +5137,771 @@
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="7" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C7" s="140" t="s">
-        <v>1118</v>
-      </c>
-      <c r="D7" s="141"/>
-      <c r="E7" s="141"/>
-      <c r="F7" s="141"/>
-      <c r="G7" s="141"/>
-      <c r="H7" s="141"/>
-      <c r="I7" s="141"/>
-      <c r="J7" s="141"/>
-      <c r="K7" s="141"/>
-      <c r="L7" s="141"/>
-      <c r="M7" s="141"/>
-      <c r="N7" s="141"/>
-      <c r="O7" s="141"/>
-      <c r="P7" s="141"/>
-      <c r="Q7" s="141"/>
+      <c r="C7" s="144" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D7" s="145"/>
+      <c r="E7" s="145"/>
+      <c r="F7" s="145"/>
+      <c r="G7" s="145"/>
+      <c r="H7" s="145"/>
+      <c r="I7" s="145"/>
+      <c r="J7" s="145"/>
+      <c r="K7" s="145"/>
+      <c r="L7" s="145"/>
+      <c r="M7" s="145"/>
+      <c r="N7" s="145"/>
+      <c r="O7" s="145"/>
+      <c r="P7" s="145"/>
+      <c r="Q7" s="145"/>
     </row>
     <row r="8" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C8" s="141"/>
-      <c r="D8" s="141"/>
-      <c r="E8" s="141"/>
-      <c r="F8" s="141"/>
-      <c r="G8" s="141"/>
-      <c r="H8" s="141"/>
-      <c r="I8" s="141"/>
-      <c r="J8" s="141"/>
-      <c r="K8" s="141"/>
-      <c r="L8" s="141"/>
-      <c r="M8" s="141"/>
-      <c r="N8" s="141"/>
-      <c r="O8" s="141"/>
-      <c r="P8" s="141"/>
-      <c r="Q8" s="141"/>
+      <c r="C8" s="145"/>
+      <c r="D8" s="145"/>
+      <c r="E8" s="145"/>
+      <c r="F8" s="145"/>
+      <c r="G8" s="145"/>
+      <c r="H8" s="145"/>
+      <c r="I8" s="145"/>
+      <c r="J8" s="145"/>
+      <c r="K8" s="145"/>
+      <c r="L8" s="145"/>
+      <c r="M8" s="145"/>
+      <c r="N8" s="145"/>
+      <c r="O8" s="145"/>
+      <c r="P8" s="145"/>
+      <c r="Q8" s="145"/>
     </row>
     <row r="9" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C9" s="141"/>
-      <c r="D9" s="141"/>
-      <c r="E9" s="141"/>
-      <c r="F9" s="141"/>
-      <c r="G9" s="141"/>
-      <c r="H9" s="141"/>
-      <c r="I9" s="141"/>
-      <c r="J9" s="141"/>
-      <c r="K9" s="141"/>
-      <c r="L9" s="141"/>
-      <c r="M9" s="141"/>
-      <c r="N9" s="141"/>
-      <c r="O9" s="141"/>
-      <c r="P9" s="141"/>
-      <c r="Q9" s="141"/>
+      <c r="C9" s="145"/>
+      <c r="D9" s="145"/>
+      <c r="E9" s="145"/>
+      <c r="F9" s="145"/>
+      <c r="G9" s="145"/>
+      <c r="H9" s="145"/>
+      <c r="I9" s="145"/>
+      <c r="J9" s="145"/>
+      <c r="K9" s="145"/>
+      <c r="L9" s="145"/>
+      <c r="M9" s="145"/>
+      <c r="N9" s="145"/>
+      <c r="O9" s="145"/>
+      <c r="P9" s="145"/>
+      <c r="Q9" s="145"/>
     </row>
     <row r="10" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C10" s="141"/>
-      <c r="D10" s="141"/>
-      <c r="E10" s="141"/>
-      <c r="F10" s="141"/>
-      <c r="G10" s="141"/>
-      <c r="H10" s="141"/>
-      <c r="I10" s="141"/>
-      <c r="J10" s="141"/>
-      <c r="K10" s="141"/>
-      <c r="L10" s="141"/>
-      <c r="M10" s="141"/>
-      <c r="N10" s="141"/>
-      <c r="O10" s="141"/>
-      <c r="P10" s="141"/>
-      <c r="Q10" s="141"/>
+      <c r="C10" s="145"/>
+      <c r="D10" s="145"/>
+      <c r="E10" s="145"/>
+      <c r="F10" s="145"/>
+      <c r="G10" s="145"/>
+      <c r="H10" s="145"/>
+      <c r="I10" s="145"/>
+      <c r="J10" s="145"/>
+      <c r="K10" s="145"/>
+      <c r="L10" s="145"/>
+      <c r="M10" s="145"/>
+      <c r="N10" s="145"/>
+      <c r="O10" s="145"/>
+      <c r="P10" s="145"/>
+      <c r="Q10" s="145"/>
     </row>
     <row r="11" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C11" s="141"/>
-      <c r="D11" s="141"/>
-      <c r="E11" s="141"/>
-      <c r="F11" s="141"/>
-      <c r="G11" s="141"/>
-      <c r="H11" s="141"/>
-      <c r="I11" s="141"/>
-      <c r="J11" s="141"/>
-      <c r="K11" s="141"/>
-      <c r="L11" s="141"/>
-      <c r="M11" s="141"/>
-      <c r="N11" s="141"/>
-      <c r="O11" s="141"/>
-      <c r="P11" s="141"/>
-      <c r="Q11" s="141"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="145"/>
+      <c r="J11" s="145"/>
+      <c r="K11" s="145"/>
+      <c r="L11" s="145"/>
+      <c r="M11" s="145"/>
+      <c r="N11" s="145"/>
+      <c r="O11" s="145"/>
+      <c r="P11" s="145"/>
+      <c r="Q11" s="145"/>
     </row>
     <row r="12" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C12" s="141"/>
-      <c r="D12" s="141"/>
-      <c r="E12" s="141"/>
-      <c r="F12" s="141"/>
-      <c r="G12" s="141"/>
-      <c r="H12" s="141"/>
-      <c r="I12" s="141"/>
-      <c r="J12" s="141"/>
-      <c r="K12" s="141"/>
-      <c r="L12" s="141"/>
-      <c r="M12" s="141"/>
-      <c r="N12" s="141"/>
-      <c r="O12" s="141"/>
-      <c r="P12" s="141"/>
-      <c r="Q12" s="141"/>
+      <c r="C12" s="145"/>
+      <c r="D12" s="145"/>
+      <c r="E12" s="145"/>
+      <c r="F12" s="145"/>
+      <c r="G12" s="145"/>
+      <c r="H12" s="145"/>
+      <c r="I12" s="145"/>
+      <c r="J12" s="145"/>
+      <c r="K12" s="145"/>
+      <c r="L12" s="145"/>
+      <c r="M12" s="145"/>
+      <c r="N12" s="145"/>
+      <c r="O12" s="145"/>
+      <c r="P12" s="145"/>
+      <c r="Q12" s="145"/>
     </row>
     <row r="13" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C13" s="141"/>
-      <c r="D13" s="141"/>
-      <c r="E13" s="141"/>
-      <c r="F13" s="141"/>
-      <c r="G13" s="141"/>
-      <c r="H13" s="141"/>
-      <c r="I13" s="141"/>
-      <c r="J13" s="141"/>
-      <c r="K13" s="141"/>
-      <c r="L13" s="141"/>
-      <c r="M13" s="141"/>
-      <c r="N13" s="141"/>
-      <c r="O13" s="141"/>
-      <c r="P13" s="141"/>
-      <c r="Q13" s="141"/>
+      <c r="C13" s="145"/>
+      <c r="D13" s="145"/>
+      <c r="E13" s="145"/>
+      <c r="F13" s="145"/>
+      <c r="G13" s="145"/>
+      <c r="H13" s="145"/>
+      <c r="I13" s="145"/>
+      <c r="J13" s="145"/>
+      <c r="K13" s="145"/>
+      <c r="L13" s="145"/>
+      <c r="M13" s="145"/>
+      <c r="N13" s="145"/>
+      <c r="O13" s="145"/>
+      <c r="P13" s="145"/>
+      <c r="Q13" s="145"/>
     </row>
     <row r="14" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C14" s="141"/>
-      <c r="D14" s="141"/>
-      <c r="E14" s="141"/>
-      <c r="F14" s="141"/>
-      <c r="G14" s="141"/>
-      <c r="H14" s="141"/>
-      <c r="I14" s="141"/>
-      <c r="J14" s="141"/>
-      <c r="K14" s="141"/>
-      <c r="L14" s="141"/>
-      <c r="M14" s="141"/>
-      <c r="N14" s="141"/>
-      <c r="O14" s="141"/>
-      <c r="P14" s="141"/>
-      <c r="Q14" s="141"/>
+      <c r="C14" s="145"/>
+      <c r="D14" s="145"/>
+      <c r="E14" s="145"/>
+      <c r="F14" s="145"/>
+      <c r="G14" s="145"/>
+      <c r="H14" s="145"/>
+      <c r="I14" s="145"/>
+      <c r="J14" s="145"/>
+      <c r="K14" s="145"/>
+      <c r="L14" s="145"/>
+      <c r="M14" s="145"/>
+      <c r="N14" s="145"/>
+      <c r="O14" s="145"/>
+      <c r="P14" s="145"/>
+      <c r="Q14" s="145"/>
     </row>
     <row r="15" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C15" s="141"/>
-      <c r="D15" s="141"/>
-      <c r="E15" s="141"/>
-      <c r="F15" s="141"/>
-      <c r="G15" s="141"/>
-      <c r="H15" s="141"/>
-      <c r="I15" s="141"/>
-      <c r="J15" s="141"/>
-      <c r="K15" s="141"/>
-      <c r="L15" s="141"/>
-      <c r="M15" s="141"/>
-      <c r="N15" s="141"/>
-      <c r="O15" s="141"/>
-      <c r="P15" s="141"/>
-      <c r="Q15" s="141"/>
+      <c r="C15" s="145"/>
+      <c r="D15" s="145"/>
+      <c r="E15" s="145"/>
+      <c r="F15" s="145"/>
+      <c r="G15" s="145"/>
+      <c r="H15" s="145"/>
+      <c r="I15" s="145"/>
+      <c r="J15" s="145"/>
+      <c r="K15" s="145"/>
+      <c r="L15" s="145"/>
+      <c r="M15" s="145"/>
+      <c r="N15" s="145"/>
+      <c r="O15" s="145"/>
+      <c r="P15" s="145"/>
+      <c r="Q15" s="145"/>
     </row>
     <row r="16" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C16" s="141"/>
-      <c r="D16" s="141"/>
-      <c r="E16" s="141"/>
-      <c r="F16" s="141"/>
-      <c r="G16" s="141"/>
-      <c r="H16" s="141"/>
-      <c r="I16" s="141"/>
-      <c r="J16" s="141"/>
-      <c r="K16" s="141"/>
-      <c r="L16" s="141"/>
-      <c r="M16" s="141"/>
-      <c r="N16" s="141"/>
-      <c r="O16" s="141"/>
-      <c r="P16" s="141"/>
-      <c r="Q16" s="141"/>
+      <c r="C16" s="145"/>
+      <c r="D16" s="145"/>
+      <c r="E16" s="145"/>
+      <c r="F16" s="145"/>
+      <c r="G16" s="145"/>
+      <c r="H16" s="145"/>
+      <c r="I16" s="145"/>
+      <c r="J16" s="145"/>
+      <c r="K16" s="145"/>
+      <c r="L16" s="145"/>
+      <c r="M16" s="145"/>
+      <c r="N16" s="145"/>
+      <c r="O16" s="145"/>
+      <c r="P16" s="145"/>
+      <c r="Q16" s="145"/>
     </row>
     <row r="17" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C17" s="141"/>
-      <c r="D17" s="141"/>
-      <c r="E17" s="141"/>
-      <c r="F17" s="141"/>
-      <c r="G17" s="141"/>
-      <c r="H17" s="141"/>
-      <c r="I17" s="141"/>
-      <c r="J17" s="141"/>
-      <c r="K17" s="141"/>
-      <c r="L17" s="141"/>
-      <c r="M17" s="141"/>
-      <c r="N17" s="141"/>
-      <c r="O17" s="141"/>
-      <c r="P17" s="141"/>
-      <c r="Q17" s="141"/>
+      <c r="C17" s="145"/>
+      <c r="D17" s="145"/>
+      <c r="E17" s="145"/>
+      <c r="F17" s="145"/>
+      <c r="G17" s="145"/>
+      <c r="H17" s="145"/>
+      <c r="I17" s="145"/>
+      <c r="J17" s="145"/>
+      <c r="K17" s="145"/>
+      <c r="L17" s="145"/>
+      <c r="M17" s="145"/>
+      <c r="N17" s="145"/>
+      <c r="O17" s="145"/>
+      <c r="P17" s="145"/>
+      <c r="Q17" s="145"/>
     </row>
     <row r="18" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C18" s="141"/>
-      <c r="D18" s="141"/>
-      <c r="E18" s="141"/>
-      <c r="F18" s="141"/>
-      <c r="G18" s="141"/>
-      <c r="H18" s="141"/>
-      <c r="I18" s="141"/>
-      <c r="J18" s="141"/>
-      <c r="K18" s="141"/>
-      <c r="L18" s="141"/>
-      <c r="M18" s="141"/>
-      <c r="N18" s="141"/>
-      <c r="O18" s="141"/>
-      <c r="P18" s="141"/>
-      <c r="Q18" s="141"/>
+      <c r="C18" s="145"/>
+      <c r="D18" s="145"/>
+      <c r="E18" s="145"/>
+      <c r="F18" s="145"/>
+      <c r="G18" s="145"/>
+      <c r="H18" s="145"/>
+      <c r="I18" s="145"/>
+      <c r="J18" s="145"/>
+      <c r="K18" s="145"/>
+      <c r="L18" s="145"/>
+      <c r="M18" s="145"/>
+      <c r="N18" s="145"/>
+      <c r="O18" s="145"/>
+      <c r="P18" s="145"/>
+      <c r="Q18" s="145"/>
     </row>
     <row r="19" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C19" s="141"/>
-      <c r="D19" s="141"/>
-      <c r="E19" s="141"/>
-      <c r="F19" s="141"/>
-      <c r="G19" s="141"/>
-      <c r="H19" s="141"/>
-      <c r="I19" s="141"/>
-      <c r="J19" s="141"/>
-      <c r="K19" s="141"/>
-      <c r="L19" s="141"/>
-      <c r="M19" s="141"/>
-      <c r="N19" s="141"/>
-      <c r="O19" s="141"/>
-      <c r="P19" s="141"/>
-      <c r="Q19" s="141"/>
+      <c r="C19" s="145"/>
+      <c r="D19" s="145"/>
+      <c r="E19" s="145"/>
+      <c r="F19" s="145"/>
+      <c r="G19" s="145"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="145"/>
+      <c r="N19" s="145"/>
+      <c r="O19" s="145"/>
+      <c r="P19" s="145"/>
+      <c r="Q19" s="145"/>
     </row>
     <row r="20" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C20" s="141"/>
-      <c r="D20" s="141"/>
-      <c r="E20" s="141"/>
-      <c r="F20" s="141"/>
-      <c r="G20" s="141"/>
-      <c r="H20" s="141"/>
-      <c r="I20" s="141"/>
-      <c r="J20" s="141"/>
-      <c r="K20" s="141"/>
-      <c r="L20" s="141"/>
-      <c r="M20" s="141"/>
-      <c r="N20" s="141"/>
-      <c r="O20" s="141"/>
-      <c r="P20" s="141"/>
-      <c r="Q20" s="141"/>
+      <c r="C20" s="145"/>
+      <c r="D20" s="145"/>
+      <c r="E20" s="145"/>
+      <c r="F20" s="145"/>
+      <c r="G20" s="145"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="145"/>
+      <c r="O20" s="145"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="145"/>
     </row>
     <row r="21" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C21" s="141"/>
-      <c r="D21" s="141"/>
-      <c r="E21" s="141"/>
-      <c r="F21" s="141"/>
-      <c r="G21" s="141"/>
-      <c r="H21" s="141"/>
-      <c r="I21" s="141"/>
-      <c r="J21" s="141"/>
-      <c r="K21" s="141"/>
-      <c r="L21" s="141"/>
-      <c r="M21" s="141"/>
-      <c r="N21" s="141"/>
-      <c r="O21" s="141"/>
-      <c r="P21" s="141"/>
-      <c r="Q21" s="141"/>
+      <c r="C21" s="145"/>
+      <c r="D21" s="145"/>
+      <c r="E21" s="145"/>
+      <c r="F21" s="145"/>
+      <c r="G21" s="145"/>
+      <c r="H21" s="145"/>
+      <c r="I21" s="145"/>
+      <c r="J21" s="145"/>
+      <c r="K21" s="145"/>
+      <c r="L21" s="145"/>
+      <c r="M21" s="145"/>
+      <c r="N21" s="145"/>
+      <c r="O21" s="145"/>
+      <c r="P21" s="145"/>
+      <c r="Q21" s="145"/>
     </row>
     <row r="22" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C22" s="141"/>
-      <c r="D22" s="141"/>
-      <c r="E22" s="141"/>
-      <c r="F22" s="141"/>
-      <c r="G22" s="141"/>
-      <c r="H22" s="141"/>
-      <c r="I22" s="141"/>
-      <c r="J22" s="141"/>
-      <c r="K22" s="141"/>
-      <c r="L22" s="141"/>
-      <c r="M22" s="141"/>
-      <c r="N22" s="141"/>
-      <c r="O22" s="141"/>
-      <c r="P22" s="141"/>
-      <c r="Q22" s="141"/>
+      <c r="C22" s="145"/>
+      <c r="D22" s="145"/>
+      <c r="E22" s="145"/>
+      <c r="F22" s="145"/>
+      <c r="G22" s="145"/>
+      <c r="H22" s="145"/>
+      <c r="I22" s="145"/>
+      <c r="J22" s="145"/>
+      <c r="K22" s="145"/>
+      <c r="L22" s="145"/>
+      <c r="M22" s="145"/>
+      <c r="N22" s="145"/>
+      <c r="O22" s="145"/>
+      <c r="P22" s="145"/>
+      <c r="Q22" s="145"/>
     </row>
     <row r="23" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C23" s="141"/>
-      <c r="D23" s="141"/>
-      <c r="E23" s="141"/>
-      <c r="F23" s="141"/>
-      <c r="G23" s="141"/>
-      <c r="H23" s="141"/>
-      <c r="I23" s="141"/>
-      <c r="J23" s="141"/>
-      <c r="K23" s="141"/>
-      <c r="L23" s="141"/>
-      <c r="M23" s="141"/>
-      <c r="N23" s="141"/>
-      <c r="O23" s="141"/>
-      <c r="P23" s="141"/>
-      <c r="Q23" s="141"/>
+      <c r="C23" s="145"/>
+      <c r="D23" s="145"/>
+      <c r="E23" s="145"/>
+      <c r="F23" s="145"/>
+      <c r="G23" s="145"/>
+      <c r="H23" s="145"/>
+      <c r="I23" s="145"/>
+      <c r="J23" s="145"/>
+      <c r="K23" s="145"/>
+      <c r="L23" s="145"/>
+      <c r="M23" s="145"/>
+      <c r="N23" s="145"/>
+      <c r="O23" s="145"/>
+      <c r="P23" s="145"/>
+      <c r="Q23" s="145"/>
     </row>
     <row r="24" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C24" s="141"/>
-      <c r="D24" s="141"/>
-      <c r="E24" s="141"/>
-      <c r="F24" s="141"/>
-      <c r="G24" s="141"/>
-      <c r="H24" s="141"/>
-      <c r="I24" s="141"/>
-      <c r="J24" s="141"/>
-      <c r="K24" s="141"/>
-      <c r="L24" s="141"/>
-      <c r="M24" s="141"/>
-      <c r="N24" s="141"/>
-      <c r="O24" s="141"/>
-      <c r="P24" s="141"/>
-      <c r="Q24" s="141"/>
+      <c r="C24" s="145"/>
+      <c r="D24" s="145"/>
+      <c r="E24" s="145"/>
+      <c r="F24" s="145"/>
+      <c r="G24" s="145"/>
+      <c r="H24" s="145"/>
+      <c r="I24" s="145"/>
+      <c r="J24" s="145"/>
+      <c r="K24" s="145"/>
+      <c r="L24" s="145"/>
+      <c r="M24" s="145"/>
+      <c r="N24" s="145"/>
+      <c r="O24" s="145"/>
+      <c r="P24" s="145"/>
+      <c r="Q24" s="145"/>
     </row>
     <row r="25" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C25" s="141"/>
-      <c r="D25" s="141"/>
-      <c r="E25" s="141"/>
-      <c r="F25" s="141"/>
-      <c r="G25" s="141"/>
-      <c r="H25" s="141"/>
-      <c r="I25" s="141"/>
-      <c r="J25" s="141"/>
-      <c r="K25" s="141"/>
-      <c r="L25" s="141"/>
-      <c r="M25" s="141"/>
-      <c r="N25" s="141"/>
-      <c r="O25" s="141"/>
-      <c r="P25" s="141"/>
-      <c r="Q25" s="141"/>
+      <c r="C25" s="145"/>
+      <c r="D25" s="145"/>
+      <c r="E25" s="145"/>
+      <c r="F25" s="145"/>
+      <c r="G25" s="145"/>
+      <c r="H25" s="145"/>
+      <c r="I25" s="145"/>
+      <c r="J25" s="145"/>
+      <c r="K25" s="145"/>
+      <c r="L25" s="145"/>
+      <c r="M25" s="145"/>
+      <c r="N25" s="145"/>
+      <c r="O25" s="145"/>
+      <c r="P25" s="145"/>
+      <c r="Q25" s="145"/>
     </row>
     <row r="26" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C26" s="141"/>
-      <c r="D26" s="141"/>
-      <c r="E26" s="141"/>
-      <c r="F26" s="141"/>
-      <c r="G26" s="141"/>
-      <c r="H26" s="141"/>
-      <c r="I26" s="141"/>
-      <c r="J26" s="141"/>
-      <c r="K26" s="141"/>
-      <c r="L26" s="141"/>
-      <c r="M26" s="141"/>
-      <c r="N26" s="141"/>
-      <c r="O26" s="141"/>
-      <c r="P26" s="141"/>
-      <c r="Q26" s="141"/>
+      <c r="C26" s="145"/>
+      <c r="D26" s="145"/>
+      <c r="E26" s="145"/>
+      <c r="F26" s="145"/>
+      <c r="G26" s="145"/>
+      <c r="H26" s="145"/>
+      <c r="I26" s="145"/>
+      <c r="J26" s="145"/>
+      <c r="K26" s="145"/>
+      <c r="L26" s="145"/>
+      <c r="M26" s="145"/>
+      <c r="N26" s="145"/>
+      <c r="O26" s="145"/>
+      <c r="P26" s="145"/>
+      <c r="Q26" s="145"/>
     </row>
     <row r="27" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C27" s="141"/>
-      <c r="D27" s="141"/>
-      <c r="E27" s="141"/>
-      <c r="F27" s="141"/>
-      <c r="G27" s="141"/>
-      <c r="H27" s="141"/>
-      <c r="I27" s="141"/>
-      <c r="J27" s="141"/>
-      <c r="K27" s="141"/>
-      <c r="L27" s="141"/>
-      <c r="M27" s="141"/>
-      <c r="N27" s="141"/>
-      <c r="O27" s="141"/>
-      <c r="P27" s="141"/>
-      <c r="Q27" s="141"/>
+      <c r="C27" s="145"/>
+      <c r="D27" s="145"/>
+      <c r="E27" s="145"/>
+      <c r="F27" s="145"/>
+      <c r="G27" s="145"/>
+      <c r="H27" s="145"/>
+      <c r="I27" s="145"/>
+      <c r="J27" s="145"/>
+      <c r="K27" s="145"/>
+      <c r="L27" s="145"/>
+      <c r="M27" s="145"/>
+      <c r="N27" s="145"/>
+      <c r="O27" s="145"/>
+      <c r="P27" s="145"/>
+      <c r="Q27" s="145"/>
     </row>
     <row r="28" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C28" s="141"/>
-      <c r="D28" s="141"/>
-      <c r="E28" s="141"/>
-      <c r="F28" s="141"/>
-      <c r="G28" s="141"/>
-      <c r="H28" s="141"/>
-      <c r="I28" s="141"/>
-      <c r="J28" s="141"/>
-      <c r="K28" s="141"/>
-      <c r="L28" s="141"/>
-      <c r="M28" s="141"/>
-      <c r="N28" s="141"/>
-      <c r="O28" s="141"/>
-      <c r="P28" s="141"/>
-      <c r="Q28" s="141"/>
+      <c r="C28" s="145"/>
+      <c r="D28" s="145"/>
+      <c r="E28" s="145"/>
+      <c r="F28" s="145"/>
+      <c r="G28" s="145"/>
+      <c r="H28" s="145"/>
+      <c r="I28" s="145"/>
+      <c r="J28" s="145"/>
+      <c r="K28" s="145"/>
+      <c r="L28" s="145"/>
+      <c r="M28" s="145"/>
+      <c r="N28" s="145"/>
+      <c r="O28" s="145"/>
+      <c r="P28" s="145"/>
+      <c r="Q28" s="145"/>
     </row>
     <row r="29" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C29" s="141"/>
-      <c r="D29" s="141"/>
-      <c r="E29" s="141"/>
-      <c r="F29" s="141"/>
-      <c r="G29" s="141"/>
-      <c r="H29" s="141"/>
-      <c r="I29" s="141"/>
-      <c r="J29" s="141"/>
-      <c r="K29" s="141"/>
-      <c r="L29" s="141"/>
-      <c r="M29" s="141"/>
-      <c r="N29" s="141"/>
-      <c r="O29" s="141"/>
-      <c r="P29" s="141"/>
-      <c r="Q29" s="141"/>
+      <c r="C29" s="145"/>
+      <c r="D29" s="145"/>
+      <c r="E29" s="145"/>
+      <c r="F29" s="145"/>
+      <c r="G29" s="145"/>
+      <c r="H29" s="145"/>
+      <c r="I29" s="145"/>
+      <c r="J29" s="145"/>
+      <c r="K29" s="145"/>
+      <c r="L29" s="145"/>
+      <c r="M29" s="145"/>
+      <c r="N29" s="145"/>
+      <c r="O29" s="145"/>
+      <c r="P29" s="145"/>
+      <c r="Q29" s="145"/>
     </row>
     <row r="30" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C30" s="141"/>
-      <c r="D30" s="141"/>
-      <c r="E30" s="141"/>
-      <c r="F30" s="141"/>
-      <c r="G30" s="141"/>
-      <c r="H30" s="141"/>
-      <c r="I30" s="141"/>
-      <c r="J30" s="141"/>
-      <c r="K30" s="141"/>
-      <c r="L30" s="141"/>
-      <c r="M30" s="141"/>
-      <c r="N30" s="141"/>
-      <c r="O30" s="141"/>
-      <c r="P30" s="141"/>
-      <c r="Q30" s="141"/>
+      <c r="C30" s="145"/>
+      <c r="D30" s="145"/>
+      <c r="E30" s="145"/>
+      <c r="F30" s="145"/>
+      <c r="G30" s="145"/>
+      <c r="H30" s="145"/>
+      <c r="I30" s="145"/>
+      <c r="J30" s="145"/>
+      <c r="K30" s="145"/>
+      <c r="L30" s="145"/>
+      <c r="M30" s="145"/>
+      <c r="N30" s="145"/>
+      <c r="O30" s="145"/>
+      <c r="P30" s="145"/>
+      <c r="Q30" s="145"/>
     </row>
     <row r="31" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C31" s="141"/>
-      <c r="D31" s="141"/>
-      <c r="E31" s="141"/>
-      <c r="F31" s="141"/>
-      <c r="G31" s="141"/>
-      <c r="H31" s="141"/>
-      <c r="I31" s="141"/>
-      <c r="J31" s="141"/>
-      <c r="K31" s="141"/>
-      <c r="L31" s="141"/>
-      <c r="M31" s="141"/>
-      <c r="N31" s="141"/>
-      <c r="O31" s="141"/>
-      <c r="P31" s="141"/>
-      <c r="Q31" s="141"/>
+      <c r="C31" s="145"/>
+      <c r="D31" s="145"/>
+      <c r="E31" s="145"/>
+      <c r="F31" s="145"/>
+      <c r="G31" s="145"/>
+      <c r="H31" s="145"/>
+      <c r="I31" s="145"/>
+      <c r="J31" s="145"/>
+      <c r="K31" s="145"/>
+      <c r="L31" s="145"/>
+      <c r="M31" s="145"/>
+      <c r="N31" s="145"/>
+      <c r="O31" s="145"/>
+      <c r="P31" s="145"/>
+      <c r="Q31" s="145"/>
     </row>
     <row r="32" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C32" s="141"/>
-      <c r="D32" s="141"/>
-      <c r="E32" s="141"/>
-      <c r="F32" s="141"/>
-      <c r="G32" s="141"/>
-      <c r="H32" s="141"/>
-      <c r="I32" s="141"/>
-      <c r="J32" s="141"/>
-      <c r="K32" s="141"/>
-      <c r="L32" s="141"/>
-      <c r="M32" s="141"/>
-      <c r="N32" s="141"/>
-      <c r="O32" s="141"/>
-      <c r="P32" s="141"/>
-      <c r="Q32" s="141"/>
+      <c r="C32" s="145"/>
+      <c r="D32" s="145"/>
+      <c r="E32" s="145"/>
+      <c r="F32" s="145"/>
+      <c r="G32" s="145"/>
+      <c r="H32" s="145"/>
+      <c r="I32" s="145"/>
+      <c r="J32" s="145"/>
+      <c r="K32" s="145"/>
+      <c r="L32" s="145"/>
+      <c r="M32" s="145"/>
+      <c r="N32" s="145"/>
+      <c r="O32" s="145"/>
+      <c r="P32" s="145"/>
+      <c r="Q32" s="145"/>
     </row>
     <row r="33" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C33" s="141"/>
-      <c r="D33" s="141"/>
-      <c r="E33" s="141"/>
-      <c r="F33" s="141"/>
-      <c r="G33" s="141"/>
-      <c r="H33" s="141"/>
-      <c r="I33" s="141"/>
-      <c r="J33" s="141"/>
-      <c r="K33" s="141"/>
-      <c r="L33" s="141"/>
-      <c r="M33" s="141"/>
-      <c r="N33" s="141"/>
-      <c r="O33" s="141"/>
-      <c r="P33" s="141"/>
-      <c r="Q33" s="141"/>
+      <c r="C33" s="145"/>
+      <c r="D33" s="145"/>
+      <c r="E33" s="145"/>
+      <c r="F33" s="145"/>
+      <c r="G33" s="145"/>
+      <c r="H33" s="145"/>
+      <c r="I33" s="145"/>
+      <c r="J33" s="145"/>
+      <c r="K33" s="145"/>
+      <c r="L33" s="145"/>
+      <c r="M33" s="145"/>
+      <c r="N33" s="145"/>
+      <c r="O33" s="145"/>
+      <c r="P33" s="145"/>
+      <c r="Q33" s="145"/>
     </row>
     <row r="34" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C34" s="141"/>
-      <c r="D34" s="141"/>
-      <c r="E34" s="141"/>
-      <c r="F34" s="141"/>
-      <c r="G34" s="141"/>
-      <c r="H34" s="141"/>
-      <c r="I34" s="141"/>
-      <c r="J34" s="141"/>
-      <c r="K34" s="141"/>
-      <c r="L34" s="141"/>
-      <c r="M34" s="141"/>
-      <c r="N34" s="141"/>
-      <c r="O34" s="141"/>
-      <c r="P34" s="141"/>
-      <c r="Q34" s="141"/>
+      <c r="C34" s="145"/>
+      <c r="D34" s="145"/>
+      <c r="E34" s="145"/>
+      <c r="F34" s="145"/>
+      <c r="G34" s="145"/>
+      <c r="H34" s="145"/>
+      <c r="I34" s="145"/>
+      <c r="J34" s="145"/>
+      <c r="K34" s="145"/>
+      <c r="L34" s="145"/>
+      <c r="M34" s="145"/>
+      <c r="N34" s="145"/>
+      <c r="O34" s="145"/>
+      <c r="P34" s="145"/>
+      <c r="Q34" s="145"/>
     </row>
     <row r="35" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C35" s="141"/>
-      <c r="D35" s="141"/>
-      <c r="E35" s="141"/>
-      <c r="F35" s="141"/>
-      <c r="G35" s="141"/>
-      <c r="H35" s="141"/>
-      <c r="I35" s="141"/>
-      <c r="J35" s="141"/>
-      <c r="K35" s="141"/>
-      <c r="L35" s="141"/>
-      <c r="M35" s="141"/>
-      <c r="N35" s="141"/>
-      <c r="O35" s="141"/>
-      <c r="P35" s="141"/>
-      <c r="Q35" s="141"/>
+      <c r="C35" s="145"/>
+      <c r="D35" s="145"/>
+      <c r="E35" s="145"/>
+      <c r="F35" s="145"/>
+      <c r="G35" s="145"/>
+      <c r="H35" s="145"/>
+      <c r="I35" s="145"/>
+      <c r="J35" s="145"/>
+      <c r="K35" s="145"/>
+      <c r="L35" s="145"/>
+      <c r="M35" s="145"/>
+      <c r="N35" s="145"/>
+      <c r="O35" s="145"/>
+      <c r="P35" s="145"/>
+      <c r="Q35" s="145"/>
     </row>
     <row r="36" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C36" s="141"/>
-      <c r="D36" s="141"/>
-      <c r="E36" s="141"/>
-      <c r="F36" s="141"/>
-      <c r="G36" s="141"/>
-      <c r="H36" s="141"/>
-      <c r="I36" s="141"/>
-      <c r="J36" s="141"/>
-      <c r="K36" s="141"/>
-      <c r="L36" s="141"/>
-      <c r="M36" s="141"/>
-      <c r="N36" s="141"/>
-      <c r="O36" s="141"/>
-      <c r="P36" s="141"/>
-      <c r="Q36" s="141"/>
+      <c r="C36" s="145"/>
+      <c r="D36" s="145"/>
+      <c r="E36" s="145"/>
+      <c r="F36" s="145"/>
+      <c r="G36" s="145"/>
+      <c r="H36" s="145"/>
+      <c r="I36" s="145"/>
+      <c r="J36" s="145"/>
+      <c r="K36" s="145"/>
+      <c r="L36" s="145"/>
+      <c r="M36" s="145"/>
+      <c r="N36" s="145"/>
+      <c r="O36" s="145"/>
+      <c r="P36" s="145"/>
+      <c r="Q36" s="145"/>
     </row>
     <row r="37" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C37" s="141"/>
-      <c r="D37" s="141"/>
-      <c r="E37" s="141"/>
-      <c r="F37" s="141"/>
-      <c r="G37" s="141"/>
-      <c r="H37" s="141"/>
-      <c r="I37" s="141"/>
-      <c r="J37" s="141"/>
-      <c r="K37" s="141"/>
-      <c r="L37" s="141"/>
-      <c r="M37" s="141"/>
-      <c r="N37" s="141"/>
-      <c r="O37" s="141"/>
-      <c r="P37" s="141"/>
-      <c r="Q37" s="141"/>
+      <c r="C37" s="145"/>
+      <c r="D37" s="145"/>
+      <c r="E37" s="145"/>
+      <c r="F37" s="145"/>
+      <c r="G37" s="145"/>
+      <c r="H37" s="145"/>
+      <c r="I37" s="145"/>
+      <c r="J37" s="145"/>
+      <c r="K37" s="145"/>
+      <c r="L37" s="145"/>
+      <c r="M37" s="145"/>
+      <c r="N37" s="145"/>
+      <c r="O37" s="145"/>
+      <c r="P37" s="145"/>
+      <c r="Q37" s="145"/>
     </row>
     <row r="38" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C38" s="141"/>
-      <c r="D38" s="141"/>
-      <c r="E38" s="141"/>
-      <c r="F38" s="141"/>
-      <c r="G38" s="141"/>
-      <c r="H38" s="141"/>
-      <c r="I38" s="141"/>
-      <c r="J38" s="141"/>
-      <c r="K38" s="141"/>
-      <c r="L38" s="141"/>
-      <c r="M38" s="141"/>
-      <c r="N38" s="141"/>
-      <c r="O38" s="141"/>
-      <c r="P38" s="141"/>
-      <c r="Q38" s="141"/>
+      <c r="C38" s="145"/>
+      <c r="D38" s="145"/>
+      <c r="E38" s="145"/>
+      <c r="F38" s="145"/>
+      <c r="G38" s="145"/>
+      <c r="H38" s="145"/>
+      <c r="I38" s="145"/>
+      <c r="J38" s="145"/>
+      <c r="K38" s="145"/>
+      <c r="L38" s="145"/>
+      <c r="M38" s="145"/>
+      <c r="N38" s="145"/>
+      <c r="O38" s="145"/>
+      <c r="P38" s="145"/>
+      <c r="Q38" s="145"/>
     </row>
     <row r="39" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C39" s="141"/>
-      <c r="D39" s="141"/>
-      <c r="E39" s="141"/>
-      <c r="F39" s="141"/>
-      <c r="G39" s="141"/>
-      <c r="H39" s="141"/>
-      <c r="I39" s="141"/>
-      <c r="J39" s="141"/>
-      <c r="K39" s="141"/>
-      <c r="L39" s="141"/>
-      <c r="M39" s="141"/>
-      <c r="N39" s="141"/>
-      <c r="O39" s="141"/>
-      <c r="P39" s="141"/>
-      <c r="Q39" s="141"/>
+      <c r="C39" s="145"/>
+      <c r="D39" s="145"/>
+      <c r="E39" s="145"/>
+      <c r="F39" s="145"/>
+      <c r="G39" s="145"/>
+      <c r="H39" s="145"/>
+      <c r="I39" s="145"/>
+      <c r="J39" s="145"/>
+      <c r="K39" s="145"/>
+      <c r="L39" s="145"/>
+      <c r="M39" s="145"/>
+      <c r="N39" s="145"/>
+      <c r="O39" s="145"/>
+      <c r="P39" s="145"/>
+      <c r="Q39" s="145"/>
     </row>
     <row r="40" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C40" s="141"/>
-      <c r="D40" s="141"/>
-      <c r="E40" s="141"/>
-      <c r="F40" s="141"/>
-      <c r="G40" s="141"/>
-      <c r="H40" s="141"/>
-      <c r="I40" s="141"/>
-      <c r="J40" s="141"/>
-      <c r="K40" s="141"/>
-      <c r="L40" s="141"/>
-      <c r="M40" s="141"/>
-      <c r="N40" s="141"/>
-      <c r="O40" s="141"/>
-      <c r="P40" s="141"/>
-      <c r="Q40" s="141"/>
+      <c r="C40" s="145"/>
+      <c r="D40" s="145"/>
+      <c r="E40" s="145"/>
+      <c r="F40" s="145"/>
+      <c r="G40" s="145"/>
+      <c r="H40" s="145"/>
+      <c r="I40" s="145"/>
+      <c r="J40" s="145"/>
+      <c r="K40" s="145"/>
+      <c r="L40" s="145"/>
+      <c r="M40" s="145"/>
+      <c r="N40" s="145"/>
+      <c r="O40" s="145"/>
+      <c r="P40" s="145"/>
+      <c r="Q40" s="145"/>
     </row>
     <row r="41" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C41" s="141"/>
-      <c r="D41" s="141"/>
-      <c r="E41" s="141"/>
-      <c r="F41" s="141"/>
-      <c r="G41" s="141"/>
-      <c r="H41" s="141"/>
-      <c r="I41" s="141"/>
-      <c r="J41" s="141"/>
-      <c r="K41" s="141"/>
-      <c r="L41" s="141"/>
-      <c r="M41" s="141"/>
-      <c r="N41" s="141"/>
-      <c r="O41" s="141"/>
-      <c r="P41" s="141"/>
-      <c r="Q41" s="141"/>
+      <c r="C41" s="145"/>
+      <c r="D41" s="145"/>
+      <c r="E41" s="145"/>
+      <c r="F41" s="145"/>
+      <c r="G41" s="145"/>
+      <c r="H41" s="145"/>
+      <c r="I41" s="145"/>
+      <c r="J41" s="145"/>
+      <c r="K41" s="145"/>
+      <c r="L41" s="145"/>
+      <c r="M41" s="145"/>
+      <c r="N41" s="145"/>
+      <c r="O41" s="145"/>
+      <c r="P41" s="145"/>
+      <c r="Q41" s="145"/>
     </row>
     <row r="42" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C42" s="141"/>
-      <c r="D42" s="141"/>
-      <c r="E42" s="141"/>
-      <c r="F42" s="141"/>
-      <c r="G42" s="141"/>
-      <c r="H42" s="141"/>
-      <c r="I42" s="141"/>
-      <c r="J42" s="141"/>
-      <c r="K42" s="141"/>
-      <c r="L42" s="141"/>
-      <c r="M42" s="141"/>
-      <c r="N42" s="141"/>
-      <c r="O42" s="141"/>
-      <c r="P42" s="141"/>
-      <c r="Q42" s="141"/>
+      <c r="C42" s="145"/>
+      <c r="D42" s="145"/>
+      <c r="E42" s="145"/>
+      <c r="F42" s="145"/>
+      <c r="G42" s="145"/>
+      <c r="H42" s="145"/>
+      <c r="I42" s="145"/>
+      <c r="J42" s="145"/>
+      <c r="K42" s="145"/>
+      <c r="L42" s="145"/>
+      <c r="M42" s="145"/>
+      <c r="N42" s="145"/>
+      <c r="O42" s="145"/>
+      <c r="P42" s="145"/>
+      <c r="Q42" s="145"/>
     </row>
     <row r="43" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C43" s="141"/>
-      <c r="D43" s="141"/>
-      <c r="E43" s="141"/>
-      <c r="F43" s="141"/>
-      <c r="G43" s="141"/>
-      <c r="H43" s="141"/>
-      <c r="I43" s="141"/>
-      <c r="J43" s="141"/>
-      <c r="K43" s="141"/>
-      <c r="L43" s="141"/>
-      <c r="M43" s="141"/>
-      <c r="N43" s="141"/>
-      <c r="O43" s="141"/>
-      <c r="P43" s="141"/>
-      <c r="Q43" s="141"/>
+      <c r="C43" s="145"/>
+      <c r="D43" s="145"/>
+      <c r="E43" s="145"/>
+      <c r="F43" s="145"/>
+      <c r="G43" s="145"/>
+      <c r="H43" s="145"/>
+      <c r="I43" s="145"/>
+      <c r="J43" s="145"/>
+      <c r="K43" s="145"/>
+      <c r="L43" s="145"/>
+      <c r="M43" s="145"/>
+      <c r="N43" s="145"/>
+      <c r="O43" s="145"/>
+      <c r="P43" s="145"/>
+      <c r="Q43" s="145"/>
     </row>
     <row r="44" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C44" s="141"/>
-      <c r="D44" s="141"/>
-      <c r="E44" s="141"/>
-      <c r="F44" s="141"/>
-      <c r="G44" s="141"/>
-      <c r="H44" s="141"/>
-      <c r="I44" s="141"/>
-      <c r="J44" s="141"/>
-      <c r="K44" s="141"/>
-      <c r="L44" s="141"/>
-      <c r="M44" s="141"/>
-      <c r="N44" s="141"/>
-      <c r="O44" s="141"/>
-      <c r="P44" s="141"/>
-      <c r="Q44" s="141"/>
+      <c r="C44" s="145"/>
+      <c r="D44" s="145"/>
+      <c r="E44" s="145"/>
+      <c r="F44" s="145"/>
+      <c r="G44" s="145"/>
+      <c r="H44" s="145"/>
+      <c r="I44" s="145"/>
+      <c r="J44" s="145"/>
+      <c r="K44" s="145"/>
+      <c r="L44" s="145"/>
+      <c r="M44" s="145"/>
+      <c r="N44" s="145"/>
+      <c r="O44" s="145"/>
+      <c r="P44" s="145"/>
+      <c r="Q44" s="145"/>
     </row>
     <row r="45" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C45" s="141"/>
-      <c r="D45" s="141"/>
-      <c r="E45" s="141"/>
-      <c r="F45" s="141"/>
-      <c r="G45" s="141"/>
-      <c r="H45" s="141"/>
-      <c r="I45" s="141"/>
-      <c r="J45" s="141"/>
-      <c r="K45" s="141"/>
-      <c r="L45" s="141"/>
-      <c r="M45" s="141"/>
-      <c r="N45" s="141"/>
-      <c r="O45" s="141"/>
-      <c r="P45" s="141"/>
-      <c r="Q45" s="141"/>
+      <c r="C45" s="145"/>
+      <c r="D45" s="145"/>
+      <c r="E45" s="145"/>
+      <c r="F45" s="145"/>
+      <c r="G45" s="145"/>
+      <c r="H45" s="145"/>
+      <c r="I45" s="145"/>
+      <c r="J45" s="145"/>
+      <c r="K45" s="145"/>
+      <c r="L45" s="145"/>
+      <c r="M45" s="145"/>
+      <c r="N45" s="145"/>
+      <c r="O45" s="145"/>
+      <c r="P45" s="145"/>
+      <c r="Q45" s="145"/>
     </row>
     <row r="46" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C46" s="141"/>
-      <c r="D46" s="141"/>
-      <c r="E46" s="141"/>
-      <c r="F46" s="141"/>
-      <c r="G46" s="141"/>
-      <c r="H46" s="141"/>
-      <c r="I46" s="141"/>
-      <c r="J46" s="141"/>
-      <c r="K46" s="141"/>
-      <c r="L46" s="141"/>
-      <c r="M46" s="141"/>
-      <c r="N46" s="141"/>
-      <c r="O46" s="141"/>
-      <c r="P46" s="141"/>
-      <c r="Q46" s="141"/>
+      <c r="C46" s="145"/>
+      <c r="D46" s="145"/>
+      <c r="E46" s="145"/>
+      <c r="F46" s="145"/>
+      <c r="G46" s="145"/>
+      <c r="H46" s="145"/>
+      <c r="I46" s="145"/>
+      <c r="J46" s="145"/>
+      <c r="K46" s="145"/>
+      <c r="L46" s="145"/>
+      <c r="M46" s="145"/>
+      <c r="N46" s="145"/>
+      <c r="O46" s="145"/>
+      <c r="P46" s="145"/>
+      <c r="Q46" s="145"/>
     </row>
     <row r="47" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C47" s="141"/>
-      <c r="D47" s="141"/>
-      <c r="E47" s="141"/>
-      <c r="F47" s="141"/>
-      <c r="G47" s="141"/>
-      <c r="H47" s="141"/>
-      <c r="I47" s="141"/>
-      <c r="J47" s="141"/>
-      <c r="K47" s="141"/>
-      <c r="L47" s="141"/>
-      <c r="M47" s="141"/>
-      <c r="N47" s="141"/>
-      <c r="O47" s="141"/>
-      <c r="P47" s="141"/>
-      <c r="Q47" s="141"/>
+      <c r="C47" s="145"/>
+      <c r="D47" s="145"/>
+      <c r="E47" s="145"/>
+      <c r="F47" s="145"/>
+      <c r="G47" s="145"/>
+      <c r="H47" s="145"/>
+      <c r="I47" s="145"/>
+      <c r="J47" s="145"/>
+      <c r="K47" s="145"/>
+      <c r="L47" s="145"/>
+      <c r="M47" s="145"/>
+      <c r="N47" s="145"/>
+      <c r="O47" s="145"/>
+      <c r="P47" s="145"/>
+      <c r="Q47" s="145"/>
     </row>
     <row r="48" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C48" s="141"/>
-      <c r="D48" s="141"/>
-      <c r="E48" s="141"/>
-      <c r="F48" s="141"/>
-      <c r="G48" s="141"/>
-      <c r="H48" s="141"/>
-      <c r="I48" s="141"/>
-      <c r="J48" s="141"/>
-      <c r="K48" s="141"/>
-      <c r="L48" s="141"/>
-      <c r="M48" s="141"/>
-      <c r="N48" s="141"/>
-      <c r="O48" s="141"/>
-      <c r="P48" s="141"/>
-      <c r="Q48" s="141"/>
+      <c r="C48" s="145"/>
+      <c r="D48" s="145"/>
+      <c r="E48" s="145"/>
+      <c r="F48" s="145"/>
+      <c r="G48" s="145"/>
+      <c r="H48" s="145"/>
+      <c r="I48" s="145"/>
+      <c r="J48" s="145"/>
+      <c r="K48" s="145"/>
+      <c r="L48" s="145"/>
+      <c r="M48" s="145"/>
+      <c r="N48" s="145"/>
+      <c r="O48" s="145"/>
+      <c r="P48" s="145"/>
+      <c r="Q48" s="145"/>
     </row>
     <row r="49" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C49" s="141"/>
-      <c r="D49" s="141"/>
-      <c r="E49" s="141"/>
-      <c r="F49" s="141"/>
-      <c r="G49" s="141"/>
-      <c r="H49" s="141"/>
-      <c r="I49" s="141"/>
-      <c r="J49" s="141"/>
-      <c r="K49" s="141"/>
-      <c r="L49" s="141"/>
-      <c r="M49" s="141"/>
-      <c r="N49" s="141"/>
-      <c r="O49" s="141"/>
-      <c r="P49" s="141"/>
-      <c r="Q49" s="141"/>
+      <c r="C49" s="145"/>
+      <c r="D49" s="145"/>
+      <c r="E49" s="145"/>
+      <c r="F49" s="145"/>
+      <c r="G49" s="145"/>
+      <c r="H49" s="145"/>
+      <c r="I49" s="145"/>
+      <c r="J49" s="145"/>
+      <c r="K49" s="145"/>
+      <c r="L49" s="145"/>
+      <c r="M49" s="145"/>
+      <c r="N49" s="145"/>
+      <c r="O49" s="145"/>
+      <c r="P49" s="145"/>
+      <c r="Q49" s="145"/>
     </row>
     <row r="50" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C50" s="141"/>
-      <c r="D50" s="141"/>
-      <c r="E50" s="141"/>
-      <c r="F50" s="141"/>
-      <c r="G50" s="141"/>
-      <c r="H50" s="141"/>
-      <c r="I50" s="141"/>
-      <c r="J50" s="141"/>
-      <c r="K50" s="141"/>
-      <c r="L50" s="141"/>
-      <c r="M50" s="141"/>
-      <c r="N50" s="141"/>
-      <c r="O50" s="141"/>
-      <c r="P50" s="141"/>
-      <c r="Q50" s="141"/>
+      <c r="C50" s="145"/>
+      <c r="D50" s="145"/>
+      <c r="E50" s="145"/>
+      <c r="F50" s="145"/>
+      <c r="G50" s="145"/>
+      <c r="H50" s="145"/>
+      <c r="I50" s="145"/>
+      <c r="J50" s="145"/>
+      <c r="K50" s="145"/>
+      <c r="L50" s="145"/>
+      <c r="M50" s="145"/>
+      <c r="N50" s="145"/>
+      <c r="O50" s="145"/>
+      <c r="P50" s="145"/>
+      <c r="Q50" s="145"/>
     </row>
     <row r="51" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C51" s="141"/>
-      <c r="D51" s="141"/>
-      <c r="E51" s="141"/>
-      <c r="F51" s="141"/>
-      <c r="G51" s="141"/>
-      <c r="H51" s="141"/>
-      <c r="I51" s="141"/>
-      <c r="J51" s="141"/>
-      <c r="K51" s="141"/>
-      <c r="L51" s="141"/>
-      <c r="M51" s="141"/>
-      <c r="N51" s="141"/>
-      <c r="O51" s="141"/>
-      <c r="P51" s="141"/>
-      <c r="Q51" s="141"/>
+      <c r="C51" s="145"/>
+      <c r="D51" s="145"/>
+      <c r="E51" s="145"/>
+      <c r="F51" s="145"/>
+      <c r="G51" s="145"/>
+      <c r="H51" s="145"/>
+      <c r="I51" s="145"/>
+      <c r="J51" s="145"/>
+      <c r="K51" s="145"/>
+      <c r="L51" s="145"/>
+      <c r="M51" s="145"/>
+      <c r="N51" s="145"/>
+      <c r="O51" s="145"/>
+      <c r="P51" s="145"/>
+      <c r="Q51" s="145"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5931,36 +5931,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="143" t="s">
         <v>395</v>
       </c>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
-      <c r="M2" s="163"/>
-      <c r="N2" s="163"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
+      <c r="K2" s="143"/>
+      <c r="L2" s="143"/>
+      <c r="M2" s="143"/>
+      <c r="N2" s="143"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="163"/>
-      <c r="C3" s="163"/>
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="163"/>
-      <c r="K3" s="163"/>
-      <c r="L3" s="163"/>
-      <c r="M3" s="163"/>
-      <c r="N3" s="163"/>
+      <c r="B3" s="143"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="143"/>
+      <c r="I3" s="143"/>
+      <c r="J3" s="143"/>
+      <c r="K3" s="143"/>
+      <c r="L3" s="143"/>
+      <c r="M3" s="143"/>
+      <c r="N3" s="143"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="69" t="s">
@@ -6717,38 +6717,38 @@
       </c>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B23" s="163" t="s">
+      <c r="B23" s="143" t="s">
         <v>413</v>
       </c>
-      <c r="C23" s="163"/>
-      <c r="D23" s="163"/>
-      <c r="F23" s="163" t="s">
+      <c r="C23" s="143"/>
+      <c r="D23" s="143"/>
+      <c r="F23" s="143" t="s">
         <v>414</v>
       </c>
-      <c r="G23" s="163"/>
-      <c r="H23" s="163"/>
-      <c r="I23" s="163"/>
-      <c r="J23" s="163"/>
-      <c r="K23" s="163"/>
-      <c r="L23" s="163"/>
-      <c r="M23" s="163"/>
-      <c r="N23" s="163"/>
-      <c r="O23" s="163"/>
+      <c r="G23" s="143"/>
+      <c r="H23" s="143"/>
+      <c r="I23" s="143"/>
+      <c r="J23" s="143"/>
+      <c r="K23" s="143"/>
+      <c r="L23" s="143"/>
+      <c r="M23" s="143"/>
+      <c r="N23" s="143"/>
+      <c r="O23" s="143"/>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B24" s="163"/>
-      <c r="C24" s="163"/>
-      <c r="D24" s="163"/>
-      <c r="F24" s="163"/>
-      <c r="G24" s="163"/>
-      <c r="H24" s="163"/>
-      <c r="I24" s="163"/>
-      <c r="J24" s="163"/>
-      <c r="K24" s="163"/>
-      <c r="L24" s="163"/>
-      <c r="M24" s="163"/>
-      <c r="N24" s="163"/>
-      <c r="O24" s="163"/>
+      <c r="B24" s="143"/>
+      <c r="C24" s="143"/>
+      <c r="D24" s="143"/>
+      <c r="F24" s="143"/>
+      <c r="G24" s="143"/>
+      <c r="H24" s="143"/>
+      <c r="I24" s="143"/>
+      <c r="J24" s="143"/>
+      <c r="K24" s="143"/>
+      <c r="L24" s="143"/>
+      <c r="M24" s="143"/>
+      <c r="N24" s="143"/>
+      <c r="O24" s="143"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B25" s="44" t="s">
@@ -7286,40 +7286,40 @@
       <c r="O40" s="5"/>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B43" s="163" t="s">
+      <c r="B43" s="143" t="s">
         <v>497</v>
       </c>
-      <c r="C43" s="163"/>
-      <c r="D43" s="163"/>
-      <c r="E43" s="163"/>
-      <c r="F43" s="163"/>
-      <c r="G43" s="163"/>
-      <c r="H43" s="163"/>
-      <c r="I43" s="163"/>
-      <c r="J43" s="163"/>
-      <c r="K43" s="163"/>
-      <c r="L43" s="163"/>
-      <c r="M43" s="163"/>
-      <c r="N43" s="163"/>
-      <c r="O43" s="163"/>
-      <c r="P43" s="163"/>
+      <c r="C43" s="143"/>
+      <c r="D43" s="143"/>
+      <c r="E43" s="143"/>
+      <c r="F43" s="143"/>
+      <c r="G43" s="143"/>
+      <c r="H43" s="143"/>
+      <c r="I43" s="143"/>
+      <c r="J43" s="143"/>
+      <c r="K43" s="143"/>
+      <c r="L43" s="143"/>
+      <c r="M43" s="143"/>
+      <c r="N43" s="143"/>
+      <c r="O43" s="143"/>
+      <c r="P43" s="143"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="163"/>
-      <c r="C44" s="163"/>
-      <c r="D44" s="163"/>
-      <c r="E44" s="163"/>
-      <c r="F44" s="163"/>
-      <c r="G44" s="163"/>
-      <c r="H44" s="163"/>
-      <c r="I44" s="163"/>
-      <c r="J44" s="163"/>
-      <c r="K44" s="163"/>
-      <c r="L44" s="163"/>
-      <c r="M44" s="163"/>
-      <c r="N44" s="163"/>
-      <c r="O44" s="163"/>
-      <c r="P44" s="163"/>
+      <c r="B44" s="143"/>
+      <c r="C44" s="143"/>
+      <c r="D44" s="143"/>
+      <c r="E44" s="143"/>
+      <c r="F44" s="143"/>
+      <c r="G44" s="143"/>
+      <c r="H44" s="143"/>
+      <c r="I44" s="143"/>
+      <c r="J44" s="143"/>
+      <c r="K44" s="143"/>
+      <c r="L44" s="143"/>
+      <c r="M44" s="143"/>
+      <c r="N44" s="143"/>
+      <c r="O44" s="143"/>
+      <c r="P44" s="143"/>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B45" s="101" t="s">
@@ -9040,11 +9040,11 @@
       <c r="P91" s="5"/>
     </row>
     <row r="92" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B92" s="209" t="s">
-        <v>1123</v>
-      </c>
-      <c r="C92" s="209" t="s">
-        <v>1119</v>
+      <c r="B92" s="140" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C92" s="140" t="s">
+        <v>1118</v>
       </c>
       <c r="D92" s="102" t="s">
         <v>440</v>
@@ -9052,82 +9052,82 @@
       <c r="E92" s="102" t="s">
         <v>435</v>
       </c>
-      <c r="F92" s="209" t="s">
+      <c r="F92" s="140" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G92" s="140" t="s">
+        <v>1126</v>
+      </c>
+      <c r="H92" s="140" t="s">
+        <v>1127</v>
+      </c>
+      <c r="I92" s="140" t="s">
+        <v>1123</v>
+      </c>
+      <c r="J92" s="140" t="s">
         <v>1130</v>
       </c>
-      <c r="G92" s="209" t="s">
-        <v>1127</v>
-      </c>
-      <c r="H92" s="209" t="s">
+      <c r="K92" s="140" t="s">
+        <v>1124</v>
+      </c>
+      <c r="L92" s="140" t="s">
+        <v>1125</v>
+      </c>
+      <c r="M92" s="140" t="s">
+        <v>1131</v>
+      </c>
+      <c r="N92" s="140" t="s">
+        <v>1132</v>
+      </c>
+      <c r="O92" s="140" t="s">
+        <v>1106</v>
+      </c>
+      <c r="P92" s="140" t="s">
         <v>1128</v>
       </c>
-      <c r="I92" s="209" t="s">
-        <v>1124</v>
-      </c>
-      <c r="J92" s="209" t="s">
-        <v>1131</v>
-      </c>
-      <c r="K92" s="209" t="s">
-        <v>1125</v>
-      </c>
-      <c r="L92" s="209" t="s">
-        <v>1126</v>
-      </c>
-      <c r="M92" s="209" t="s">
-        <v>1132</v>
-      </c>
-      <c r="N92" s="209" t="s">
-        <v>1133</v>
-      </c>
-      <c r="O92" s="209" t="s">
-        <v>1106</v>
-      </c>
-      <c r="P92" s="209" t="s">
-        <v>1129</v>
-      </c>
     </row>
     <row r="93" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D93" s="211" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E93" s="211" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F93" s="211" t="s">
+      <c r="D93" s="142" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E93" s="142" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F93" s="142" t="s">
         <v>431</v>
       </c>
-      <c r="G93" s="211" t="s">
+      <c r="G93" s="142" t="s">
         <v>431</v>
       </c>
-      <c r="H93" s="211" t="s">
+      <c r="H93" s="142" t="s">
         <v>431</v>
       </c>
-      <c r="I93" s="211" t="s">
+      <c r="I93" s="142" t="s">
         <v>431</v>
       </c>
-      <c r="J93" s="211" t="s">
+      <c r="J93" s="142" t="s">
         <v>431</v>
       </c>
-      <c r="K93" s="211" t="s">
+      <c r="K93" s="142" t="s">
         <v>431</v>
       </c>
-      <c r="L93" s="211" t="s">
+      <c r="L93" s="142" t="s">
         <v>431</v>
       </c>
-      <c r="M93" s="211" t="s">
+      <c r="M93" s="142" t="s">
         <v>431</v>
       </c>
-      <c r="N93" s="211" t="s">
+      <c r="N93" s="142" t="s">
         <v>431</v>
       </c>
-      <c r="O93" s="211" t="s">
+      <c r="O93" s="142" t="s">
         <v>431</v>
       </c>
-      <c r="P93" s="211" t="s">
-        <v>1121</v>
-      </c>
-      <c r="Q93" s="210" t="s">
+      <c r="P93" s="142" t="s">
         <v>1120</v>
+      </c>
+      <c r="Q93" s="141" t="s">
+        <v>1119</v>
       </c>
     </row>
   </sheetData>
@@ -9178,7 +9178,7 @@
       <c r="B3" s="63" t="s">
         <v>627</v>
       </c>
-      <c r="D3" s="175" t="s">
+      <c r="D3" s="182" t="s">
         <v>628</v>
       </c>
       <c r="F3" s="180" t="s">
@@ -9198,7 +9198,7 @@
       <c r="B4" s="63" t="s">
         <v>632</v>
       </c>
-      <c r="D4" s="176"/>
+      <c r="D4" s="183"/>
       <c r="F4" s="181"/>
       <c r="G4" s="181"/>
       <c r="H4" s="181"/>
@@ -9208,7 +9208,7 @@
       <c r="K4" s="63" t="s">
         <v>634</v>
       </c>
-      <c r="L4" s="179" t="s">
+      <c r="L4" s="178" t="s">
         <v>635</v>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       <c r="B5" s="63" t="s">
         <v>636</v>
       </c>
-      <c r="D5" s="176"/>
+      <c r="D5" s="183"/>
       <c r="F5" s="181"/>
       <c r="G5" s="181"/>
       <c r="H5" s="181"/>
@@ -9226,13 +9226,13 @@
       <c r="K5" s="63" t="s">
         <v>638</v>
       </c>
-      <c r="L5" s="178"/>
+      <c r="L5" s="179"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="63" t="s">
         <v>639</v>
       </c>
-      <c r="D6" s="176"/>
+      <c r="D6" s="183"/>
       <c r="F6" s="181"/>
       <c r="G6" s="181"/>
       <c r="H6" s="181"/>
@@ -9242,13 +9242,13 @@
       <c r="K6" s="63" t="s">
         <v>641</v>
       </c>
-      <c r="L6" s="178"/>
+      <c r="L6" s="179"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="63" t="s">
         <v>642</v>
       </c>
-      <c r="D7" s="176"/>
+      <c r="D7" s="183"/>
       <c r="F7" s="181"/>
       <c r="G7" s="181"/>
       <c r="H7" s="181"/>
@@ -9258,13 +9258,13 @@
       <c r="K7" s="63" t="s">
         <v>636</v>
       </c>
-      <c r="L7" s="178"/>
+      <c r="L7" s="179"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="63" t="s">
         <v>641</v>
       </c>
-      <c r="D8" s="176"/>
+      <c r="D8" s="183"/>
       <c r="E8" s="62"/>
       <c r="F8" s="62"/>
       <c r="G8" s="62"/>
@@ -9278,7 +9278,7 @@
       <c r="B9" s="63" t="s">
         <v>644</v>
       </c>
-      <c r="D9" s="176"/>
+      <c r="D9" s="183"/>
       <c r="F9" s="64"/>
       <c r="G9" s="65" t="s">
         <v>630</v>
@@ -9298,14 +9298,14 @@
       <c r="B10" s="63" t="s">
         <v>634</v>
       </c>
-      <c r="D10" s="176"/>
+      <c r="D10" s="183"/>
       <c r="F10" s="67" t="s">
         <v>645</v>
       </c>
       <c r="G10" s="63" t="s">
         <v>627</v>
       </c>
-      <c r="H10" s="178" t="s">
+      <c r="H10" s="179" t="s">
         <v>646</v>
       </c>
       <c r="J10" s="67" t="s">
@@ -9314,7 +9314,7 @@
       <c r="K10" s="63" t="s">
         <v>634</v>
       </c>
-      <c r="L10" s="179" t="s">
+      <c r="L10" s="178" t="s">
         <v>648</v>
       </c>
     </row>
@@ -9322,61 +9322,61 @@
       <c r="B11" s="63" t="s">
         <v>638</v>
       </c>
-      <c r="D11" s="176"/>
+      <c r="D11" s="183"/>
       <c r="F11" s="67" t="s">
         <v>649</v>
       </c>
       <c r="G11" s="63" t="s">
         <v>636</v>
       </c>
-      <c r="H11" s="178"/>
+      <c r="H11" s="179"/>
       <c r="J11" s="67" t="s">
         <v>650</v>
       </c>
       <c r="K11" s="63" t="s">
         <v>651</v>
       </c>
-      <c r="L11" s="178"/>
+      <c r="L11" s="179"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="63" t="s">
         <v>651</v>
       </c>
-      <c r="D12" s="176"/>
+      <c r="D12" s="183"/>
       <c r="F12" s="67" t="s">
         <v>652</v>
       </c>
       <c r="G12" s="63" t="s">
         <v>642</v>
       </c>
-      <c r="H12" s="178"/>
+      <c r="H12" s="179"/>
       <c r="J12" s="67" t="s">
         <v>653</v>
       </c>
       <c r="K12" s="63" t="s">
         <v>639</v>
       </c>
-      <c r="L12" s="178"/>
+      <c r="L12" s="179"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D13" s="176"/>
+      <c r="D13" s="183"/>
       <c r="F13" s="67" t="s">
         <v>654</v>
       </c>
       <c r="G13" s="63" t="s">
         <v>632</v>
       </c>
-      <c r="H13" s="178"/>
+      <c r="H13" s="179"/>
       <c r="J13" s="67" t="s">
         <v>655</v>
       </c>
       <c r="K13" s="63" t="s">
         <v>638</v>
       </c>
-      <c r="L13" s="178"/>
+      <c r="L13" s="179"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D14" s="176"/>
+      <c r="D14" s="183"/>
       <c r="E14" s="62"/>
       <c r="F14" s="62"/>
       <c r="G14" s="62"/>
@@ -9387,7 +9387,7 @@
       <c r="L14" s="62"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D15" s="176"/>
+      <c r="D15" s="183"/>
       <c r="F15" s="64"/>
       <c r="G15" s="65" t="s">
         <v>630</v>
@@ -9404,14 +9404,14 @@
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D16" s="176"/>
+      <c r="D16" s="183"/>
       <c r="F16" s="67" t="s">
         <v>656</v>
       </c>
       <c r="G16" s="63" t="s">
         <v>644</v>
       </c>
-      <c r="H16" s="178" t="s">
+      <c r="H16" s="179" t="s">
         <v>657</v>
       </c>
       <c r="J16" s="67" t="s">
@@ -9420,63 +9420,63 @@
       <c r="K16" s="63" t="s">
         <v>639</v>
       </c>
-      <c r="L16" s="179" t="s">
+      <c r="L16" s="178" t="s">
         <v>659</v>
       </c>
     </row>
     <row r="17" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D17" s="176"/>
+      <c r="D17" s="183"/>
       <c r="F17" s="67" t="s">
         <v>660</v>
       </c>
       <c r="G17" s="63" t="s">
         <v>627</v>
       </c>
-      <c r="H17" s="178"/>
+      <c r="H17" s="179"/>
       <c r="J17" s="67" t="s">
         <v>661</v>
       </c>
       <c r="K17" s="63" t="s">
         <v>642</v>
       </c>
-      <c r="L17" s="178"/>
+      <c r="L17" s="179"/>
     </row>
     <row r="18" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D18" s="176"/>
+      <c r="D18" s="183"/>
       <c r="F18" s="67" t="s">
         <v>662</v>
       </c>
       <c r="G18" s="63" t="s">
         <v>632</v>
       </c>
-      <c r="H18" s="178"/>
+      <c r="H18" s="179"/>
       <c r="J18" s="67" t="s">
         <v>663</v>
       </c>
       <c r="K18" s="63" t="s">
         <v>634</v>
       </c>
-      <c r="L18" s="178"/>
+      <c r="L18" s="179"/>
     </row>
     <row r="19" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D19" s="176"/>
+      <c r="D19" s="183"/>
       <c r="F19" s="67" t="s">
         <v>664</v>
       </c>
       <c r="G19" s="63" t="s">
         <v>639</v>
       </c>
-      <c r="H19" s="178"/>
+      <c r="H19" s="179"/>
       <c r="J19" s="67" t="s">
         <v>665</v>
       </c>
       <c r="K19" s="63" t="s">
         <v>641</v>
       </c>
-      <c r="L19" s="178"/>
+      <c r="L19" s="179"/>
     </row>
     <row r="20" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D20" s="176"/>
+      <c r="D20" s="183"/>
       <c r="E20" s="62"/>
       <c r="F20" s="62"/>
       <c r="G20" s="62"/>
@@ -9487,7 +9487,7 @@
       <c r="L20" s="62"/>
     </row>
     <row r="21" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D21" s="176"/>
+      <c r="D21" s="183"/>
       <c r="F21" s="64"/>
       <c r="G21" s="65" t="s">
         <v>630</v>
@@ -9504,14 +9504,14 @@
       </c>
     </row>
     <row r="22" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D22" s="176"/>
+      <c r="D22" s="183"/>
       <c r="F22" s="67" t="s">
         <v>666</v>
       </c>
       <c r="G22" s="63" t="s">
         <v>642</v>
       </c>
-      <c r="H22" s="178" t="s">
+      <c r="H22" s="179" t="s">
         <v>667</v>
       </c>
       <c r="J22" s="67" t="s">
@@ -9520,63 +9520,63 @@
       <c r="K22" s="63" t="s">
         <v>641</v>
       </c>
-      <c r="L22" s="179" t="s">
+      <c r="L22" s="178" t="s">
         <v>669</v>
       </c>
     </row>
     <row r="23" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D23" s="176"/>
+      <c r="D23" s="183"/>
       <c r="F23" s="67" t="s">
         <v>670</v>
       </c>
       <c r="G23" s="63" t="s">
         <v>644</v>
       </c>
-      <c r="H23" s="178"/>
+      <c r="H23" s="179"/>
       <c r="J23" s="67" t="s">
         <v>671</v>
       </c>
       <c r="K23" s="63" t="s">
         <v>651</v>
       </c>
-      <c r="L23" s="178"/>
+      <c r="L23" s="179"/>
     </row>
     <row r="24" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D24" s="176"/>
+      <c r="D24" s="183"/>
       <c r="F24" s="67" t="s">
         <v>672</v>
       </c>
       <c r="G24" s="63" t="s">
         <v>636</v>
       </c>
-      <c r="H24" s="178"/>
+      <c r="H24" s="179"/>
       <c r="J24" s="67" t="s">
         <v>673</v>
       </c>
       <c r="K24" s="63" t="s">
         <v>634</v>
       </c>
-      <c r="L24" s="178"/>
+      <c r="L24" s="179"/>
     </row>
     <row r="25" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D25" s="176"/>
+      <c r="D25" s="183"/>
       <c r="F25" s="67" t="s">
         <v>674</v>
       </c>
       <c r="G25" s="63" t="s">
         <v>627</v>
       </c>
-      <c r="H25" s="178"/>
+      <c r="H25" s="179"/>
       <c r="J25" s="67" t="s">
         <v>675</v>
       </c>
       <c r="K25" s="63" t="s">
         <v>638</v>
       </c>
-      <c r="L25" s="178"/>
+      <c r="L25" s="179"/>
     </row>
     <row r="26" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D26" s="176"/>
+      <c r="D26" s="183"/>
       <c r="E26" s="62"/>
       <c r="F26" s="62"/>
       <c r="G26" s="62"/>
@@ -9587,7 +9587,7 @@
       <c r="L26" s="62"/>
     </row>
     <row r="27" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D27" s="176"/>
+      <c r="D27" s="183"/>
       <c r="F27" s="64"/>
       <c r="G27" s="65" t="s">
         <v>630</v>
@@ -9604,14 +9604,14 @@
       </c>
     </row>
     <row r="28" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D28" s="176"/>
+      <c r="D28" s="183"/>
       <c r="F28" s="67" t="s">
         <v>676</v>
       </c>
       <c r="G28" s="63" t="s">
         <v>642</v>
       </c>
-      <c r="H28" s="178" t="s">
+      <c r="H28" s="179" t="s">
         <v>131</v>
       </c>
       <c r="J28" s="67" t="s">
@@ -9620,63 +9620,63 @@
       <c r="K28" s="63" t="s">
         <v>638</v>
       </c>
-      <c r="L28" s="178" t="s">
+      <c r="L28" s="179" t="s">
         <v>678</v>
       </c>
     </row>
     <row r="29" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D29" s="176"/>
+      <c r="D29" s="183"/>
       <c r="F29" s="67" t="s">
         <v>679</v>
       </c>
       <c r="G29" s="63" t="s">
         <v>632</v>
       </c>
-      <c r="H29" s="178"/>
+      <c r="H29" s="179"/>
       <c r="J29" s="67" t="s">
         <v>680</v>
       </c>
       <c r="K29" s="63" t="s">
         <v>639</v>
       </c>
-      <c r="L29" s="178"/>
+      <c r="L29" s="179"/>
     </row>
     <row r="30" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D30" s="176"/>
+      <c r="D30" s="183"/>
       <c r="F30" s="67" t="s">
         <v>681</v>
       </c>
       <c r="G30" s="63" t="s">
         <v>627</v>
       </c>
-      <c r="H30" s="178"/>
+      <c r="H30" s="179"/>
       <c r="J30" s="67" t="s">
         <v>682</v>
       </c>
       <c r="K30" s="63" t="s">
         <v>651</v>
       </c>
-      <c r="L30" s="178"/>
+      <c r="L30" s="179"/>
     </row>
     <row r="31" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D31" s="176"/>
+      <c r="D31" s="183"/>
       <c r="F31" s="67" t="s">
         <v>683</v>
       </c>
       <c r="G31" s="63" t="s">
         <v>644</v>
       </c>
-      <c r="H31" s="178"/>
+      <c r="H31" s="179"/>
       <c r="J31" s="67" t="s">
         <v>684</v>
       </c>
       <c r="K31" s="63" t="s">
         <v>634</v>
       </c>
-      <c r="L31" s="178"/>
+      <c r="L31" s="179"/>
     </row>
     <row r="32" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D32" s="176"/>
+      <c r="D32" s="183"/>
       <c r="E32" s="62"/>
       <c r="F32" s="62"/>
       <c r="G32" s="62"/>
@@ -9687,7 +9687,7 @@
       <c r="L32" s="62"/>
     </row>
     <row r="33" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D33" s="176"/>
+      <c r="D33" s="183"/>
       <c r="F33" s="64"/>
       <c r="G33" s="65" t="s">
         <v>630</v>
@@ -9704,14 +9704,14 @@
       </c>
     </row>
     <row r="34" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D34" s="176"/>
+      <c r="D34" s="183"/>
       <c r="F34" s="67" t="s">
         <v>685</v>
       </c>
       <c r="G34" s="63" t="s">
         <v>632</v>
       </c>
-      <c r="H34" s="179" t="s">
+      <c r="H34" s="178" t="s">
         <v>686</v>
       </c>
       <c r="J34" s="67" t="s">
@@ -9720,63 +9720,63 @@
       <c r="K34" s="63" t="s">
         <v>639</v>
       </c>
-      <c r="L34" s="179" t="s">
+      <c r="L34" s="178" t="s">
         <v>688</v>
       </c>
     </row>
     <row r="35" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D35" s="176"/>
+      <c r="D35" s="183"/>
       <c r="F35" s="67" t="s">
         <v>689</v>
       </c>
       <c r="G35" s="63" t="s">
         <v>641</v>
       </c>
-      <c r="H35" s="178"/>
+      <c r="H35" s="179"/>
       <c r="J35" s="67" t="s">
         <v>690</v>
       </c>
       <c r="K35" s="63" t="s">
         <v>636</v>
       </c>
-      <c r="L35" s="178"/>
+      <c r="L35" s="179"/>
     </row>
     <row r="36" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D36" s="176"/>
+      <c r="D36" s="183"/>
       <c r="F36" s="67" t="s">
         <v>691</v>
       </c>
       <c r="G36" s="63" t="s">
         <v>644</v>
       </c>
-      <c r="H36" s="178"/>
+      <c r="H36" s="179"/>
       <c r="J36" s="67" t="s">
         <v>692</v>
       </c>
       <c r="K36" t="s">
         <v>651</v>
       </c>
-      <c r="L36" s="178"/>
+      <c r="L36" s="179"/>
     </row>
     <row r="37" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D37" s="176"/>
+      <c r="D37" s="183"/>
       <c r="F37" s="67" t="s">
         <v>693</v>
       </c>
       <c r="G37" s="63" t="s">
         <v>642</v>
       </c>
-      <c r="H37" s="178"/>
+      <c r="H37" s="179"/>
       <c r="J37" s="67" t="s">
         <v>694</v>
       </c>
       <c r="K37" s="63" t="s">
         <v>641</v>
       </c>
-      <c r="L37" s="178"/>
+      <c r="L37" s="179"/>
     </row>
     <row r="38" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D38" s="176"/>
+      <c r="D38" s="183"/>
       <c r="E38" s="62"/>
       <c r="F38" s="62"/>
       <c r="G38" s="62"/>
@@ -9787,7 +9787,7 @@
       <c r="L38" s="62"/>
     </row>
     <row r="39" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D39" s="176"/>
+      <c r="D39" s="183"/>
       <c r="F39" s="64"/>
       <c r="G39" s="65" t="s">
         <v>630</v>
@@ -9804,14 +9804,14 @@
       </c>
     </row>
     <row r="40" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D40" s="176"/>
+      <c r="D40" s="183"/>
       <c r="F40" s="67" t="s">
         <v>695</v>
       </c>
       <c r="G40" s="63" t="s">
         <v>636</v>
       </c>
-      <c r="H40" s="179" t="s">
+      <c r="H40" s="178" t="s">
         <v>696</v>
       </c>
       <c r="J40" s="67" t="s">
@@ -9820,63 +9820,63 @@
       <c r="K40" s="63" t="s">
         <v>642</v>
       </c>
-      <c r="L40" s="178" t="s">
+      <c r="L40" s="179" t="s">
         <v>698</v>
       </c>
     </row>
     <row r="41" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D41" s="176"/>
+      <c r="D41" s="183"/>
       <c r="F41" s="67" t="s">
         <v>699</v>
       </c>
       <c r="G41" s="63" t="s">
         <v>639</v>
       </c>
-      <c r="H41" s="178"/>
+      <c r="H41" s="179"/>
       <c r="J41" s="67" t="s">
         <v>700</v>
       </c>
       <c r="K41" s="63" t="s">
         <v>639</v>
       </c>
-      <c r="L41" s="178"/>
+      <c r="L41" s="179"/>
     </row>
     <row r="42" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D42" s="176"/>
+      <c r="D42" s="183"/>
       <c r="F42" s="67" t="s">
         <v>701</v>
       </c>
       <c r="G42" s="63" t="s">
         <v>642</v>
       </c>
-      <c r="H42" s="178"/>
+      <c r="H42" s="179"/>
       <c r="J42" s="67" t="s">
         <v>702</v>
       </c>
       <c r="K42" s="63" t="s">
         <v>638</v>
       </c>
-      <c r="L42" s="178"/>
+      <c r="L42" s="179"/>
     </row>
     <row r="43" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D43" s="176"/>
+      <c r="D43" s="183"/>
       <c r="F43" s="67" t="s">
         <v>703</v>
       </c>
       <c r="G43" s="63" t="s">
         <v>627</v>
       </c>
-      <c r="H43" s="178"/>
+      <c r="H43" s="179"/>
       <c r="J43" s="67" t="s">
         <v>704</v>
       </c>
       <c r="K43" s="63" t="s">
         <v>651</v>
       </c>
-      <c r="L43" s="178"/>
+      <c r="L43" s="179"/>
     </row>
     <row r="44" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D44" s="176"/>
+      <c r="D44" s="183"/>
       <c r="F44" s="62"/>
       <c r="G44" s="62"/>
       <c r="H44" s="62"/>
@@ -9886,7 +9886,7 @@
       <c r="L44" s="62"/>
     </row>
     <row r="45" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D45" s="176"/>
+      <c r="D45" s="183"/>
       <c r="F45" s="64"/>
       <c r="G45" s="65" t="s">
         <v>630</v>
@@ -9903,14 +9903,14 @@
       </c>
     </row>
     <row r="46" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D46" s="176"/>
+      <c r="D46" s="183"/>
       <c r="F46" s="67" t="s">
         <v>705</v>
       </c>
       <c r="G46" s="63" t="s">
         <v>651</v>
       </c>
-      <c r="H46" s="179" t="s">
+      <c r="H46" s="178" t="s">
         <v>706</v>
       </c>
       <c r="J46" s="67" t="s">
@@ -9919,60 +9919,60 @@
       <c r="K46" s="63" t="s">
         <v>641</v>
       </c>
-      <c r="L46" s="179" t="s">
+      <c r="L46" s="178" t="s">
         <v>708</v>
       </c>
     </row>
     <row r="47" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D47" s="176"/>
+      <c r="D47" s="183"/>
       <c r="F47" s="67" t="s">
         <v>709</v>
       </c>
       <c r="G47" s="63" t="s">
         <v>638</v>
       </c>
-      <c r="H47" s="178"/>
+      <c r="H47" s="179"/>
       <c r="J47" s="67" t="s">
         <v>710</v>
       </c>
       <c r="K47" s="63" t="s">
         <v>634</v>
       </c>
-      <c r="L47" s="178"/>
+      <c r="L47" s="179"/>
     </row>
     <row r="48" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D48" s="176"/>
+      <c r="D48" s="183"/>
       <c r="F48" s="67" t="s">
         <v>711</v>
       </c>
       <c r="G48" s="63" t="s">
         <v>634</v>
       </c>
-      <c r="H48" s="178"/>
+      <c r="H48" s="179"/>
       <c r="J48" s="67" t="s">
         <v>712</v>
       </c>
       <c r="K48" s="63" t="s">
         <v>642</v>
       </c>
-      <c r="L48" s="178"/>
+      <c r="L48" s="179"/>
     </row>
     <row r="49" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D49" s="177"/>
+      <c r="D49" s="184"/>
       <c r="F49" s="67" t="s">
         <v>713</v>
       </c>
       <c r="G49" s="63" t="s">
         <v>641</v>
       </c>
-      <c r="H49" s="178"/>
+      <c r="H49" s="179"/>
       <c r="J49" s="67" t="s">
         <v>714</v>
       </c>
       <c r="K49" s="63" t="s">
         <v>636</v>
       </c>
-      <c r="L49" s="178"/>
+      <c r="L49" s="179"/>
     </row>
     <row r="50" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D50" s="62"/>
@@ -9987,6 +9987,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="D3:D49"/>
+    <mergeCell ref="H10:H13"/>
+    <mergeCell ref="H16:H19"/>
+    <mergeCell ref="H22:H25"/>
+    <mergeCell ref="H28:H31"/>
+    <mergeCell ref="H34:H37"/>
+    <mergeCell ref="H40:H43"/>
+    <mergeCell ref="H46:H49"/>
     <mergeCell ref="L34:L37"/>
     <mergeCell ref="L40:L43"/>
     <mergeCell ref="L46:L49"/>
@@ -9996,14 +10004,6 @@
     <mergeCell ref="L16:L19"/>
     <mergeCell ref="L22:L25"/>
     <mergeCell ref="L28:L31"/>
-    <mergeCell ref="D3:D49"/>
-    <mergeCell ref="H10:H13"/>
-    <mergeCell ref="H16:H19"/>
-    <mergeCell ref="H22:H25"/>
-    <mergeCell ref="H28:H31"/>
-    <mergeCell ref="H34:H37"/>
-    <mergeCell ref="H40:H43"/>
-    <mergeCell ref="H46:H49"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10052,13 +10052,13 @@
       <c r="O1" s="4"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="182" t="s">
+      <c r="A2" s="185" t="s">
         <v>715</v>
       </c>
-      <c r="B2" s="182"/>
-      <c r="C2" s="182"/>
-      <c r="D2" s="182"/>
-      <c r="E2" s="182"/>
+      <c r="B2" s="185"/>
+      <c r="C2" s="185"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="185"/>
       <c r="F2" s="4"/>
       <c r="I2" s="4"/>
       <c r="L2" s="4"/>
@@ -10189,66 +10189,66 @@
       <c r="R8" s="4"/>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A9" s="184" t="s">
+      <c r="A9" s="187" t="s">
         <v>726</v>
       </c>
-      <c r="B9" s="184"/>
-      <c r="C9" s="184"/>
-      <c r="D9" s="184"/>
-      <c r="E9" s="184"/>
-      <c r="F9" s="184"/>
-      <c r="G9" s="184"/>
-      <c r="H9" s="184"/>
-      <c r="I9" s="184"/>
-      <c r="J9" s="184"/>
-      <c r="K9" s="184"/>
-      <c r="L9" s="184"/>
-      <c r="M9" s="184"/>
-      <c r="N9" s="184"/>
-      <c r="O9" s="184"/>
-      <c r="P9" s="184"/>
-      <c r="Q9" s="184"/>
-      <c r="R9" s="184"/>
-      <c r="S9" s="184"/>
-      <c r="T9" s="184"/>
-      <c r="U9" s="184"/>
-      <c r="V9" s="184"/>
-      <c r="W9" s="184"/>
-      <c r="X9" s="184"/>
-      <c r="Y9" s="184"/>
+      <c r="B9" s="187"/>
+      <c r="C9" s="187"/>
+      <c r="D9" s="187"/>
+      <c r="E9" s="187"/>
+      <c r="F9" s="187"/>
+      <c r="G9" s="187"/>
+      <c r="H9" s="187"/>
+      <c r="I9" s="187"/>
+      <c r="J9" s="187"/>
+      <c r="K9" s="187"/>
+      <c r="L9" s="187"/>
+      <c r="M9" s="187"/>
+      <c r="N9" s="187"/>
+      <c r="O9" s="187"/>
+      <c r="P9" s="187"/>
+      <c r="Q9" s="187"/>
+      <c r="R9" s="187"/>
+      <c r="S9" s="187"/>
+      <c r="T9" s="187"/>
+      <c r="U9" s="187"/>
+      <c r="V9" s="187"/>
+      <c r="W9" s="187"/>
+      <c r="X9" s="187"/>
+      <c r="Y9" s="187"/>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10" s="184"/>
-      <c r="B10" s="184"/>
-      <c r="C10" s="184"/>
-      <c r="D10" s="184"/>
-      <c r="E10" s="184"/>
-      <c r="F10" s="184"/>
-      <c r="G10" s="184"/>
-      <c r="H10" s="184"/>
-      <c r="I10" s="184"/>
-      <c r="J10" s="184"/>
-      <c r="K10" s="184"/>
-      <c r="L10" s="184"/>
-      <c r="M10" s="184"/>
-      <c r="N10" s="184"/>
-      <c r="O10" s="184"/>
-      <c r="P10" s="184"/>
-      <c r="Q10" s="184"/>
-      <c r="R10" s="184"/>
-      <c r="S10" s="184"/>
-      <c r="T10" s="184"/>
-      <c r="U10" s="184"/>
-      <c r="V10" s="184"/>
-      <c r="W10" s="184"/>
-      <c r="X10" s="184"/>
-      <c r="Y10" s="184"/>
+      <c r="A10" s="187"/>
+      <c r="B10" s="187"/>
+      <c r="C10" s="187"/>
+      <c r="D10" s="187"/>
+      <c r="E10" s="187"/>
+      <c r="F10" s="187"/>
+      <c r="G10" s="187"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="187"/>
+      <c r="K10" s="187"/>
+      <c r="L10" s="187"/>
+      <c r="M10" s="187"/>
+      <c r="N10" s="187"/>
+      <c r="O10" s="187"/>
+      <c r="P10" s="187"/>
+      <c r="Q10" s="187"/>
+      <c r="R10" s="187"/>
+      <c r="S10" s="187"/>
+      <c r="T10" s="187"/>
+      <c r="U10" s="187"/>
+      <c r="V10" s="187"/>
+      <c r="W10" s="187"/>
+      <c r="X10" s="187"/>
+      <c r="Y10" s="187"/>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B11" s="183" t="s">
+      <c r="B11" s="186" t="s">
         <v>727</v>
       </c>
-      <c r="C11" s="183"/>
+      <c r="C11" s="186"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
@@ -13037,66 +13037,66 @@
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A56" s="185" t="s">
+      <c r="A56" s="188" t="s">
         <v>892</v>
       </c>
-      <c r="B56" s="185"/>
-      <c r="C56" s="185"/>
-      <c r="D56" s="185"/>
-      <c r="E56" s="185"/>
-      <c r="F56" s="185"/>
-      <c r="G56" s="185"/>
-      <c r="H56" s="185"/>
-      <c r="I56" s="185"/>
-      <c r="J56" s="185"/>
-      <c r="K56" s="185"/>
-      <c r="L56" s="185"/>
-      <c r="M56" s="185"/>
-      <c r="N56" s="185"/>
-      <c r="O56" s="185"/>
-      <c r="P56" s="185"/>
-      <c r="Q56" s="185"/>
-      <c r="R56" s="185"/>
-      <c r="S56" s="185"/>
-      <c r="T56" s="185"/>
-      <c r="U56" s="185"/>
-      <c r="V56" s="185"/>
-      <c r="W56" s="185"/>
-      <c r="X56" s="185"/>
-      <c r="Y56" s="185"/>
+      <c r="B56" s="188"/>
+      <c r="C56" s="188"/>
+      <c r="D56" s="188"/>
+      <c r="E56" s="188"/>
+      <c r="F56" s="188"/>
+      <c r="G56" s="188"/>
+      <c r="H56" s="188"/>
+      <c r="I56" s="188"/>
+      <c r="J56" s="188"/>
+      <c r="K56" s="188"/>
+      <c r="L56" s="188"/>
+      <c r="M56" s="188"/>
+      <c r="N56" s="188"/>
+      <c r="O56" s="188"/>
+      <c r="P56" s="188"/>
+      <c r="Q56" s="188"/>
+      <c r="R56" s="188"/>
+      <c r="S56" s="188"/>
+      <c r="T56" s="188"/>
+      <c r="U56" s="188"/>
+      <c r="V56" s="188"/>
+      <c r="W56" s="188"/>
+      <c r="X56" s="188"/>
+      <c r="Y56" s="188"/>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A57" s="185"/>
-      <c r="B57" s="185"/>
-      <c r="C57" s="185"/>
-      <c r="D57" s="185"/>
-      <c r="E57" s="185"/>
-      <c r="F57" s="185"/>
-      <c r="G57" s="185"/>
-      <c r="H57" s="185"/>
-      <c r="I57" s="185"/>
-      <c r="J57" s="185"/>
-      <c r="K57" s="185"/>
-      <c r="L57" s="185"/>
-      <c r="M57" s="185"/>
-      <c r="N57" s="185"/>
-      <c r="O57" s="185"/>
-      <c r="P57" s="185"/>
-      <c r="Q57" s="185"/>
-      <c r="R57" s="185"/>
-      <c r="S57" s="185"/>
-      <c r="T57" s="185"/>
-      <c r="U57" s="185"/>
-      <c r="V57" s="185"/>
-      <c r="W57" s="185"/>
-      <c r="X57" s="185"/>
-      <c r="Y57" s="185"/>
+      <c r="A57" s="188"/>
+      <c r="B57" s="188"/>
+      <c r="C57" s="188"/>
+      <c r="D57" s="188"/>
+      <c r="E57" s="188"/>
+      <c r="F57" s="188"/>
+      <c r="G57" s="188"/>
+      <c r="H57" s="188"/>
+      <c r="I57" s="188"/>
+      <c r="J57" s="188"/>
+      <c r="K57" s="188"/>
+      <c r="L57" s="188"/>
+      <c r="M57" s="188"/>
+      <c r="N57" s="188"/>
+      <c r="O57" s="188"/>
+      <c r="P57" s="188"/>
+      <c r="Q57" s="188"/>
+      <c r="R57" s="188"/>
+      <c r="S57" s="188"/>
+      <c r="T57" s="188"/>
+      <c r="U57" s="188"/>
+      <c r="V57" s="188"/>
+      <c r="W57" s="188"/>
+      <c r="X57" s="188"/>
+      <c r="Y57" s="188"/>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B58" s="183" t="s">
+      <c r="B58" s="186" t="s">
         <v>727</v>
       </c>
-      <c r="C58" s="183"/>
+      <c r="C58" s="186"/>
       <c r="J58" s="4"/>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
@@ -15714,66 +15714,66 @@
       <c r="K98" s="4"/>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A99" s="186" t="s">
+      <c r="A99" s="189" t="s">
         <v>896</v>
       </c>
-      <c r="B99" s="186"/>
-      <c r="C99" s="186"/>
-      <c r="D99" s="186"/>
-      <c r="E99" s="186"/>
-      <c r="F99" s="186"/>
-      <c r="G99" s="186"/>
-      <c r="H99" s="186"/>
-      <c r="I99" s="186"/>
-      <c r="J99" s="186"/>
-      <c r="K99" s="186"/>
-      <c r="L99" s="186"/>
-      <c r="M99" s="186"/>
-      <c r="N99" s="186"/>
-      <c r="O99" s="186"/>
-      <c r="P99" s="186"/>
-      <c r="Q99" s="186"/>
-      <c r="R99" s="186"/>
-      <c r="S99" s="186"/>
-      <c r="T99" s="186"/>
-      <c r="U99" s="186"/>
-      <c r="V99" s="186"/>
-      <c r="W99" s="186"/>
-      <c r="X99" s="186"/>
-      <c r="Y99" s="186"/>
+      <c r="B99" s="189"/>
+      <c r="C99" s="189"/>
+      <c r="D99" s="189"/>
+      <c r="E99" s="189"/>
+      <c r="F99" s="189"/>
+      <c r="G99" s="189"/>
+      <c r="H99" s="189"/>
+      <c r="I99" s="189"/>
+      <c r="J99" s="189"/>
+      <c r="K99" s="189"/>
+      <c r="L99" s="189"/>
+      <c r="M99" s="189"/>
+      <c r="N99" s="189"/>
+      <c r="O99" s="189"/>
+      <c r="P99" s="189"/>
+      <c r="Q99" s="189"/>
+      <c r="R99" s="189"/>
+      <c r="S99" s="189"/>
+      <c r="T99" s="189"/>
+      <c r="U99" s="189"/>
+      <c r="V99" s="189"/>
+      <c r="W99" s="189"/>
+      <c r="X99" s="189"/>
+      <c r="Y99" s="189"/>
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A100" s="186"/>
-      <c r="B100" s="186"/>
-      <c r="C100" s="186"/>
-      <c r="D100" s="186"/>
-      <c r="E100" s="186"/>
-      <c r="F100" s="186"/>
-      <c r="G100" s="186"/>
-      <c r="H100" s="186"/>
-      <c r="I100" s="186"/>
-      <c r="J100" s="186"/>
-      <c r="K100" s="186"/>
-      <c r="L100" s="186"/>
-      <c r="M100" s="186"/>
-      <c r="N100" s="186"/>
-      <c r="O100" s="186"/>
-      <c r="P100" s="186"/>
-      <c r="Q100" s="186"/>
-      <c r="R100" s="186"/>
-      <c r="S100" s="186"/>
-      <c r="T100" s="186"/>
-      <c r="U100" s="186"/>
-      <c r="V100" s="186"/>
-      <c r="W100" s="186"/>
-      <c r="X100" s="186"/>
-      <c r="Y100" s="186"/>
+      <c r="A100" s="189"/>
+      <c r="B100" s="189"/>
+      <c r="C100" s="189"/>
+      <c r="D100" s="189"/>
+      <c r="E100" s="189"/>
+      <c r="F100" s="189"/>
+      <c r="G100" s="189"/>
+      <c r="H100" s="189"/>
+      <c r="I100" s="189"/>
+      <c r="J100" s="189"/>
+      <c r="K100" s="189"/>
+      <c r="L100" s="189"/>
+      <c r="M100" s="189"/>
+      <c r="N100" s="189"/>
+      <c r="O100" s="189"/>
+      <c r="P100" s="189"/>
+      <c r="Q100" s="189"/>
+      <c r="R100" s="189"/>
+      <c r="S100" s="189"/>
+      <c r="T100" s="189"/>
+      <c r="U100" s="189"/>
+      <c r="V100" s="189"/>
+      <c r="W100" s="189"/>
+      <c r="X100" s="189"/>
+      <c r="Y100" s="189"/>
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B101" s="183" t="s">
+      <c r="B101" s="186" t="s">
         <v>897</v>
       </c>
-      <c r="C101" s="183"/>
+      <c r="C101" s="186"/>
       <c r="I101" s="4"/>
       <c r="J101" s="4"/>
       <c r="K101" s="4"/>
@@ -18573,54 +18573,54 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:26" x14ac:dyDescent="0.25">
-      <c r="C3" s="187" t="s">
+      <c r="C3" s="190" t="s">
         <v>920</v>
       </c>
-      <c r="D3" s="187"/>
-      <c r="E3" s="187"/>
-      <c r="F3" s="187"/>
-      <c r="G3" s="187"/>
-      <c r="H3" s="187"/>
-      <c r="I3" s="187"/>
-      <c r="J3" s="187"/>
-      <c r="K3" s="187"/>
-      <c r="L3" s="187"/>
-      <c r="M3" s="187"/>
-      <c r="P3" s="187" t="s">
+      <c r="D3" s="190"/>
+      <c r="E3" s="190"/>
+      <c r="F3" s="190"/>
+      <c r="G3" s="190"/>
+      <c r="H3" s="190"/>
+      <c r="I3" s="190"/>
+      <c r="J3" s="190"/>
+      <c r="K3" s="190"/>
+      <c r="L3" s="190"/>
+      <c r="M3" s="190"/>
+      <c r="P3" s="190" t="s">
         <v>921</v>
       </c>
-      <c r="Q3" s="187"/>
-      <c r="R3" s="187"/>
-      <c r="S3" s="187"/>
-      <c r="T3" s="187"/>
-      <c r="W3" s="187" t="s">
+      <c r="Q3" s="190"/>
+      <c r="R3" s="190"/>
+      <c r="S3" s="190"/>
+      <c r="T3" s="190"/>
+      <c r="W3" s="190" t="s">
         <v>922</v>
       </c>
-      <c r="X3" s="187"/>
-      <c r="Y3" s="187"/>
-      <c r="Z3" s="187"/>
+      <c r="X3" s="190"/>
+      <c r="Y3" s="190"/>
+      <c r="Z3" s="190"/>
     </row>
     <row r="4" spans="3:26" x14ac:dyDescent="0.25">
-      <c r="C4" s="187"/>
-      <c r="D4" s="187"/>
-      <c r="E4" s="187"/>
-      <c r="F4" s="187"/>
-      <c r="G4" s="187"/>
-      <c r="H4" s="187"/>
-      <c r="I4" s="187"/>
-      <c r="J4" s="187"/>
-      <c r="K4" s="187"/>
-      <c r="L4" s="187"/>
-      <c r="M4" s="187"/>
-      <c r="P4" s="187"/>
-      <c r="Q4" s="187"/>
-      <c r="R4" s="187"/>
-      <c r="S4" s="187"/>
-      <c r="T4" s="187"/>
-      <c r="W4" s="187"/>
-      <c r="X4" s="187"/>
-      <c r="Y4" s="187"/>
-      <c r="Z4" s="187"/>
+      <c r="C4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="190"/>
+      <c r="K4" s="190"/>
+      <c r="L4" s="190"/>
+      <c r="M4" s="190"/>
+      <c r="P4" s="190"/>
+      <c r="Q4" s="190"/>
+      <c r="R4" s="190"/>
+      <c r="S4" s="190"/>
+      <c r="T4" s="190"/>
+      <c r="W4" s="190"/>
+      <c r="X4" s="190"/>
+      <c r="Y4" s="190"/>
+      <c r="Z4" s="190"/>
     </row>
     <row r="7" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C7" s="4"/>
@@ -19386,12 +19386,12 @@
       </c>
       <c r="Q38" s="4"/>
       <c r="T38" s="4"/>
-      <c r="W38" s="187" t="s">
+      <c r="W38" s="190" t="s">
         <v>970</v>
       </c>
-      <c r="X38" s="187"/>
-      <c r="Y38" s="187"/>
-      <c r="Z38" s="187"/>
+      <c r="X38" s="190"/>
+      <c r="Y38" s="190"/>
+      <c r="Z38" s="190"/>
     </row>
     <row r="39" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C39" s="4"/>
@@ -19409,10 +19409,10 @@
       </c>
       <c r="Q39" s="4"/>
       <c r="T39" s="4"/>
-      <c r="W39" s="187"/>
-      <c r="X39" s="187"/>
-      <c r="Y39" s="187"/>
-      <c r="Z39" s="187"/>
+      <c r="W39" s="190"/>
+      <c r="X39" s="190"/>
+      <c r="Y39" s="190"/>
+      <c r="Z39" s="190"/>
     </row>
     <row r="40" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C40" s="4"/>
@@ -19430,12 +19430,12 @@
       </c>
       <c r="Q40" s="4"/>
       <c r="T40" s="4"/>
-      <c r="W40" s="188" t="s">
+      <c r="W40" s="191" t="s">
         <v>971</v>
       </c>
-      <c r="X40" s="188"/>
-      <c r="Y40" s="188"/>
-      <c r="Z40" s="188"/>
+      <c r="X40" s="191"/>
+      <c r="Y40" s="191"/>
+      <c r="Z40" s="191"/>
     </row>
     <row r="41" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C41" s="4"/>
@@ -19453,10 +19453,10 @@
       </c>
       <c r="Q41" s="4"/>
       <c r="T41" s="4"/>
-      <c r="W41" s="188"/>
-      <c r="X41" s="188"/>
-      <c r="Y41" s="188"/>
-      <c r="Z41" s="188"/>
+      <c r="W41" s="191"/>
+      <c r="X41" s="191"/>
+      <c r="Y41" s="191"/>
+      <c r="Z41" s="191"/>
     </row>
     <row r="42" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C42" s="4"/>
@@ -19754,59 +19754,59 @@
       </c>
     </row>
     <row r="10" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C10" s="187" t="s">
+      <c r="C10" s="190" t="s">
         <v>988</v>
       </c>
-      <c r="D10" s="187"/>
-      <c r="E10" s="187"/>
-      <c r="F10" s="187"/>
-      <c r="G10" s="187"/>
-      <c r="H10" s="187"/>
-      <c r="I10" s="187"/>
-      <c r="J10" s="187"/>
-      <c r="N10" s="187" t="s">
+      <c r="D10" s="190"/>
+      <c r="E10" s="190"/>
+      <c r="F10" s="190"/>
+      <c r="G10" s="190"/>
+      <c r="H10" s="190"/>
+      <c r="I10" s="190"/>
+      <c r="J10" s="190"/>
+      <c r="N10" s="190" t="s">
         <v>989</v>
       </c>
-      <c r="O10" s="187"/>
-      <c r="P10" s="187"/>
-      <c r="Q10" s="187"/>
-      <c r="R10" s="187"/>
-      <c r="S10" s="187"/>
+      <c r="O10" s="190"/>
+      <c r="P10" s="190"/>
+      <c r="Q10" s="190"/>
+      <c r="R10" s="190"/>
+      <c r="S10" s="190"/>
     </row>
     <row r="11" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C11" s="187"/>
-      <c r="D11" s="187"/>
-      <c r="E11" s="187"/>
-      <c r="F11" s="187"/>
-      <c r="G11" s="187"/>
-      <c r="H11" s="187"/>
-      <c r="I11" s="187"/>
-      <c r="J11" s="187"/>
-      <c r="N11" s="187"/>
-      <c r="O11" s="187"/>
-      <c r="P11" s="187"/>
-      <c r="Q11" s="187"/>
-      <c r="R11" s="187"/>
-      <c r="S11" s="187"/>
+      <c r="C11" s="190"/>
+      <c r="D11" s="190"/>
+      <c r="E11" s="190"/>
+      <c r="F11" s="190"/>
+      <c r="G11" s="190"/>
+      <c r="H11" s="190"/>
+      <c r="I11" s="190"/>
+      <c r="J11" s="190"/>
+      <c r="N11" s="190"/>
+      <c r="O11" s="190"/>
+      <c r="P11" s="190"/>
+      <c r="Q11" s="190"/>
+      <c r="R11" s="190"/>
+      <c r="S11" s="190"/>
     </row>
     <row r="12" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C12" s="187"/>
-      <c r="D12" s="187"/>
-      <c r="E12" s="187"/>
-      <c r="F12" s="187"/>
-      <c r="G12" s="187"/>
-      <c r="H12" s="187"/>
-      <c r="I12" s="187"/>
-      <c r="J12" s="187"/>
-      <c r="N12" s="187"/>
-      <c r="O12" s="187"/>
-      <c r="P12" s="187"/>
-      <c r="Q12" s="187"/>
-      <c r="R12" s="187"/>
-      <c r="S12" s="187"/>
+      <c r="C12" s="190"/>
+      <c r="D12" s="190"/>
+      <c r="E12" s="190"/>
+      <c r="F12" s="190"/>
+      <c r="G12" s="190"/>
+      <c r="H12" s="190"/>
+      <c r="I12" s="190"/>
+      <c r="J12" s="190"/>
+      <c r="N12" s="190"/>
+      <c r="O12" s="190"/>
+      <c r="P12" s="190"/>
+      <c r="Q12" s="190"/>
+      <c r="R12" s="190"/>
+      <c r="S12" s="190"/>
     </row>
     <row r="13" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C13" s="190" t="s">
+      <c r="C13" s="193" t="s">
         <v>972</v>
       </c>
       <c r="D13" s="21" t="s">
@@ -19820,7 +19820,7 @@
         <f>F14/SUM(E14:F14)</f>
         <v>0.30769230769230799</v>
       </c>
-      <c r="N13" s="190" t="s">
+      <c r="N13" s="193" t="s">
         <v>978</v>
       </c>
       <c r="O13" s="21" t="s">
@@ -19844,7 +19844,7 @@
       </c>
     </row>
     <row r="14" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C14" s="191"/>
+      <c r="C14" s="194"/>
       <c r="D14" s="21" t="s">
         <v>991</v>
       </c>
@@ -19856,7 +19856,7 @@
         <f>F16*F15</f>
         <v>8</v>
       </c>
-      <c r="N14" s="191"/>
+      <c r="N14" s="194"/>
       <c r="O14" s="21" t="s">
         <v>991</v>
       </c>
@@ -19878,7 +19878,7 @@
       </c>
     </row>
     <row r="15" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C15" s="191"/>
+      <c r="C15" s="194"/>
       <c r="D15" s="24" t="s">
         <v>992</v>
       </c>
@@ -19888,7 +19888,7 @@
       <c r="F15" s="25">
         <v>1</v>
       </c>
-      <c r="N15" s="191"/>
+      <c r="N15" s="194"/>
       <c r="O15" s="26" t="s">
         <v>992</v>
       </c>
@@ -19906,7 +19906,7 @@
       </c>
     </row>
     <row r="16" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C16" s="191"/>
+      <c r="C16" s="194"/>
       <c r="D16" s="24" t="s">
         <v>993</v>
       </c>
@@ -19916,7 +19916,7 @@
       <c r="F16" s="25">
         <v>8</v>
       </c>
-      <c r="N16" s="191"/>
+      <c r="N16" s="194"/>
       <c r="O16" s="24" t="s">
         <v>993</v>
       </c>
@@ -19934,7 +19934,7 @@
       </c>
     </row>
     <row r="17" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C17" s="192"/>
+      <c r="C17" s="195"/>
       <c r="D17" s="27" t="s">
         <v>994</v>
       </c>
@@ -19944,7 +19944,7 @@
       <c r="F17" s="28" t="s">
         <v>326</v>
       </c>
-      <c r="N17" s="192"/>
+      <c r="N17" s="195"/>
       <c r="O17" s="28" t="s">
         <v>994</v>
       </c>
@@ -19976,7 +19976,7 @@
       <c r="S18" s="9"/>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C19" s="190" t="s">
+      <c r="C19" s="193" t="s">
         <v>974</v>
       </c>
       <c r="D19" s="21" t="s">
@@ -19994,7 +19994,7 @@
         <f>G20/SUM(E20:H20)</f>
         <v>0.11764705882352899</v>
       </c>
-      <c r="N19" s="190" t="s">
+      <c r="N19" s="193" t="s">
         <v>982</v>
       </c>
       <c r="O19" s="21" t="s">
@@ -20018,7 +20018,7 @@
       </c>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C20" s="191"/>
+      <c r="C20" s="194"/>
       <c r="D20" s="21" t="s">
         <v>991</v>
       </c>
@@ -20034,7 +20034,7 @@
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="N20" s="191"/>
+      <c r="N20" s="194"/>
       <c r="O20" s="21" t="s">
         <v>991</v>
       </c>
@@ -20056,7 +20056,7 @@
       </c>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C21" s="191"/>
+      <c r="C21" s="194"/>
       <c r="D21" s="24" t="s">
         <v>992</v>
       </c>
@@ -20069,7 +20069,7 @@
       <c r="G21" s="25">
         <v>2</v>
       </c>
-      <c r="N21" s="191"/>
+      <c r="N21" s="194"/>
       <c r="O21" s="26" t="s">
         <v>992</v>
       </c>
@@ -20087,7 +20087,7 @@
       </c>
     </row>
     <row r="22" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C22" s="191"/>
+      <c r="C22" s="194"/>
       <c r="D22" s="24" t="s">
         <v>993</v>
       </c>
@@ -20100,7 +20100,7 @@
       <c r="G22" s="25">
         <v>22</v>
       </c>
-      <c r="N22" s="191"/>
+      <c r="N22" s="194"/>
       <c r="O22" s="24" t="s">
         <v>993</v>
       </c>
@@ -20118,7 +20118,7 @@
       </c>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C23" s="192"/>
+      <c r="C23" s="195"/>
       <c r="D23" s="27" t="s">
         <v>994</v>
       </c>
@@ -20131,7 +20131,7 @@
       <c r="G23" s="28" t="s">
         <v>331</v>
       </c>
-      <c r="N23" s="192"/>
+      <c r="N23" s="195"/>
       <c r="O23" s="28" t="s">
         <v>994</v>
       </c>
@@ -20163,7 +20163,7 @@
       <c r="S24" s="9"/>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C25" s="190" t="s">
+      <c r="C25" s="193" t="s">
         <v>976</v>
       </c>
       <c r="D25" s="21" t="s">
@@ -20185,7 +20185,7 @@
         <f>H26/SUM(E26:H26)</f>
         <v>3.7267080745341602E-2</v>
       </c>
-      <c r="N25" s="189" t="s">
+      <c r="N25" s="192" t="s">
         <v>986</v>
       </c>
       <c r="O25" s="21" t="s">
@@ -20209,7 +20209,7 @@
       </c>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C26" s="191"/>
+      <c r="C26" s="194"/>
       <c r="D26" s="21" t="s">
         <v>991</v>
       </c>
@@ -20229,7 +20229,7 @@
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="N26" s="189"/>
+      <c r="N26" s="192"/>
       <c r="O26" s="21" t="s">
         <v>991</v>
       </c>
@@ -20251,7 +20251,7 @@
       </c>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C27" s="191"/>
+      <c r="C27" s="194"/>
       <c r="D27" s="24" t="s">
         <v>992</v>
       </c>
@@ -20267,7 +20267,7 @@
       <c r="H27" s="25">
         <v>1</v>
       </c>
-      <c r="N27" s="189"/>
+      <c r="N27" s="192"/>
       <c r="O27" s="26" t="s">
         <v>992</v>
       </c>
@@ -20285,7 +20285,7 @@
       </c>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C28" s="191"/>
+      <c r="C28" s="194"/>
       <c r="D28" s="24" t="s">
         <v>993</v>
       </c>
@@ -20301,7 +20301,7 @@
       <c r="H28" s="25">
         <v>24</v>
       </c>
-      <c r="N28" s="189"/>
+      <c r="N28" s="192"/>
       <c r="O28" s="24" t="s">
         <v>993</v>
       </c>
@@ -20319,7 +20319,7 @@
       </c>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C29" s="192"/>
+      <c r="C29" s="195"/>
       <c r="D29" s="27" t="s">
         <v>994</v>
       </c>
@@ -20335,7 +20335,7 @@
       <c r="H29" s="28" t="s">
         <v>998</v>
       </c>
-      <c r="N29" s="189"/>
+      <c r="N29" s="192"/>
       <c r="O29" s="29" t="s">
         <v>999</v>
       </c>
@@ -20359,7 +20359,7 @@
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
-      <c r="N30" s="189"/>
+      <c r="N30" s="192"/>
       <c r="O30" s="31" t="s">
         <v>1000</v>
       </c>
@@ -20377,7 +20377,7 @@
       </c>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C31" s="189" t="s">
+      <c r="C31" s="192" t="s">
         <v>980</v>
       </c>
       <c r="D31" s="21" t="s">
@@ -20403,7 +20403,7 @@
         <f>I32/SUM(F32:I32)</f>
         <v>0.20597790773229399</v>
       </c>
-      <c r="N31" s="189"/>
+      <c r="N31" s="192"/>
       <c r="O31" s="28" t="s">
         <v>994</v>
       </c>
@@ -20421,7 +20421,7 @@
       </c>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C32" s="189"/>
+      <c r="C32" s="192"/>
       <c r="D32" s="21" t="s">
         <v>991</v>
       </c>
@@ -20447,7 +20447,7 @@
       </c>
     </row>
     <row r="33" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C33" s="189"/>
+      <c r="C33" s="192"/>
       <c r="D33" s="26" t="s">
         <v>992</v>
       </c>
@@ -20468,7 +20468,7 @@
       </c>
     </row>
     <row r="34" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C34" s="189"/>
+      <c r="C34" s="192"/>
       <c r="D34" s="24" t="s">
         <v>993</v>
       </c>
@@ -20489,7 +20489,7 @@
       </c>
     </row>
     <row r="35" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C35" s="189"/>
+      <c r="C35" s="192"/>
       <c r="D35" s="29" t="s">
         <v>999</v>
       </c>
@@ -20510,7 +20510,7 @@
       </c>
     </row>
     <row r="36" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C36" s="189"/>
+      <c r="C36" s="192"/>
       <c r="D36" s="31" t="s">
         <v>1000</v>
       </c>
@@ -20531,7 +20531,7 @@
       </c>
     </row>
     <row r="37" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C37" s="189"/>
+      <c r="C37" s="192"/>
       <c r="D37" s="28" t="s">
         <v>994</v>
       </c>
@@ -20552,7 +20552,7 @@
       </c>
     </row>
     <row r="39" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C39" s="189" t="s">
+      <c r="C39" s="192" t="s">
         <v>984</v>
       </c>
       <c r="D39" s="21" t="s">
@@ -20584,7 +20584,7 @@
       </c>
     </row>
     <row r="40" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C40" s="189"/>
+      <c r="C40" s="192"/>
       <c r="D40" s="21" t="s">
         <v>991</v>
       </c>
@@ -20614,7 +20614,7 @@
       </c>
     </row>
     <row r="41" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C41" s="189"/>
+      <c r="C41" s="192"/>
       <c r="D41" s="26" t="s">
         <v>992</v>
       </c>
@@ -20638,7 +20638,7 @@
       </c>
     </row>
     <row r="42" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C42" s="189"/>
+      <c r="C42" s="192"/>
       <c r="D42" s="24" t="s">
         <v>993</v>
       </c>
@@ -20662,7 +20662,7 @@
       </c>
     </row>
     <row r="43" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C43" s="189"/>
+      <c r="C43" s="192"/>
       <c r="D43" s="29" t="s">
         <v>999</v>
       </c>
@@ -20686,7 +20686,7 @@
       </c>
     </row>
     <row r="44" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C44" s="189"/>
+      <c r="C44" s="192"/>
       <c r="D44" s="31" t="s">
         <v>1000</v>
       </c>
@@ -20710,7 +20710,7 @@
       </c>
     </row>
     <row r="45" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C45" s="189"/>
+      <c r="C45" s="192"/>
       <c r="D45" s="28" t="s">
         <v>994</v>
       </c>
@@ -20774,79 +20774,79 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C2" s="199" t="s">
+      <c r="C2" s="196" t="s">
         <v>1005</v>
       </c>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="200"/>
-      <c r="H2" s="200"/>
-      <c r="I2" s="200"/>
-      <c r="J2" s="200"/>
-      <c r="K2" s="200"/>
-      <c r="L2" s="200"/>
-      <c r="M2" s="201"/>
+      <c r="D2" s="197"/>
+      <c r="E2" s="197"/>
+      <c r="F2" s="197"/>
+      <c r="G2" s="197"/>
+      <c r="H2" s="197"/>
+      <c r="I2" s="197"/>
+      <c r="J2" s="197"/>
+      <c r="K2" s="197"/>
+      <c r="L2" s="197"/>
+      <c r="M2" s="198"/>
       <c r="N2" s="4"/>
       <c r="P2" s="4"/>
     </row>
     <row r="3" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C3" s="202"/>
-      <c r="D3" s="203"/>
-      <c r="E3" s="203"/>
-      <c r="F3" s="203"/>
-      <c r="G3" s="203"/>
-      <c r="H3" s="203"/>
-      <c r="I3" s="203"/>
-      <c r="J3" s="203"/>
-      <c r="K3" s="203"/>
-      <c r="L3" s="203"/>
-      <c r="M3" s="204"/>
+      <c r="C3" s="199"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="200"/>
+      <c r="H3" s="200"/>
+      <c r="I3" s="200"/>
+      <c r="J3" s="200"/>
+      <c r="K3" s="200"/>
+      <c r="L3" s="200"/>
+      <c r="M3" s="201"/>
       <c r="N3" s="4"/>
       <c r="P3" s="4"/>
     </row>
     <row r="4" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C4" s="205"/>
-      <c r="D4" s="206"/>
-      <c r="E4" s="206"/>
-      <c r="F4" s="206"/>
-      <c r="G4" s="206"/>
-      <c r="H4" s="206"/>
-      <c r="I4" s="206"/>
-      <c r="J4" s="206"/>
-      <c r="K4" s="206"/>
-      <c r="L4" s="206"/>
-      <c r="M4" s="207"/>
+      <c r="C4" s="202"/>
+      <c r="D4" s="203"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="203"/>
+      <c r="G4" s="203"/>
+      <c r="H4" s="203"/>
+      <c r="I4" s="203"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="203"/>
+      <c r="L4" s="203"/>
+      <c r="M4" s="204"/>
     </row>
     <row r="6" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C6" s="193" t="s">
+      <c r="C6" s="208" t="s">
         <v>730</v>
       </c>
-      <c r="D6" s="196" t="s">
+      <c r="D6" s="205" t="s">
         <v>1006</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>1007</v>
       </c>
-      <c r="F6" s="196" t="s">
+      <c r="F6" s="205" t="s">
         <v>1008</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>1009</v>
       </c>
-      <c r="H6" s="196" t="s">
+      <c r="H6" s="205" t="s">
         <v>1010</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="J6" s="196" t="s">
+      <c r="J6" s="205" t="s">
         <v>105</v>
       </c>
       <c r="K6" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="L6" s="196" t="s">
+      <c r="L6" s="205" t="s">
         <v>1013</v>
       </c>
       <c r="M6" s="6" t="s">
@@ -20854,58 +20854,58 @@
       </c>
     </row>
     <row r="7" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C7" s="194"/>
-      <c r="D7" s="197"/>
+      <c r="C7" s="209"/>
+      <c r="D7" s="206"/>
       <c r="E7" s="7"/>
-      <c r="F7" s="197"/>
+      <c r="F7" s="206"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="197"/>
+      <c r="H7" s="206"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="197"/>
+      <c r="J7" s="206"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="197"/>
+      <c r="L7" s="206"/>
       <c r="M7" s="7"/>
     </row>
     <row r="8" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C8" s="194"/>
-      <c r="D8" s="198"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="207"/>
       <c r="E8" s="8"/>
-      <c r="F8" s="198"/>
+      <c r="F8" s="207"/>
       <c r="G8" s="8"/>
-      <c r="H8" s="198"/>
+      <c r="H8" s="207"/>
       <c r="I8" s="8"/>
-      <c r="J8" s="198"/>
+      <c r="J8" s="207"/>
       <c r="K8" s="8"/>
-      <c r="L8" s="198"/>
+      <c r="L8" s="207"/>
       <c r="M8" s="8"/>
     </row>
     <row r="9" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C9" s="194"/>
-      <c r="D9" s="196" t="s">
+      <c r="C9" s="209"/>
+      <c r="D9" s="205" t="s">
         <v>1015</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>1016</v>
       </c>
-      <c r="F9" s="196" t="s">
+      <c r="F9" s="205" t="s">
         <v>1017</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>1018</v>
       </c>
-      <c r="H9" s="196" t="s">
+      <c r="H9" s="205" t="s">
         <v>1019</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>1020</v>
       </c>
-      <c r="J9" s="196" t="s">
+      <c r="J9" s="205" t="s">
         <v>1021</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>1022</v>
       </c>
-      <c r="L9" s="196" t="s">
+      <c r="L9" s="205" t="s">
         <v>1023</v>
       </c>
       <c r="M9" s="6" t="s">
@@ -20913,58 +20913,58 @@
       </c>
     </row>
     <row r="10" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C10" s="194"/>
-      <c r="D10" s="197"/>
+      <c r="C10" s="209"/>
+      <c r="D10" s="206"/>
       <c r="E10" s="7"/>
-      <c r="F10" s="197"/>
+      <c r="F10" s="206"/>
       <c r="G10" s="7"/>
-      <c r="H10" s="197"/>
+      <c r="H10" s="206"/>
       <c r="I10" s="7"/>
-      <c r="J10" s="197"/>
+      <c r="J10" s="206"/>
       <c r="K10" s="7"/>
-      <c r="L10" s="197"/>
+      <c r="L10" s="206"/>
       <c r="M10" s="7"/>
     </row>
     <row r="11" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C11" s="194"/>
-      <c r="D11" s="198"/>
+      <c r="C11" s="209"/>
+      <c r="D11" s="207"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="198"/>
+      <c r="F11" s="207"/>
       <c r="G11" s="8"/>
-      <c r="H11" s="198"/>
+      <c r="H11" s="207"/>
       <c r="I11" s="8"/>
-      <c r="J11" s="198"/>
+      <c r="J11" s="207"/>
       <c r="K11" s="8"/>
-      <c r="L11" s="198"/>
+      <c r="L11" s="207"/>
       <c r="M11" s="8"/>
     </row>
     <row r="12" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C12" s="194"/>
-      <c r="D12" s="196" t="s">
+      <c r="C12" s="209"/>
+      <c r="D12" s="205" t="s">
         <v>1025</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>1026</v>
       </c>
-      <c r="F12" s="196" t="s">
+      <c r="F12" s="205" t="s">
         <v>1027</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>1028</v>
       </c>
-      <c r="H12" s="196" t="s">
+      <c r="H12" s="205" t="s">
         <v>1029</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>1030</v>
       </c>
-      <c r="J12" s="196" t="s">
+      <c r="J12" s="205" t="s">
         <v>1031</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>1032</v>
       </c>
-      <c r="L12" s="196" t="s">
+      <c r="L12" s="205" t="s">
         <v>1033</v>
       </c>
       <c r="M12" s="6" t="s">
@@ -20972,36 +20972,36 @@
       </c>
     </row>
     <row r="13" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C13" s="194"/>
-      <c r="D13" s="197"/>
+      <c r="C13" s="209"/>
+      <c r="D13" s="206"/>
       <c r="E13" s="7"/>
-      <c r="F13" s="197"/>
+      <c r="F13" s="206"/>
       <c r="G13" s="7"/>
-      <c r="H13" s="197"/>
+      <c r="H13" s="206"/>
       <c r="I13" s="7"/>
-      <c r="J13" s="197"/>
+      <c r="J13" s="206"/>
       <c r="K13" s="7"/>
-      <c r="L13" s="197"/>
+      <c r="L13" s="206"/>
       <c r="M13" s="7"/>
     </row>
     <row r="14" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C14" s="195"/>
-      <c r="D14" s="198"/>
+      <c r="C14" s="210"/>
+      <c r="D14" s="207"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="198"/>
+      <c r="F14" s="207"/>
       <c r="G14" s="8"/>
-      <c r="H14" s="198"/>
+      <c r="H14" s="207"/>
       <c r="I14" s="8"/>
-      <c r="J14" s="198"/>
+      <c r="J14" s="207"/>
       <c r="K14" s="8"/>
-      <c r="L14" s="198"/>
+      <c r="L14" s="207"/>
       <c r="M14" s="8"/>
     </row>
     <row r="16" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C16" s="193" t="s">
+      <c r="C16" s="208" t="s">
         <v>497</v>
       </c>
-      <c r="D16" s="196" t="s">
+      <c r="D16" s="205" t="s">
         <v>1035</v>
       </c>
       <c r="E16" s="6" t="s">
@@ -21009,18 +21009,18 @@
       </c>
     </row>
     <row r="17" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C17" s="194"/>
-      <c r="D17" s="197"/>
+      <c r="C17" s="209"/>
+      <c r="D17" s="206"/>
       <c r="E17" s="7"/>
     </row>
     <row r="18" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C18" s="194"/>
-      <c r="D18" s="198"/>
+      <c r="C18" s="209"/>
+      <c r="D18" s="207"/>
       <c r="E18" s="8"/>
     </row>
     <row r="19" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C19" s="194"/>
-      <c r="D19" s="196" t="s">
+      <c r="C19" s="209"/>
+      <c r="D19" s="205" t="s">
         <v>1037</v>
       </c>
       <c r="E19" s="6" t="s">
@@ -21028,36 +21028,36 @@
       </c>
     </row>
     <row r="20" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C20" s="194"/>
-      <c r="D20" s="197"/>
+      <c r="C20" s="209"/>
+      <c r="D20" s="206"/>
       <c r="E20" s="7"/>
     </row>
     <row r="21" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C21" s="194"/>
-      <c r="D21" s="198"/>
+      <c r="C21" s="209"/>
+      <c r="D21" s="207"/>
       <c r="E21" s="8"/>
     </row>
     <row r="22" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C22" s="194"/>
-      <c r="D22" s="196" t="s">
+      <c r="C22" s="209"/>
+      <c r="D22" s="205" t="s">
         <v>1039</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>1038</v>
       </c>
-      <c r="F22" s="196" t="s">
+      <c r="F22" s="205" t="s">
         <v>1040</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>1041</v>
       </c>
-      <c r="H22" s="196" t="s">
+      <c r="H22" s="205" t="s">
         <v>1042</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>1043</v>
       </c>
-      <c r="J22" s="196" t="s">
+      <c r="J22" s="205" t="s">
         <v>1044</v>
       </c>
       <c r="K22" s="6" t="s">
@@ -21065,36 +21065,36 @@
       </c>
     </row>
     <row r="23" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C23" s="194"/>
-      <c r="D23" s="197"/>
+      <c r="C23" s="209"/>
+      <c r="D23" s="206"/>
       <c r="E23" s="7" t="s">
         <v>1046</v>
       </c>
-      <c r="F23" s="197"/>
+      <c r="F23" s="206"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="197"/>
+      <c r="H23" s="206"/>
       <c r="I23" s="7"/>
-      <c r="J23" s="197"/>
+      <c r="J23" s="206"/>
       <c r="K23" s="7" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="24" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C24" s="195"/>
-      <c r="D24" s="198"/>
+      <c r="C24" s="210"/>
+      <c r="D24" s="207"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="198"/>
+      <c r="F24" s="207"/>
       <c r="G24" s="8"/>
-      <c r="H24" s="198"/>
+      <c r="H24" s="207"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="198"/>
+      <c r="J24" s="207"/>
       <c r="K24" s="8"/>
     </row>
     <row r="26" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C26" s="193" t="s">
+      <c r="C26" s="208" t="s">
         <v>1048</v>
       </c>
-      <c r="D26" s="196" t="s">
+      <c r="D26" s="205" t="s">
         <v>1049</v>
       </c>
       <c r="E26" s="6" t="s">
@@ -21102,18 +21102,18 @@
       </c>
     </row>
     <row r="27" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C27" s="194"/>
-      <c r="D27" s="197"/>
+      <c r="C27" s="209"/>
+      <c r="D27" s="206"/>
       <c r="E27" s="7"/>
     </row>
     <row r="28" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C28" s="194"/>
-      <c r="D28" s="198"/>
+      <c r="C28" s="209"/>
+      <c r="D28" s="207"/>
       <c r="E28" s="8"/>
     </row>
     <row r="29" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C29" s="194"/>
-      <c r="D29" s="196" t="s">
+      <c r="C29" s="209"/>
+      <c r="D29" s="205" t="s">
         <v>1051</v>
       </c>
       <c r="E29" s="6" t="s">
@@ -21121,20 +21121,20 @@
       </c>
     </row>
     <row r="30" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C30" s="194"/>
-      <c r="D30" s="197"/>
+      <c r="C30" s="209"/>
+      <c r="D30" s="206"/>
       <c r="E30" s="7" t="s">
         <v>1046</v>
       </c>
     </row>
     <row r="31" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C31" s="194"/>
-      <c r="D31" s="198"/>
+      <c r="C31" s="209"/>
+      <c r="D31" s="207"/>
       <c r="E31" s="8"/>
     </row>
     <row r="32" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C32" s="194"/>
-      <c r="D32" s="196" t="s">
+      <c r="C32" s="209"/>
+      <c r="D32" s="205" t="s">
         <v>53</v>
       </c>
       <c r="E32" s="6" t="s">
@@ -21142,15 +21142,15 @@
       </c>
     </row>
     <row r="33" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C33" s="194"/>
-      <c r="D33" s="197"/>
+      <c r="C33" s="209"/>
+      <c r="D33" s="206"/>
       <c r="E33" s="7" t="s">
         <v>1053</v>
       </c>
     </row>
     <row r="34" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C34" s="195"/>
-      <c r="D34" s="198"/>
+      <c r="C34" s="210"/>
+      <c r="D34" s="207"/>
       <c r="E34" s="8"/>
     </row>
     <row r="36" spans="3:15" x14ac:dyDescent="0.25">
@@ -21164,6 +21164,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C6:C14"/>
+    <mergeCell ref="C16:C24"/>
+    <mergeCell ref="C26:C34"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="D32:D34"/>
     <mergeCell ref="C2:M4"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="J9:J11"/>
@@ -21180,18 +21192,6 @@
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="H12:H14"/>
     <mergeCell ref="H22:H24"/>
-    <mergeCell ref="C6:C14"/>
-    <mergeCell ref="C16:C24"/>
-    <mergeCell ref="C26:C34"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="D26:D28"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="D32:D34"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21208,20 +21208,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="165" t="s">
+      <c r="A2" s="168" t="s">
         <v>1054</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="166"/>
-      <c r="D2" s="166"/>
-      <c r="E2" s="167"/>
+      <c r="B2" s="169"/>
+      <c r="C2" s="169"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="170"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="168"/>
-      <c r="B3" s="169"/>
-      <c r="C3" s="169"/>
-      <c r="D3" s="169"/>
-      <c r="E3" s="170"/>
+      <c r="A3" s="171"/>
+      <c r="B3" s="172"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="173"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
@@ -21448,28 +21448,28 @@
       <c r="E29" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="F29" s="164" t="s">
+      <c r="F29" s="167" t="s">
         <v>1101</v>
       </c>
-      <c r="G29" s="164"/>
-      <c r="H29" s="164"/>
-      <c r="I29" s="164"/>
-      <c r="J29" s="164"/>
-      <c r="K29" s="164"/>
-      <c r="L29" s="164"/>
-      <c r="M29" s="164"/>
-      <c r="N29" s="164"/>
+      <c r="G29" s="167"/>
+      <c r="H29" s="167"/>
+      <c r="I29" s="167"/>
+      <c r="J29" s="167"/>
+      <c r="K29" s="167"/>
+      <c r="L29" s="167"/>
+      <c r="M29" s="167"/>
+      <c r="N29" s="167"/>
     </row>
     <row r="31" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D31" t="s">
         <v>1102</v>
       </c>
-      <c r="E31" s="208" t="s">
+      <c r="E31" s="211" t="s">
         <v>1103</v>
       </c>
-      <c r="F31" s="208"/>
-      <c r="G31" s="208"/>
-      <c r="H31" s="208"/>
+      <c r="F31" s="211"/>
+      <c r="G31" s="211"/>
+      <c r="H31" s="211"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -21586,149 +21586,149 @@
       <c r="F13" s="10"/>
     </row>
     <row r="16" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C16" s="147" t="s">
+      <c r="C16" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="148"/>
-      <c r="E16" s="148"/>
-      <c r="F16" s="148"/>
-      <c r="G16" s="148"/>
-      <c r="H16" s="148"/>
-      <c r="I16" s="148"/>
-      <c r="J16" s="148"/>
-      <c r="K16" s="148"/>
-      <c r="L16" s="148"/>
-      <c r="M16" s="148"/>
-      <c r="N16" s="148"/>
-      <c r="O16" s="149"/>
+      <c r="D16" s="149"/>
+      <c r="E16" s="149"/>
+      <c r="F16" s="149"/>
+      <c r="G16" s="149"/>
+      <c r="H16" s="149"/>
+      <c r="I16" s="149"/>
+      <c r="J16" s="149"/>
+      <c r="K16" s="149"/>
+      <c r="L16" s="149"/>
+      <c r="M16" s="149"/>
+      <c r="N16" s="149"/>
+      <c r="O16" s="150"/>
     </row>
     <row r="17" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C17" s="150"/>
-      <c r="D17" s="151"/>
-      <c r="E17" s="151"/>
-      <c r="F17" s="151"/>
-      <c r="G17" s="151"/>
-      <c r="H17" s="151"/>
-      <c r="I17" s="151"/>
-      <c r="J17" s="151"/>
-      <c r="K17" s="151"/>
-      <c r="L17" s="151"/>
-      <c r="M17" s="151"/>
-      <c r="N17" s="151"/>
-      <c r="O17" s="152"/>
+      <c r="C17" s="151"/>
+      <c r="D17" s="152"/>
+      <c r="E17" s="152"/>
+      <c r="F17" s="152"/>
+      <c r="G17" s="152"/>
+      <c r="H17" s="152"/>
+      <c r="I17" s="152"/>
+      <c r="J17" s="152"/>
+      <c r="K17" s="152"/>
+      <c r="L17" s="152"/>
+      <c r="M17" s="152"/>
+      <c r="N17" s="152"/>
+      <c r="O17" s="153"/>
     </row>
     <row r="18" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C18" s="150"/>
-      <c r="D18" s="151"/>
-      <c r="E18" s="151"/>
-      <c r="F18" s="151"/>
-      <c r="G18" s="151"/>
-      <c r="H18" s="151"/>
-      <c r="I18" s="151"/>
-      <c r="J18" s="151"/>
-      <c r="K18" s="151"/>
-      <c r="L18" s="151"/>
-      <c r="M18" s="151"/>
-      <c r="N18" s="151"/>
-      <c r="O18" s="152"/>
+      <c r="C18" s="151"/>
+      <c r="D18" s="152"/>
+      <c r="E18" s="152"/>
+      <c r="F18" s="152"/>
+      <c r="G18" s="152"/>
+      <c r="H18" s="152"/>
+      <c r="I18" s="152"/>
+      <c r="J18" s="152"/>
+      <c r="K18" s="152"/>
+      <c r="L18" s="152"/>
+      <c r="M18" s="152"/>
+      <c r="N18" s="152"/>
+      <c r="O18" s="153"/>
     </row>
     <row r="19" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C19" s="150"/>
-      <c r="D19" s="151"/>
-      <c r="E19" s="151"/>
-      <c r="F19" s="151"/>
-      <c r="G19" s="151"/>
-      <c r="H19" s="151"/>
-      <c r="I19" s="151"/>
-      <c r="J19" s="151"/>
-      <c r="K19" s="151"/>
-      <c r="L19" s="151"/>
-      <c r="M19" s="151"/>
-      <c r="N19" s="151"/>
-      <c r="O19" s="152"/>
+      <c r="C19" s="151"/>
+      <c r="D19" s="152"/>
+      <c r="E19" s="152"/>
+      <c r="F19" s="152"/>
+      <c r="G19" s="152"/>
+      <c r="H19" s="152"/>
+      <c r="I19" s="152"/>
+      <c r="J19" s="152"/>
+      <c r="K19" s="152"/>
+      <c r="L19" s="152"/>
+      <c r="M19" s="152"/>
+      <c r="N19" s="152"/>
+      <c r="O19" s="153"/>
     </row>
     <row r="20" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C20" s="150"/>
-      <c r="D20" s="151"/>
-      <c r="E20" s="151"/>
-      <c r="F20" s="151"/>
-      <c r="G20" s="151"/>
-      <c r="H20" s="151"/>
-      <c r="I20" s="151"/>
-      <c r="J20" s="151"/>
-      <c r="K20" s="151"/>
-      <c r="L20" s="151"/>
-      <c r="M20" s="151"/>
-      <c r="N20" s="151"/>
-      <c r="O20" s="152"/>
+      <c r="C20" s="151"/>
+      <c r="D20" s="152"/>
+      <c r="E20" s="152"/>
+      <c r="F20" s="152"/>
+      <c r="G20" s="152"/>
+      <c r="H20" s="152"/>
+      <c r="I20" s="152"/>
+      <c r="J20" s="152"/>
+      <c r="K20" s="152"/>
+      <c r="L20" s="152"/>
+      <c r="M20" s="152"/>
+      <c r="N20" s="152"/>
+      <c r="O20" s="153"/>
     </row>
     <row r="21" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C21" s="150"/>
-      <c r="D21" s="151"/>
-      <c r="E21" s="151"/>
-      <c r="F21" s="151"/>
-      <c r="G21" s="151"/>
-      <c r="H21" s="151"/>
-      <c r="I21" s="151"/>
-      <c r="J21" s="151"/>
-      <c r="K21" s="151"/>
-      <c r="L21" s="151"/>
-      <c r="M21" s="151"/>
-      <c r="N21" s="151"/>
-      <c r="O21" s="152"/>
+      <c r="C21" s="151"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="152"/>
+      <c r="H21" s="152"/>
+      <c r="I21" s="152"/>
+      <c r="J21" s="152"/>
+      <c r="K21" s="152"/>
+      <c r="L21" s="152"/>
+      <c r="M21" s="152"/>
+      <c r="N21" s="152"/>
+      <c r="O21" s="153"/>
     </row>
     <row r="22" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C22" s="153"/>
-      <c r="D22" s="154"/>
-      <c r="E22" s="154"/>
-      <c r="F22" s="154"/>
-      <c r="G22" s="154"/>
-      <c r="H22" s="154"/>
-      <c r="I22" s="154"/>
-      <c r="J22" s="154"/>
-      <c r="K22" s="154"/>
-      <c r="L22" s="154"/>
-      <c r="M22" s="154"/>
-      <c r="N22" s="154"/>
-      <c r="O22" s="155"/>
+      <c r="C22" s="154"/>
+      <c r="D22" s="155"/>
+      <c r="E22" s="155"/>
+      <c r="F22" s="155"/>
+      <c r="G22" s="155"/>
+      <c r="H22" s="155"/>
+      <c r="I22" s="155"/>
+      <c r="J22" s="155"/>
+      <c r="K22" s="155"/>
+      <c r="L22" s="155"/>
+      <c r="M22" s="155"/>
+      <c r="N22" s="155"/>
+      <c r="O22" s="156"/>
     </row>
     <row r="24" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C24" s="144" t="s">
+      <c r="C24" s="162" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="144" t="s">
+      <c r="D24" s="162" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="144" t="s">
+      <c r="E24" s="162" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="144" t="s">
+      <c r="F24" s="162" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="144" t="s">
+      <c r="G24" s="162" t="s">
         <v>23</v>
       </c>
-      <c r="H24" s="156" t="s">
+      <c r="H24" s="159" t="s">
         <v>24</v>
       </c>
-      <c r="I24" s="157"/>
-      <c r="J24" s="157"/>
-      <c r="K24" s="157"/>
-      <c r="L24" s="157"/>
-      <c r="M24" s="157"/>
-      <c r="N24" s="157"/>
-      <c r="O24" s="158"/>
+      <c r="I24" s="160"/>
+      <c r="J24" s="160"/>
+      <c r="K24" s="160"/>
+      <c r="L24" s="160"/>
+      <c r="M24" s="160"/>
+      <c r="N24" s="160"/>
+      <c r="O24" s="161"/>
     </row>
     <row r="25" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C25" s="144"/>
-      <c r="D25" s="144"/>
-      <c r="E25" s="144"/>
-      <c r="F25" s="144"/>
-      <c r="G25" s="144"/>
-      <c r="H25" s="156" t="s">
+      <c r="C25" s="162"/>
+      <c r="D25" s="162"/>
+      <c r="E25" s="162"/>
+      <c r="F25" s="162"/>
+      <c r="G25" s="162"/>
+      <c r="H25" s="159" t="s">
         <v>25</v>
       </c>
-      <c r="I25" s="158"/>
+      <c r="I25" s="161"/>
       <c r="J25" s="128" t="s">
         <v>26</v>
       </c>
@@ -21739,7 +21739,7 @@
       <c r="O25" s="130"/>
     </row>
     <row r="26" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C26" s="142" t="s">
+      <c r="C26" s="146" t="s">
         <v>27</v>
       </c>
       <c r="D26" s="131" t="s">
@@ -21748,56 +21748,56 @@
       <c r="E26" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="F26" s="142" t="s">
+      <c r="F26" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="G26" s="145" t="s">
+      <c r="G26" s="157" t="s">
         <v>31</v>
       </c>
-      <c r="H26" s="142" t="s">
+      <c r="H26" s="146" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="142" t="s">
+      <c r="I26" s="146" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="142" t="s">
+      <c r="J26" s="146" t="s">
         <v>34</v>
       </c>
-      <c r="K26" s="142" t="s">
+      <c r="K26" s="146" t="s">
         <v>35</v>
       </c>
-      <c r="L26" s="142" t="s">
+      <c r="L26" s="146" t="s">
         <v>36</v>
       </c>
-      <c r="M26" s="142" t="s">
+      <c r="M26" s="146" t="s">
         <v>37</v>
       </c>
-      <c r="N26" s="145" t="s">
+      <c r="N26" s="157" t="s">
         <v>38</v>
       </c>
-      <c r="O26" s="142"/>
+      <c r="O26" s="146"/>
     </row>
     <row r="27" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C27" s="142"/>
+      <c r="C27" s="146"/>
       <c r="D27" s="131" t="s">
         <v>29</v>
       </c>
       <c r="E27" s="131" t="s">
         <v>39</v>
       </c>
-      <c r="F27" s="142"/>
-      <c r="G27" s="145"/>
-      <c r="H27" s="142"/>
-      <c r="I27" s="142"/>
-      <c r="J27" s="142"/>
-      <c r="K27" s="142"/>
-      <c r="L27" s="142"/>
-      <c r="M27" s="142"/>
-      <c r="N27" s="145"/>
-      <c r="O27" s="142"/>
+      <c r="F27" s="146"/>
+      <c r="G27" s="157"/>
+      <c r="H27" s="146"/>
+      <c r="I27" s="146"/>
+      <c r="J27" s="146"/>
+      <c r="K27" s="146"/>
+      <c r="L27" s="146"/>
+      <c r="M27" s="146"/>
+      <c r="N27" s="157"/>
+      <c r="O27" s="146"/>
     </row>
     <row r="28" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C28" s="143" t="s">
+      <c r="C28" s="147" t="s">
         <v>40</v>
       </c>
       <c r="D28" s="132" t="s">
@@ -21806,55 +21806,55 @@
       <c r="E28" s="132" t="s">
         <v>41</v>
       </c>
-      <c r="F28" s="143" t="s">
+      <c r="F28" s="147" t="s">
         <v>42</v>
       </c>
-      <c r="G28" s="146" t="s">
+      <c r="G28" s="158" t="s">
         <v>43</v>
       </c>
-      <c r="H28" s="143" t="s">
+      <c r="H28" s="147" t="s">
         <v>44</v>
       </c>
-      <c r="I28" s="143" t="s">
+      <c r="I28" s="147" t="s">
         <v>45</v>
       </c>
-      <c r="J28" s="143" t="s">
+      <c r="J28" s="147" t="s">
         <v>46</v>
       </c>
-      <c r="K28" s="143" t="s">
+      <c r="K28" s="147" t="s">
         <v>47</v>
       </c>
-      <c r="L28" s="143" t="s">
+      <c r="L28" s="147" t="s">
         <v>48</v>
       </c>
-      <c r="M28" s="143" t="s">
+      <c r="M28" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="N28" s="146" t="s">
+      <c r="N28" s="158" t="s">
         <v>50</v>
       </c>
-      <c r="O28" s="143" t="s">
+      <c r="O28" s="147" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="29" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C29" s="143"/>
+      <c r="C29" s="147"/>
       <c r="D29" s="132" t="s">
         <v>41</v>
       </c>
       <c r="E29" s="132" t="s">
         <v>52</v>
       </c>
-      <c r="F29" s="143"/>
-      <c r="G29" s="146"/>
-      <c r="H29" s="143"/>
-      <c r="I29" s="143"/>
-      <c r="J29" s="143"/>
-      <c r="K29" s="143"/>
-      <c r="L29" s="143"/>
-      <c r="M29" s="143"/>
-      <c r="N29" s="146"/>
-      <c r="O29" s="143"/>
+      <c r="F29" s="147"/>
+      <c r="G29" s="158"/>
+      <c r="H29" s="147"/>
+      <c r="I29" s="147"/>
+      <c r="J29" s="147"/>
+      <c r="K29" s="147"/>
+      <c r="L29" s="147"/>
+      <c r="M29" s="147"/>
+      <c r="N29" s="158"/>
+      <c r="O29" s="147"/>
     </row>
     <row r="30" spans="3:15" ht="28" x14ac:dyDescent="0.25">
       <c r="C30" s="133" t="s">
@@ -21973,6 +21973,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
     <mergeCell ref="O26:O27"/>
     <mergeCell ref="O28:O29"/>
     <mergeCell ref="C16:O22"/>
@@ -21989,20 +22003,6 @@
     <mergeCell ref="K28:K29"/>
     <mergeCell ref="H24:O24"/>
     <mergeCell ref="H25:I25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="G28:G29"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22027,111 +22027,111 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="148" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="148"/>
-      <c r="E4" s="148"/>
-      <c r="F4" s="148"/>
-      <c r="G4" s="148"/>
-      <c r="H4" s="148"/>
-      <c r="I4" s="148"/>
-      <c r="J4" s="148"/>
-      <c r="K4" s="148"/>
-      <c r="L4" s="148"/>
-      <c r="M4" s="148"/>
-      <c r="N4" s="148"/>
-      <c r="O4" s="149"/>
+      <c r="D4" s="149"/>
+      <c r="E4" s="149"/>
+      <c r="F4" s="149"/>
+      <c r="G4" s="149"/>
+      <c r="H4" s="149"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="149"/>
+      <c r="L4" s="149"/>
+      <c r="M4" s="149"/>
+      <c r="N4" s="149"/>
+      <c r="O4" s="150"/>
     </row>
     <row r="5" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C5" s="150"/>
-      <c r="D5" s="151"/>
-      <c r="E5" s="151"/>
-      <c r="F5" s="151"/>
-      <c r="G5" s="151"/>
-      <c r="H5" s="151"/>
-      <c r="I5" s="151"/>
-      <c r="J5" s="151"/>
-      <c r="K5" s="151"/>
-      <c r="L5" s="151"/>
-      <c r="M5" s="151"/>
-      <c r="N5" s="151"/>
-      <c r="O5" s="152"/>
+      <c r="C5" s="151"/>
+      <c r="D5" s="152"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="152"/>
+      <c r="G5" s="152"/>
+      <c r="H5" s="152"/>
+      <c r="I5" s="152"/>
+      <c r="J5" s="152"/>
+      <c r="K5" s="152"/>
+      <c r="L5" s="152"/>
+      <c r="M5" s="152"/>
+      <c r="N5" s="152"/>
+      <c r="O5" s="153"/>
     </row>
     <row r="6" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C6" s="150"/>
-      <c r="D6" s="151"/>
-      <c r="E6" s="151"/>
-      <c r="F6" s="151"/>
-      <c r="G6" s="151"/>
-      <c r="H6" s="151"/>
-      <c r="I6" s="151"/>
-      <c r="J6" s="151"/>
-      <c r="K6" s="151"/>
-      <c r="L6" s="151"/>
-      <c r="M6" s="151"/>
-      <c r="N6" s="151"/>
-      <c r="O6" s="152"/>
+      <c r="C6" s="151"/>
+      <c r="D6" s="152"/>
+      <c r="E6" s="152"/>
+      <c r="F6" s="152"/>
+      <c r="G6" s="152"/>
+      <c r="H6" s="152"/>
+      <c r="I6" s="152"/>
+      <c r="J6" s="152"/>
+      <c r="K6" s="152"/>
+      <c r="L6" s="152"/>
+      <c r="M6" s="152"/>
+      <c r="N6" s="152"/>
+      <c r="O6" s="153"/>
     </row>
     <row r="7" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C7" s="150"/>
-      <c r="D7" s="151"/>
-      <c r="E7" s="151"/>
-      <c r="F7" s="151"/>
-      <c r="G7" s="151"/>
-      <c r="H7" s="151"/>
-      <c r="I7" s="151"/>
-      <c r="J7" s="151"/>
-      <c r="K7" s="151"/>
-      <c r="L7" s="151"/>
-      <c r="M7" s="151"/>
-      <c r="N7" s="151"/>
-      <c r="O7" s="152"/>
+      <c r="C7" s="151"/>
+      <c r="D7" s="152"/>
+      <c r="E7" s="152"/>
+      <c r="F7" s="152"/>
+      <c r="G7" s="152"/>
+      <c r="H7" s="152"/>
+      <c r="I7" s="152"/>
+      <c r="J7" s="152"/>
+      <c r="K7" s="152"/>
+      <c r="L7" s="152"/>
+      <c r="M7" s="152"/>
+      <c r="N7" s="152"/>
+      <c r="O7" s="153"/>
     </row>
     <row r="8" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C8" s="150"/>
-      <c r="D8" s="151"/>
-      <c r="E8" s="151"/>
-      <c r="F8" s="151"/>
-      <c r="G8" s="151"/>
-      <c r="H8" s="151"/>
-      <c r="I8" s="151"/>
-      <c r="J8" s="151"/>
-      <c r="K8" s="151"/>
-      <c r="L8" s="151"/>
-      <c r="M8" s="151"/>
-      <c r="N8" s="151"/>
-      <c r="O8" s="152"/>
+      <c r="C8" s="151"/>
+      <c r="D8" s="152"/>
+      <c r="E8" s="152"/>
+      <c r="F8" s="152"/>
+      <c r="G8" s="152"/>
+      <c r="H8" s="152"/>
+      <c r="I8" s="152"/>
+      <c r="J8" s="152"/>
+      <c r="K8" s="152"/>
+      <c r="L8" s="152"/>
+      <c r="M8" s="152"/>
+      <c r="N8" s="152"/>
+      <c r="O8" s="153"/>
     </row>
     <row r="9" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C9" s="150"/>
-      <c r="D9" s="151"/>
-      <c r="E9" s="151"/>
-      <c r="F9" s="151"/>
-      <c r="G9" s="151"/>
-      <c r="H9" s="151"/>
-      <c r="I9" s="151"/>
-      <c r="J9" s="151"/>
-      <c r="K9" s="151"/>
-      <c r="L9" s="151"/>
-      <c r="M9" s="151"/>
-      <c r="N9" s="151"/>
-      <c r="O9" s="152"/>
+      <c r="C9" s="151"/>
+      <c r="D9" s="152"/>
+      <c r="E9" s="152"/>
+      <c r="F9" s="152"/>
+      <c r="G9" s="152"/>
+      <c r="H9" s="152"/>
+      <c r="I9" s="152"/>
+      <c r="J9" s="152"/>
+      <c r="K9" s="152"/>
+      <c r="L9" s="152"/>
+      <c r="M9" s="152"/>
+      <c r="N9" s="152"/>
+      <c r="O9" s="153"/>
     </row>
     <row r="10" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C10" s="153"/>
-      <c r="D10" s="154"/>
-      <c r="E10" s="154"/>
-      <c r="F10" s="154"/>
-      <c r="G10" s="154"/>
-      <c r="H10" s="154"/>
-      <c r="I10" s="154"/>
-      <c r="J10" s="154"/>
-      <c r="K10" s="154"/>
-      <c r="L10" s="154"/>
-      <c r="M10" s="154"/>
-      <c r="N10" s="154"/>
-      <c r="O10" s="155"/>
+      <c r="C10" s="154"/>
+      <c r="D10" s="155"/>
+      <c r="E10" s="155"/>
+      <c r="F10" s="155"/>
+      <c r="G10" s="155"/>
+      <c r="H10" s="155"/>
+      <c r="I10" s="155"/>
+      <c r="J10" s="155"/>
+      <c r="K10" s="155"/>
+      <c r="L10" s="155"/>
+      <c r="M10" s="155"/>
+      <c r="N10" s="155"/>
+      <c r="O10" s="156"/>
     </row>
     <row r="15" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D15" s="115" t="s">
@@ -22157,10 +22157,10 @@
       </c>
     </row>
     <row r="16" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="D16" s="159" t="s">
+      <c r="D16" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="159" t="s">
+      <c r="E16" s="163" t="s">
         <v>91</v>
       </c>
       <c r="F16" s="48" t="s">
@@ -22183,8 +22183,8 @@
       <c r="C17" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="159"/>
-      <c r="E17" s="159"/>
+      <c r="D17" s="163"/>
+      <c r="E17" s="163"/>
       <c r="F17" s="48" t="s">
         <v>97</v>
       </c>
@@ -22202,8 +22202,8 @@
       </c>
     </row>
     <row r="18" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="D18" s="159"/>
-      <c r="E18" s="159"/>
+      <c r="D18" s="163"/>
+      <c r="E18" s="163"/>
       <c r="F18" s="48" t="s">
         <v>101</v>
       </c>
@@ -22221,10 +22221,10 @@
       </c>
     </row>
     <row r="19" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="D19" s="159" t="s">
+      <c r="D19" s="163" t="s">
         <v>105</v>
       </c>
-      <c r="E19" s="159" t="s">
+      <c r="E19" s="163" t="s">
         <v>106</v>
       </c>
       <c r="F19" s="48" t="s">
@@ -22248,8 +22248,8 @@
       <c r="C20" t="s">
         <v>111</v>
       </c>
-      <c r="D20" s="159"/>
-      <c r="E20" s="159"/>
+      <c r="D20" s="163"/>
+      <c r="E20" s="163"/>
       <c r="F20" s="48" t="s">
         <v>112</v>
       </c>
@@ -22268,8 +22268,8 @@
       <c r="P20" s="113"/>
     </row>
     <row r="21" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="D21" s="159"/>
-      <c r="E21" s="159"/>
+      <c r="D21" s="163"/>
+      <c r="E21" s="163"/>
       <c r="F21" s="48" t="s">
         <v>116</v>
       </c>
@@ -22287,10 +22287,10 @@
       </c>
     </row>
     <row r="22" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="D22" s="159" t="s">
+      <c r="D22" s="163" t="s">
         <v>120</v>
       </c>
-      <c r="E22" s="159" t="s">
+      <c r="E22" s="163" t="s">
         <v>121</v>
       </c>
       <c r="F22" s="48" t="s">
@@ -22313,8 +22313,8 @@
       <c r="C23" t="s">
         <v>125</v>
       </c>
-      <c r="D23" s="159"/>
-      <c r="E23" s="159"/>
+      <c r="D23" s="163"/>
+      <c r="E23" s="163"/>
       <c r="F23" s="48" t="s">
         <v>112</v>
       </c>
@@ -22332,8 +22332,8 @@
       </c>
     </row>
     <row r="24" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="D24" s="159"/>
-      <c r="E24" s="159"/>
+      <c r="D24" s="163"/>
+      <c r="E24" s="163"/>
       <c r="F24" s="48" t="s">
         <v>116</v>
       </c>
@@ -22351,10 +22351,10 @@
       </c>
     </row>
     <row r="25" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="D25" s="159" t="s">
+      <c r="D25" s="163" t="s">
         <v>132</v>
       </c>
-      <c r="E25" s="159" t="s">
+      <c r="E25" s="163" t="s">
         <v>133</v>
       </c>
       <c r="F25" s="48" t="s">
@@ -22378,8 +22378,8 @@
       <c r="C26" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="159"/>
-      <c r="E26" s="159"/>
+      <c r="D26" s="163"/>
+      <c r="E26" s="163"/>
       <c r="F26" s="48" t="s">
         <v>139</v>
       </c>
@@ -22397,8 +22397,8 @@
       </c>
     </row>
     <row r="27" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="D27" s="159"/>
-      <c r="E27" s="159"/>
+      <c r="D27" s="163"/>
+      <c r="E27" s="163"/>
       <c r="F27" s="48" t="s">
         <v>143</v>
       </c>
@@ -22416,10 +22416,10 @@
       </c>
     </row>
     <row r="28" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="D28" s="160" t="s">
+      <c r="D28" s="164" t="s">
         <v>147</v>
       </c>
-      <c r="E28" s="159" t="s">
+      <c r="E28" s="163" t="s">
         <v>148</v>
       </c>
       <c r="F28" s="48" t="s">
@@ -22442,8 +22442,8 @@
       <c r="C29" t="s">
         <v>153</v>
       </c>
-      <c r="D29" s="161"/>
-      <c r="E29" s="159"/>
+      <c r="D29" s="165"/>
+      <c r="E29" s="163"/>
       <c r="F29" s="48" t="s">
         <v>154</v>
       </c>
@@ -22461,8 +22461,8 @@
       </c>
     </row>
     <row r="30" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="D30" s="162"/>
-      <c r="E30" s="159"/>
+      <c r="D30" s="166"/>
+      <c r="E30" s="163"/>
       <c r="F30" s="48" t="s">
         <v>158</v>
       </c>
@@ -22481,10 +22481,10 @@
       <c r="R30" s="113"/>
     </row>
     <row r="31" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="D31" s="159" t="s">
+      <c r="D31" s="163" t="s">
         <v>162</v>
       </c>
-      <c r="E31" s="159" t="s">
+      <c r="E31" s="163" t="s">
         <v>163</v>
       </c>
       <c r="F31" s="48" t="s">
@@ -22508,8 +22508,8 @@
       <c r="C32" t="s">
         <v>168</v>
       </c>
-      <c r="D32" s="159"/>
-      <c r="E32" s="159"/>
+      <c r="D32" s="163"/>
+      <c r="E32" s="163"/>
       <c r="F32" s="48" t="s">
         <v>169</v>
       </c>
@@ -22527,8 +22527,8 @@
       </c>
     </row>
     <row r="33" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D33" s="159"/>
-      <c r="E33" s="159"/>
+      <c r="D33" s="163"/>
+      <c r="E33" s="163"/>
       <c r="F33" s="48" t="s">
         <v>173</v>
       </c>
@@ -22623,140 +22623,140 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C2" s="163" t="s">
+      <c r="C2" s="143" t="s">
         <v>189</v>
       </c>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
-      <c r="M2" s="163"/>
-      <c r="N2" s="163"/>
-      <c r="O2" s="163"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
+      <c r="K2" s="143"/>
+      <c r="L2" s="143"/>
+      <c r="M2" s="143"/>
+      <c r="N2" s="143"/>
+      <c r="O2" s="143"/>
     </row>
     <row r="3" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C3" s="163"/>
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="163"/>
-      <c r="K3" s="163"/>
-      <c r="L3" s="163"/>
-      <c r="M3" s="163"/>
-      <c r="N3" s="163"/>
-      <c r="O3" s="163"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="143"/>
+      <c r="I3" s="143"/>
+      <c r="J3" s="143"/>
+      <c r="K3" s="143"/>
+      <c r="L3" s="143"/>
+      <c r="M3" s="143"/>
+      <c r="N3" s="143"/>
+      <c r="O3" s="143"/>
     </row>
     <row r="5" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>133</v>
       </c>
-      <c r="E5" s="164" t="s">
+      <c r="E5" s="167" t="s">
         <v>190</v>
       </c>
-      <c r="F5" s="164"/>
-      <c r="G5" s="164"/>
-      <c r="H5" s="164"/>
-      <c r="I5" s="164"/>
-      <c r="J5" s="164"/>
-      <c r="K5" s="164"/>
-      <c r="L5" s="164"/>
-      <c r="M5" s="164"/>
-      <c r="N5" s="164"/>
-      <c r="O5" s="164"/>
+      <c r="F5" s="167"/>
+      <c r="G5" s="167"/>
+      <c r="H5" s="167"/>
+      <c r="I5" s="167"/>
+      <c r="J5" s="167"/>
+      <c r="K5" s="167"/>
+      <c r="L5" s="167"/>
+      <c r="M5" s="167"/>
+      <c r="N5" s="167"/>
+      <c r="O5" s="167"/>
     </row>
     <row r="6" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>191</v>
       </c>
-      <c r="E6" s="164" t="s">
+      <c r="E6" s="167" t="s">
         <v>190</v>
       </c>
-      <c r="F6" s="164"/>
-      <c r="G6" s="164"/>
-      <c r="H6" s="164"/>
-      <c r="I6" s="164"/>
-      <c r="J6" s="164"/>
-      <c r="K6" s="164"/>
-      <c r="L6" s="164"/>
-      <c r="M6" s="164"/>
-      <c r="N6" s="164"/>
-      <c r="O6" s="164"/>
+      <c r="F6" s="167"/>
+      <c r="G6" s="167"/>
+      <c r="H6" s="167"/>
+      <c r="I6" s="167"/>
+      <c r="J6" s="167"/>
+      <c r="K6" s="167"/>
+      <c r="L6" s="167"/>
+      <c r="M6" s="167"/>
+      <c r="N6" s="167"/>
+      <c r="O6" s="167"/>
     </row>
     <row r="7" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="164" t="s">
+      <c r="E7" s="167" t="s">
         <v>190</v>
       </c>
-      <c r="F7" s="164"/>
-      <c r="G7" s="164"/>
-      <c r="H7" s="164"/>
-      <c r="I7" s="164"/>
-      <c r="J7" s="164"/>
-      <c r="K7" s="164"/>
-      <c r="L7" s="164"/>
-      <c r="M7" s="164"/>
-      <c r="N7" s="164"/>
-      <c r="O7" s="164"/>
+      <c r="F7" s="167"/>
+      <c r="G7" s="167"/>
+      <c r="H7" s="167"/>
+      <c r="I7" s="167"/>
+      <c r="J7" s="167"/>
+      <c r="K7" s="167"/>
+      <c r="L7" s="167"/>
+      <c r="M7" s="167"/>
+      <c r="N7" s="167"/>
+      <c r="O7" s="167"/>
     </row>
     <row r="8" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>192</v>
       </c>
-      <c r="E8" s="164" t="s">
+      <c r="E8" s="167" t="s">
         <v>193</v>
       </c>
-      <c r="F8" s="164"/>
-      <c r="G8" s="164"/>
-      <c r="H8" s="164"/>
-      <c r="I8" s="164"/>
-      <c r="J8" s="164"/>
-      <c r="K8" s="164"/>
-      <c r="L8" s="164"/>
-      <c r="M8" s="164"/>
-      <c r="N8" s="164"/>
-      <c r="O8" s="164"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="167"/>
+      <c r="H8" s="167"/>
+      <c r="I8" s="167"/>
+      <c r="J8" s="167"/>
+      <c r="K8" s="167"/>
+      <c r="L8" s="167"/>
+      <c r="M8" s="167"/>
+      <c r="N8" s="167"/>
+      <c r="O8" s="167"/>
     </row>
     <row r="12" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C12" s="163" t="s">
+      <c r="C12" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="D12" s="163"/>
-      <c r="E12" s="163"/>
-      <c r="F12" s="163"/>
-      <c r="G12" s="163"/>
-      <c r="H12" s="163"/>
-      <c r="I12" s="163"/>
-      <c r="J12" s="163"/>
-      <c r="K12" s="163"/>
-      <c r="L12" s="163"/>
-      <c r="M12" s="163"/>
-      <c r="N12" s="163"/>
-      <c r="O12" s="163"/>
+      <c r="D12" s="143"/>
+      <c r="E12" s="143"/>
+      <c r="F12" s="143"/>
+      <c r="G12" s="143"/>
+      <c r="H12" s="143"/>
+      <c r="I12" s="143"/>
+      <c r="J12" s="143"/>
+      <c r="K12" s="143"/>
+      <c r="L12" s="143"/>
+      <c r="M12" s="143"/>
+      <c r="N12" s="143"/>
+      <c r="O12" s="143"/>
     </row>
     <row r="13" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C13" s="163"/>
-      <c r="D13" s="163"/>
-      <c r="E13" s="163"/>
-      <c r="F13" s="163"/>
-      <c r="G13" s="163"/>
-      <c r="H13" s="163"/>
-      <c r="I13" s="163"/>
-      <c r="J13" s="163"/>
-      <c r="K13" s="163"/>
-      <c r="L13" s="163"/>
-      <c r="M13" s="163"/>
-      <c r="N13" s="163"/>
-      <c r="O13" s="163"/>
+      <c r="C13" s="143"/>
+      <c r="D13" s="143"/>
+      <c r="E13" s="143"/>
+      <c r="F13" s="143"/>
+      <c r="G13" s="143"/>
+      <c r="H13" s="143"/>
+      <c r="I13" s="143"/>
+      <c r="J13" s="143"/>
+      <c r="K13" s="143"/>
+      <c r="L13" s="143"/>
+      <c r="M13" s="143"/>
+      <c r="N13" s="143"/>
+      <c r="O13" s="143"/>
     </row>
     <row r="14" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D14" s="113"/>
@@ -22768,129 +22768,129 @@
       <c r="C15" t="s">
         <v>195</v>
       </c>
-      <c r="E15" s="164"/>
-      <c r="F15" s="164"/>
-      <c r="G15" s="164"/>
-      <c r="H15" s="164"/>
-      <c r="I15" s="164"/>
-      <c r="J15" s="164"/>
-      <c r="K15" s="164"/>
-      <c r="L15" s="164"/>
-      <c r="M15" s="164"/>
-      <c r="N15" s="164"/>
-      <c r="O15" s="164"/>
+      <c r="E15" s="167"/>
+      <c r="F15" s="167"/>
+      <c r="G15" s="167"/>
+      <c r="H15" s="167"/>
+      <c r="I15" s="167"/>
+      <c r="J15" s="167"/>
+      <c r="K15" s="167"/>
+      <c r="L15" s="167"/>
+      <c r="M15" s="167"/>
+      <c r="N15" s="167"/>
+      <c r="O15" s="167"/>
     </row>
     <row r="16" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>196</v>
       </c>
-      <c r="E16" s="164"/>
-      <c r="F16" s="164"/>
-      <c r="G16" s="164"/>
-      <c r="H16" s="164"/>
-      <c r="I16" s="164"/>
-      <c r="J16" s="164"/>
-      <c r="K16" s="164"/>
-      <c r="L16" s="164"/>
-      <c r="M16" s="164"/>
-      <c r="N16" s="164"/>
-      <c r="O16" s="164"/>
+      <c r="E16" s="167"/>
+      <c r="F16" s="167"/>
+      <c r="G16" s="167"/>
+      <c r="H16" s="167"/>
+      <c r="I16" s="167"/>
+      <c r="J16" s="167"/>
+      <c r="K16" s="167"/>
+      <c r="L16" s="167"/>
+      <c r="M16" s="167"/>
+      <c r="N16" s="167"/>
+      <c r="O16" s="167"/>
     </row>
     <row r="17" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>197</v>
       </c>
-      <c r="E17" s="164"/>
-      <c r="F17" s="164"/>
-      <c r="G17" s="164"/>
-      <c r="H17" s="164"/>
-      <c r="I17" s="164"/>
-      <c r="J17" s="164"/>
-      <c r="K17" s="164"/>
-      <c r="L17" s="164"/>
-      <c r="M17" s="164"/>
-      <c r="N17" s="164"/>
-      <c r="O17" s="164"/>
+      <c r="E17" s="167"/>
+      <c r="F17" s="167"/>
+      <c r="G17" s="167"/>
+      <c r="H17" s="167"/>
+      <c r="I17" s="167"/>
+      <c r="J17" s="167"/>
+      <c r="K17" s="167"/>
+      <c r="L17" s="167"/>
+      <c r="M17" s="167"/>
+      <c r="N17" s="167"/>
+      <c r="O17" s="167"/>
     </row>
     <row r="18" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>198</v>
       </c>
-      <c r="E18" s="164"/>
-      <c r="F18" s="164"/>
-      <c r="G18" s="164"/>
-      <c r="H18" s="164"/>
-      <c r="I18" s="164"/>
-      <c r="J18" s="164"/>
-      <c r="K18" s="164"/>
-      <c r="L18" s="164"/>
-      <c r="M18" s="164"/>
-      <c r="N18" s="164"/>
-      <c r="O18" s="164"/>
+      <c r="E18" s="167"/>
+      <c r="F18" s="167"/>
+      <c r="G18" s="167"/>
+      <c r="H18" s="167"/>
+      <c r="I18" s="167"/>
+      <c r="J18" s="167"/>
+      <c r="K18" s="167"/>
+      <c r="L18" s="167"/>
+      <c r="M18" s="167"/>
+      <c r="N18" s="167"/>
+      <c r="O18" s="167"/>
     </row>
     <row r="19" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>199</v>
       </c>
-      <c r="E19" s="164"/>
-      <c r="F19" s="164"/>
-      <c r="G19" s="164"/>
-      <c r="H19" s="164"/>
-      <c r="I19" s="164"/>
-      <c r="J19" s="164"/>
-      <c r="K19" s="164"/>
-      <c r="L19" s="164"/>
-      <c r="M19" s="164"/>
-      <c r="N19" s="164"/>
-      <c r="O19" s="164"/>
+      <c r="E19" s="167"/>
+      <c r="F19" s="167"/>
+      <c r="G19" s="167"/>
+      <c r="H19" s="167"/>
+      <c r="I19" s="167"/>
+      <c r="J19" s="167"/>
+      <c r="K19" s="167"/>
+      <c r="L19" s="167"/>
+      <c r="M19" s="167"/>
+      <c r="N19" s="167"/>
+      <c r="O19" s="167"/>
     </row>
     <row r="20" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>200</v>
       </c>
-      <c r="E20" s="164"/>
-      <c r="F20" s="164"/>
-      <c r="G20" s="164"/>
-      <c r="H20" s="164"/>
-      <c r="I20" s="164"/>
-      <c r="J20" s="164"/>
-      <c r="K20" s="164"/>
-      <c r="L20" s="164"/>
-      <c r="M20" s="164"/>
-      <c r="N20" s="164"/>
-      <c r="O20" s="164"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="167"/>
+      <c r="G20" s="167"/>
+      <c r="H20" s="167"/>
+      <c r="I20" s="167"/>
+      <c r="J20" s="167"/>
+      <c r="K20" s="167"/>
+      <c r="L20" s="167"/>
+      <c r="M20" s="167"/>
+      <c r="N20" s="167"/>
+      <c r="O20" s="167"/>
     </row>
     <row r="24" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C24" s="163" t="s">
+      <c r="C24" s="143" t="s">
         <v>201</v>
       </c>
-      <c r="D24" s="163"/>
-      <c r="E24" s="163"/>
-      <c r="F24" s="163"/>
-      <c r="G24" s="163"/>
-      <c r="H24" s="163"/>
-      <c r="I24" s="163"/>
-      <c r="J24" s="163"/>
-      <c r="K24" s="163"/>
-      <c r="L24" s="163"/>
-      <c r="M24" s="163"/>
-      <c r="N24" s="163"/>
-      <c r="O24" s="163"/>
+      <c r="D24" s="143"/>
+      <c r="E24" s="143"/>
+      <c r="F24" s="143"/>
+      <c r="G24" s="143"/>
+      <c r="H24" s="143"/>
+      <c r="I24" s="143"/>
+      <c r="J24" s="143"/>
+      <c r="K24" s="143"/>
+      <c r="L24" s="143"/>
+      <c r="M24" s="143"/>
+      <c r="N24" s="143"/>
+      <c r="O24" s="143"/>
     </row>
     <row r="25" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C25" s="163"/>
-      <c r="D25" s="163"/>
-      <c r="E25" s="163"/>
-      <c r="F25" s="163"/>
-      <c r="G25" s="163"/>
-      <c r="H25" s="163"/>
-      <c r="I25" s="163"/>
-      <c r="J25" s="163"/>
-      <c r="K25" s="163"/>
-      <c r="L25" s="163"/>
-      <c r="M25" s="163"/>
-      <c r="N25" s="163"/>
-      <c r="O25" s="163"/>
+      <c r="C25" s="143"/>
+      <c r="D25" s="143"/>
+      <c r="E25" s="143"/>
+      <c r="F25" s="143"/>
+      <c r="G25" s="143"/>
+      <c r="H25" s="143"/>
+      <c r="I25" s="143"/>
+      <c r="J25" s="143"/>
+      <c r="K25" s="143"/>
+      <c r="L25" s="143"/>
+      <c r="M25" s="143"/>
+      <c r="N25" s="143"/>
+      <c r="O25" s="143"/>
     </row>
     <row r="26" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D26" s="113" t="s">
@@ -23209,36 +23209,36 @@
       <c r="K41" s="2"/>
     </row>
     <row r="44" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C44" s="163" t="s">
+      <c r="C44" s="143" t="s">
         <v>207</v>
       </c>
-      <c r="D44" s="163"/>
-      <c r="E44" s="163"/>
-      <c r="F44" s="163"/>
-      <c r="G44" s="163"/>
-      <c r="H44" s="163"/>
-      <c r="I44" s="163"/>
-      <c r="J44" s="163"/>
-      <c r="K44" s="163"/>
-      <c r="L44" s="163"/>
-      <c r="M44" s="163"/>
-      <c r="N44" s="163"/>
-      <c r="O44" s="163"/>
+      <c r="D44" s="143"/>
+      <c r="E44" s="143"/>
+      <c r="F44" s="143"/>
+      <c r="G44" s="143"/>
+      <c r="H44" s="143"/>
+      <c r="I44" s="143"/>
+      <c r="J44" s="143"/>
+      <c r="K44" s="143"/>
+      <c r="L44" s="143"/>
+      <c r="M44" s="143"/>
+      <c r="N44" s="143"/>
+      <c r="O44" s="143"/>
     </row>
     <row r="45" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C45" s="163"/>
-      <c r="D45" s="163"/>
-      <c r="E45" s="163"/>
-      <c r="F45" s="163"/>
-      <c r="G45" s="163"/>
-      <c r="H45" s="163"/>
-      <c r="I45" s="163"/>
-      <c r="J45" s="163"/>
-      <c r="K45" s="163"/>
-      <c r="L45" s="163"/>
-      <c r="M45" s="163"/>
-      <c r="N45" s="163"/>
-      <c r="O45" s="163"/>
+      <c r="C45" s="143"/>
+      <c r="D45" s="143"/>
+      <c r="E45" s="143"/>
+      <c r="F45" s="143"/>
+      <c r="G45" s="143"/>
+      <c r="H45" s="143"/>
+      <c r="I45" s="143"/>
+      <c r="J45" s="143"/>
+      <c r="K45" s="143"/>
+      <c r="L45" s="143"/>
+      <c r="M45" s="143"/>
+      <c r="N45" s="143"/>
+      <c r="O45" s="143"/>
     </row>
     <row r="46" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C46" s="2"/>
@@ -23437,356 +23437,356 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C2" s="163" t="s">
+      <c r="C2" s="143" t="s">
         <v>165</v>
       </c>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
-      <c r="M2" s="163"/>
-      <c r="N2" s="163"/>
-      <c r="O2" s="163"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
+      <c r="K2" s="143"/>
+      <c r="L2" s="143"/>
+      <c r="M2" s="143"/>
+      <c r="N2" s="143"/>
+      <c r="O2" s="143"/>
     </row>
     <row r="3" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C3" s="163"/>
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="163"/>
-      <c r="K3" s="163"/>
-      <c r="L3" s="163"/>
-      <c r="M3" s="163"/>
-      <c r="N3" s="163"/>
-      <c r="O3" s="163"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="143"/>
+      <c r="I3" s="143"/>
+      <c r="J3" s="143"/>
+      <c r="K3" s="143"/>
+      <c r="L3" s="143"/>
+      <c r="M3" s="143"/>
+      <c r="N3" s="143"/>
+      <c r="O3" s="143"/>
     </row>
     <row r="5" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C5" s="139" t="s">
         <v>1117</v>
       </c>
-      <c r="E5" s="164" t="s">
+      <c r="E5" s="167" t="s">
         <v>220</v>
       </c>
-      <c r="F5" s="164"/>
-      <c r="G5" s="164"/>
-      <c r="H5" s="164"/>
-      <c r="I5" s="164"/>
-      <c r="J5" s="164"/>
-      <c r="K5" s="164"/>
-      <c r="L5" s="164"/>
-      <c r="M5" s="164"/>
-      <c r="N5" s="164"/>
-      <c r="O5" s="164"/>
+      <c r="F5" s="167"/>
+      <c r="G5" s="167"/>
+      <c r="H5" s="167"/>
+      <c r="I5" s="167"/>
+      <c r="J5" s="167"/>
+      <c r="K5" s="167"/>
+      <c r="L5" s="167"/>
+      <c r="M5" s="167"/>
+      <c r="N5" s="167"/>
+      <c r="O5" s="167"/>
     </row>
     <row r="6" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>221</v>
       </c>
-      <c r="E6" s="164" t="s">
+      <c r="E6" s="167" t="s">
         <v>220</v>
       </c>
-      <c r="F6" s="164"/>
-      <c r="G6" s="164"/>
-      <c r="H6" s="164"/>
-      <c r="I6" s="164"/>
-      <c r="J6" s="164"/>
-      <c r="K6" s="164"/>
-      <c r="L6" s="164"/>
-      <c r="M6" s="164"/>
-      <c r="N6" s="164"/>
-      <c r="O6" s="164"/>
+      <c r="F6" s="167"/>
+      <c r="G6" s="167"/>
+      <c r="H6" s="167"/>
+      <c r="I6" s="167"/>
+      <c r="J6" s="167"/>
+      <c r="K6" s="167"/>
+      <c r="L6" s="167"/>
+      <c r="M6" s="167"/>
+      <c r="N6" s="167"/>
+      <c r="O6" s="167"/>
     </row>
     <row r="7" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>222</v>
       </c>
-      <c r="E7" s="164" t="s">
+      <c r="E7" s="167" t="s">
         <v>220</v>
       </c>
-      <c r="F7" s="164"/>
-      <c r="G7" s="164"/>
-      <c r="H7" s="164"/>
-      <c r="I7" s="164"/>
-      <c r="J7" s="164"/>
-      <c r="K7" s="164"/>
-      <c r="L7" s="164"/>
-      <c r="M7" s="164"/>
-      <c r="N7" s="164"/>
-      <c r="O7" s="164"/>
+      <c r="F7" s="167"/>
+      <c r="G7" s="167"/>
+      <c r="H7" s="167"/>
+      <c r="I7" s="167"/>
+      <c r="J7" s="167"/>
+      <c r="K7" s="167"/>
+      <c r="L7" s="167"/>
+      <c r="M7" s="167"/>
+      <c r="N7" s="167"/>
+      <c r="O7" s="167"/>
     </row>
     <row r="8" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>223</v>
       </c>
-      <c r="E8" s="164" t="s">
+      <c r="E8" s="167" t="s">
         <v>220</v>
       </c>
-      <c r="F8" s="164"/>
-      <c r="G8" s="164"/>
-      <c r="H8" s="164"/>
-      <c r="I8" s="164"/>
-      <c r="J8" s="164"/>
-      <c r="K8" s="164"/>
-      <c r="L8" s="164"/>
-      <c r="M8" s="164"/>
-      <c r="N8" s="164"/>
-      <c r="O8" s="164"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="167"/>
+      <c r="H8" s="167"/>
+      <c r="I8" s="167"/>
+      <c r="J8" s="167"/>
+      <c r="K8" s="167"/>
+      <c r="L8" s="167"/>
+      <c r="M8" s="167"/>
+      <c r="N8" s="167"/>
+      <c r="O8" s="167"/>
     </row>
     <row r="9" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>224</v>
       </c>
-      <c r="E9" s="164" t="s">
+      <c r="E9" s="167" t="s">
         <v>220</v>
       </c>
-      <c r="F9" s="164"/>
-      <c r="G9" s="164"/>
-      <c r="H9" s="164"/>
-      <c r="I9" s="164"/>
-      <c r="J9" s="164"/>
-      <c r="K9" s="164"/>
-      <c r="L9" s="164"/>
-      <c r="M9" s="164"/>
-      <c r="N9" s="164"/>
-      <c r="O9" s="164"/>
+      <c r="F9" s="167"/>
+      <c r="G9" s="167"/>
+      <c r="H9" s="167"/>
+      <c r="I9" s="167"/>
+      <c r="J9" s="167"/>
+      <c r="K9" s="167"/>
+      <c r="L9" s="167"/>
+      <c r="M9" s="167"/>
+      <c r="N9" s="167"/>
+      <c r="O9" s="167"/>
     </row>
     <row r="10" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>225</v>
       </c>
-      <c r="E10" s="164" t="s">
+      <c r="E10" s="167" t="s">
         <v>226</v>
       </c>
-      <c r="F10" s="164"/>
-      <c r="G10" s="164"/>
-      <c r="H10" s="164"/>
-      <c r="I10" s="164"/>
-      <c r="J10" s="164"/>
-      <c r="K10" s="164"/>
-      <c r="L10" s="164"/>
-      <c r="M10" s="164"/>
-      <c r="N10" s="164"/>
-      <c r="O10" s="164"/>
+      <c r="F10" s="167"/>
+      <c r="G10" s="167"/>
+      <c r="H10" s="167"/>
+      <c r="I10" s="167"/>
+      <c r="J10" s="167"/>
+      <c r="K10" s="167"/>
+      <c r="L10" s="167"/>
+      <c r="M10" s="167"/>
+      <c r="N10" s="167"/>
+      <c r="O10" s="167"/>
     </row>
     <row r="14" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C14" s="163" t="s">
+      <c r="C14" s="143" t="s">
         <v>227</v>
       </c>
-      <c r="D14" s="163"/>
-      <c r="E14" s="163"/>
-      <c r="F14" s="163"/>
-      <c r="G14" s="163"/>
-      <c r="H14" s="163"/>
-      <c r="I14" s="163"/>
-      <c r="J14" s="163"/>
-      <c r="K14" s="163"/>
-      <c r="L14" s="163"/>
-      <c r="M14" s="163"/>
-      <c r="N14" s="163"/>
-      <c r="O14" s="163"/>
+      <c r="D14" s="143"/>
+      <c r="E14" s="143"/>
+      <c r="F14" s="143"/>
+      <c r="G14" s="143"/>
+      <c r="H14" s="143"/>
+      <c r="I14" s="143"/>
+      <c r="J14" s="143"/>
+      <c r="K14" s="143"/>
+      <c r="L14" s="143"/>
+      <c r="M14" s="143"/>
+      <c r="N14" s="143"/>
+      <c r="O14" s="143"/>
     </row>
     <row r="15" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C15" s="163"/>
-      <c r="D15" s="163"/>
-      <c r="E15" s="163"/>
-      <c r="F15" s="163"/>
-      <c r="G15" s="163"/>
-      <c r="H15" s="163"/>
-      <c r="I15" s="163"/>
-      <c r="J15" s="163"/>
-      <c r="K15" s="163"/>
-      <c r="L15" s="163"/>
-      <c r="M15" s="163"/>
-      <c r="N15" s="163"/>
-      <c r="O15" s="163"/>
+      <c r="C15" s="143"/>
+      <c r="D15" s="143"/>
+      <c r="E15" s="143"/>
+      <c r="F15" s="143"/>
+      <c r="G15" s="143"/>
+      <c r="H15" s="143"/>
+      <c r="I15" s="143"/>
+      <c r="J15" s="143"/>
+      <c r="K15" s="143"/>
+      <c r="L15" s="143"/>
+      <c r="M15" s="143"/>
+      <c r="N15" s="143"/>
+      <c r="O15" s="143"/>
     </row>
     <row r="17" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>228</v>
       </c>
-      <c r="E17" s="164" t="s">
+      <c r="E17" s="167" t="s">
         <v>229</v>
       </c>
-      <c r="F17" s="164"/>
-      <c r="G17" s="164"/>
-      <c r="H17" s="164"/>
-      <c r="I17" s="164"/>
-      <c r="J17" s="164"/>
-      <c r="K17" s="164"/>
-      <c r="L17" s="164"/>
-      <c r="M17" s="164"/>
-      <c r="N17" s="164"/>
-      <c r="O17" s="164"/>
+      <c r="F17" s="167"/>
+      <c r="G17" s="167"/>
+      <c r="H17" s="167"/>
+      <c r="I17" s="167"/>
+      <c r="J17" s="167"/>
+      <c r="K17" s="167"/>
+      <c r="L17" s="167"/>
+      <c r="M17" s="167"/>
+      <c r="N17" s="167"/>
+      <c r="O17" s="167"/>
     </row>
     <row r="18" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>230</v>
       </c>
-      <c r="E18" s="164" t="s">
+      <c r="E18" s="167" t="s">
         <v>231</v>
       </c>
-      <c r="F18" s="164"/>
-      <c r="G18" s="164"/>
-      <c r="H18" s="164"/>
-      <c r="I18" s="164"/>
-      <c r="J18" s="164"/>
-      <c r="K18" s="164"/>
-      <c r="L18" s="164"/>
-      <c r="M18" s="164"/>
-      <c r="N18" s="164"/>
-      <c r="O18" s="164"/>
+      <c r="F18" s="167"/>
+      <c r="G18" s="167"/>
+      <c r="H18" s="167"/>
+      <c r="I18" s="167"/>
+      <c r="J18" s="167"/>
+      <c r="K18" s="167"/>
+      <c r="L18" s="167"/>
+      <c r="M18" s="167"/>
+      <c r="N18" s="167"/>
+      <c r="O18" s="167"/>
     </row>
     <row r="19" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>232</v>
       </c>
-      <c r="E19" s="164" t="s">
+      <c r="E19" s="167" t="s">
         <v>233</v>
       </c>
-      <c r="F19" s="164"/>
-      <c r="G19" s="164"/>
-      <c r="H19" s="164"/>
-      <c r="I19" s="164"/>
-      <c r="J19" s="164"/>
-      <c r="K19" s="164"/>
-      <c r="L19" s="164"/>
-      <c r="M19" s="164"/>
-      <c r="N19" s="164"/>
-      <c r="O19" s="164"/>
+      <c r="F19" s="167"/>
+      <c r="G19" s="167"/>
+      <c r="H19" s="167"/>
+      <c r="I19" s="167"/>
+      <c r="J19" s="167"/>
+      <c r="K19" s="167"/>
+      <c r="L19" s="167"/>
+      <c r="M19" s="167"/>
+      <c r="N19" s="167"/>
+      <c r="O19" s="167"/>
     </row>
     <row r="20" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>234</v>
       </c>
-      <c r="E20" s="164" t="s">
+      <c r="E20" s="167" t="s">
         <v>235</v>
       </c>
-      <c r="F20" s="164"/>
-      <c r="G20" s="164"/>
-      <c r="H20" s="164"/>
-      <c r="I20" s="164"/>
-      <c r="J20" s="164"/>
-      <c r="K20" s="164"/>
-      <c r="L20" s="164"/>
-      <c r="M20" s="164"/>
-      <c r="N20" s="164"/>
-      <c r="O20" s="164"/>
+      <c r="F20" s="167"/>
+      <c r="G20" s="167"/>
+      <c r="H20" s="167"/>
+      <c r="I20" s="167"/>
+      <c r="J20" s="167"/>
+      <c r="K20" s="167"/>
+      <c r="L20" s="167"/>
+      <c r="M20" s="167"/>
+      <c r="N20" s="167"/>
+      <c r="O20" s="167"/>
     </row>
     <row r="21" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>236</v>
       </c>
-      <c r="E21" s="164" t="s">
+      <c r="E21" s="167" t="s">
         <v>237</v>
       </c>
-      <c r="F21" s="164"/>
-      <c r="G21" s="164"/>
-      <c r="H21" s="164"/>
-      <c r="I21" s="164"/>
-      <c r="J21" s="164"/>
-      <c r="K21" s="164"/>
-      <c r="L21" s="164"/>
-      <c r="M21" s="164"/>
-      <c r="N21" s="164"/>
-      <c r="O21" s="164"/>
+      <c r="F21" s="167"/>
+      <c r="G21" s="167"/>
+      <c r="H21" s="167"/>
+      <c r="I21" s="167"/>
+      <c r="J21" s="167"/>
+      <c r="K21" s="167"/>
+      <c r="L21" s="167"/>
+      <c r="M21" s="167"/>
+      <c r="N21" s="167"/>
+      <c r="O21" s="167"/>
     </row>
     <row r="22" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>238</v>
       </c>
-      <c r="E22" s="164" t="s">
+      <c r="E22" s="167" t="s">
         <v>239</v>
       </c>
-      <c r="F22" s="164"/>
-      <c r="G22" s="164"/>
-      <c r="H22" s="164"/>
-      <c r="I22" s="164"/>
-      <c r="J22" s="164"/>
-      <c r="K22" s="164"/>
-      <c r="L22" s="164"/>
-      <c r="M22" s="164"/>
-      <c r="N22" s="164"/>
-      <c r="O22" s="164"/>
+      <c r="F22" s="167"/>
+      <c r="G22" s="167"/>
+      <c r="H22" s="167"/>
+      <c r="I22" s="167"/>
+      <c r="J22" s="167"/>
+      <c r="K22" s="167"/>
+      <c r="L22" s="167"/>
+      <c r="M22" s="167"/>
+      <c r="N22" s="167"/>
+      <c r="O22" s="167"/>
     </row>
     <row r="23" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>240</v>
       </c>
-      <c r="E23" s="164" t="s">
+      <c r="E23" s="167" t="s">
         <v>241</v>
       </c>
-      <c r="F23" s="164"/>
-      <c r="G23" s="164"/>
-      <c r="H23" s="164"/>
-      <c r="I23" s="164"/>
-      <c r="J23" s="164"/>
-      <c r="K23" s="164"/>
-      <c r="L23" s="164"/>
-      <c r="M23" s="164"/>
-      <c r="N23" s="164"/>
-      <c r="O23" s="164"/>
+      <c r="F23" s="167"/>
+      <c r="G23" s="167"/>
+      <c r="H23" s="167"/>
+      <c r="I23" s="167"/>
+      <c r="J23" s="167"/>
+      <c r="K23" s="167"/>
+      <c r="L23" s="167"/>
+      <c r="M23" s="167"/>
+      <c r="N23" s="167"/>
+      <c r="O23" s="167"/>
     </row>
     <row r="24" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
         <v>242</v>
       </c>
-      <c r="E24" s="164" t="s">
+      <c r="E24" s="167" t="s">
         <v>243</v>
       </c>
-      <c r="F24" s="164"/>
-      <c r="G24" s="164"/>
-      <c r="H24" s="164"/>
-      <c r="I24" s="164"/>
-      <c r="J24" s="164"/>
-      <c r="K24" s="164"/>
-      <c r="L24" s="164"/>
-      <c r="M24" s="164"/>
-      <c r="N24" s="164"/>
-      <c r="O24" s="164"/>
+      <c r="F24" s="167"/>
+      <c r="G24" s="167"/>
+      <c r="H24" s="167"/>
+      <c r="I24" s="167"/>
+      <c r="J24" s="167"/>
+      <c r="K24" s="167"/>
+      <c r="L24" s="167"/>
+      <c r="M24" s="167"/>
+      <c r="N24" s="167"/>
+      <c r="O24" s="167"/>
     </row>
     <row r="25" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
         <v>244</v>
       </c>
-      <c r="E25" s="164" t="s">
+      <c r="E25" s="167" t="s">
         <v>245</v>
       </c>
-      <c r="F25" s="164"/>
-      <c r="G25" s="164"/>
-      <c r="H25" s="164"/>
-      <c r="I25" s="164"/>
-      <c r="J25" s="164"/>
-      <c r="K25" s="164"/>
-      <c r="L25" s="164"/>
-      <c r="M25" s="164"/>
-      <c r="N25" s="164"/>
-      <c r="O25" s="164"/>
+      <c r="F25" s="167"/>
+      <c r="G25" s="167"/>
+      <c r="H25" s="167"/>
+      <c r="I25" s="167"/>
+      <c r="J25" s="167"/>
+      <c r="K25" s="167"/>
+      <c r="L25" s="167"/>
+      <c r="M25" s="167"/>
+      <c r="N25" s="167"/>
+      <c r="O25" s="167"/>
     </row>
     <row r="26" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>246</v>
       </c>
-      <c r="E26" s="164" t="s">
+      <c r="E26" s="167" t="s">
         <v>247</v>
       </c>
-      <c r="F26" s="164"/>
-      <c r="G26" s="164"/>
-      <c r="H26" s="164"/>
-      <c r="I26" s="164"/>
-      <c r="J26" s="164"/>
-      <c r="K26" s="164"/>
-      <c r="L26" s="164"/>
-      <c r="M26" s="164"/>
-      <c r="N26" s="164"/>
-      <c r="O26" s="164"/>
+      <c r="F26" s="167"/>
+      <c r="G26" s="167"/>
+      <c r="H26" s="167"/>
+      <c r="I26" s="167"/>
+      <c r="J26" s="167"/>
+      <c r="K26" s="167"/>
+      <c r="L26" s="167"/>
+      <c r="M26" s="167"/>
+      <c r="N26" s="167"/>
+      <c r="O26" s="167"/>
     </row>
     <row r="27" spans="3:15" x14ac:dyDescent="0.25">
       <c r="E27" s="3"/>
@@ -23815,273 +23815,289 @@
       <c r="O28" s="3"/>
     </row>
     <row r="30" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C30" s="163" t="s">
+      <c r="C30" s="143" t="s">
         <v>248</v>
       </c>
-      <c r="D30" s="163"/>
-      <c r="E30" s="163"/>
-      <c r="F30" s="163"/>
-      <c r="G30" s="163"/>
-      <c r="H30" s="163"/>
-      <c r="I30" s="163"/>
-      <c r="J30" s="163"/>
-      <c r="K30" s="163"/>
-      <c r="L30" s="163"/>
-      <c r="M30" s="163"/>
-      <c r="N30" s="163"/>
-      <c r="O30" s="163"/>
+      <c r="D30" s="143"/>
+      <c r="E30" s="143"/>
+      <c r="F30" s="143"/>
+      <c r="G30" s="143"/>
+      <c r="H30" s="143"/>
+      <c r="I30" s="143"/>
+      <c r="J30" s="143"/>
+      <c r="K30" s="143"/>
+      <c r="L30" s="143"/>
+      <c r="M30" s="143"/>
+      <c r="N30" s="143"/>
+      <c r="O30" s="143"/>
     </row>
     <row r="31" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C31" s="163"/>
-      <c r="D31" s="163"/>
-      <c r="E31" s="163"/>
-      <c r="F31" s="163"/>
-      <c r="G31" s="163"/>
-      <c r="H31" s="163"/>
-      <c r="I31" s="163"/>
-      <c r="J31" s="163"/>
-      <c r="K31" s="163"/>
-      <c r="L31" s="163"/>
-      <c r="M31" s="163"/>
-      <c r="N31" s="163"/>
-      <c r="O31" s="163"/>
+      <c r="C31" s="143"/>
+      <c r="D31" s="143"/>
+      <c r="E31" s="143"/>
+      <c r="F31" s="143"/>
+      <c r="G31" s="143"/>
+      <c r="H31" s="143"/>
+      <c r="I31" s="143"/>
+      <c r="J31" s="143"/>
+      <c r="K31" s="143"/>
+      <c r="L31" s="143"/>
+      <c r="M31" s="143"/>
+      <c r="N31" s="143"/>
+      <c r="O31" s="143"/>
     </row>
     <row r="33" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
         <v>249</v>
       </c>
-      <c r="E33" s="164" t="s">
+      <c r="E33" s="167" t="s">
         <v>250</v>
       </c>
-      <c r="F33" s="164"/>
-      <c r="G33" s="164"/>
-      <c r="H33" s="164"/>
-      <c r="I33" s="164"/>
-      <c r="J33" s="164"/>
-      <c r="K33" s="164"/>
-      <c r="L33" s="164"/>
-      <c r="M33" s="164"/>
-      <c r="N33" s="164"/>
-      <c r="O33" s="164"/>
+      <c r="F33" s="167"/>
+      <c r="G33" s="167"/>
+      <c r="H33" s="167"/>
+      <c r="I33" s="167"/>
+      <c r="J33" s="167"/>
+      <c r="K33" s="167"/>
+      <c r="L33" s="167"/>
+      <c r="M33" s="167"/>
+      <c r="N33" s="167"/>
+      <c r="O33" s="167"/>
     </row>
     <row r="34" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
         <v>251</v>
       </c>
-      <c r="E34" s="164" t="s">
+      <c r="E34" s="167" t="s">
         <v>252</v>
       </c>
-      <c r="F34" s="164"/>
-      <c r="G34" s="164"/>
-      <c r="H34" s="164"/>
-      <c r="I34" s="164"/>
-      <c r="J34" s="164"/>
-      <c r="K34" s="164"/>
-      <c r="L34" s="164"/>
-      <c r="M34" s="164"/>
-      <c r="N34" s="164"/>
-      <c r="O34" s="164"/>
+      <c r="F34" s="167"/>
+      <c r="G34" s="167"/>
+      <c r="H34" s="167"/>
+      <c r="I34" s="167"/>
+      <c r="J34" s="167"/>
+      <c r="K34" s="167"/>
+      <c r="L34" s="167"/>
+      <c r="M34" s="167"/>
+      <c r="N34" s="167"/>
+      <c r="O34" s="167"/>
     </row>
     <row r="35" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
         <v>253</v>
       </c>
-      <c r="E35" s="164" t="s">
+      <c r="E35" s="167" t="s">
         <v>254</v>
       </c>
-      <c r="F35" s="164"/>
-      <c r="G35" s="164"/>
-      <c r="H35" s="164"/>
-      <c r="I35" s="164"/>
-      <c r="J35" s="164"/>
-      <c r="K35" s="164"/>
-      <c r="L35" s="164"/>
-      <c r="M35" s="164"/>
-      <c r="N35" s="164"/>
-      <c r="O35" s="164"/>
+      <c r="F35" s="167"/>
+      <c r="G35" s="167"/>
+      <c r="H35" s="167"/>
+      <c r="I35" s="167"/>
+      <c r="J35" s="167"/>
+      <c r="K35" s="167"/>
+      <c r="L35" s="167"/>
+      <c r="M35" s="167"/>
+      <c r="N35" s="167"/>
+      <c r="O35" s="167"/>
     </row>
     <row r="36" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
         <v>255</v>
       </c>
-      <c r="E36" s="164" t="s">
+      <c r="E36" s="167" t="s">
         <v>256</v>
       </c>
-      <c r="F36" s="164"/>
-      <c r="G36" s="164"/>
-      <c r="H36" s="164"/>
-      <c r="I36" s="164"/>
-      <c r="J36" s="164"/>
-      <c r="K36" s="164"/>
-      <c r="L36" s="164"/>
-      <c r="M36" s="164"/>
-      <c r="N36" s="164"/>
-      <c r="O36" s="164"/>
+      <c r="F36" s="167"/>
+      <c r="G36" s="167"/>
+      <c r="H36" s="167"/>
+      <c r="I36" s="167"/>
+      <c r="J36" s="167"/>
+      <c r="K36" s="167"/>
+      <c r="L36" s="167"/>
+      <c r="M36" s="167"/>
+      <c r="N36" s="167"/>
+      <c r="O36" s="167"/>
     </row>
     <row r="37" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
         <v>257</v>
       </c>
-      <c r="E37" s="164" t="s">
+      <c r="E37" s="167" t="s">
         <v>258</v>
       </c>
-      <c r="F37" s="164"/>
-      <c r="G37" s="164"/>
-      <c r="H37" s="164"/>
-      <c r="I37" s="164"/>
-      <c r="J37" s="164"/>
-      <c r="K37" s="164"/>
-      <c r="L37" s="164"/>
-      <c r="M37" s="164"/>
-      <c r="N37" s="164"/>
-      <c r="O37" s="164"/>
+      <c r="F37" s="167"/>
+      <c r="G37" s="167"/>
+      <c r="H37" s="167"/>
+      <c r="I37" s="167"/>
+      <c r="J37" s="167"/>
+      <c r="K37" s="167"/>
+      <c r="L37" s="167"/>
+      <c r="M37" s="167"/>
+      <c r="N37" s="167"/>
+      <c r="O37" s="167"/>
     </row>
     <row r="39" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
         <v>259</v>
       </c>
-      <c r="E39" s="164" t="s">
+      <c r="E39" s="167" t="s">
         <v>260</v>
       </c>
-      <c r="F39" s="164"/>
-      <c r="G39" s="164"/>
-      <c r="H39" s="164"/>
-      <c r="I39" s="164"/>
-      <c r="J39" s="164"/>
-      <c r="K39" s="164"/>
-      <c r="L39" s="164"/>
-      <c r="M39" s="164"/>
-      <c r="N39" s="164"/>
-      <c r="O39" s="164"/>
+      <c r="F39" s="167"/>
+      <c r="G39" s="167"/>
+      <c r="H39" s="167"/>
+      <c r="I39" s="167"/>
+      <c r="J39" s="167"/>
+      <c r="K39" s="167"/>
+      <c r="L39" s="167"/>
+      <c r="M39" s="167"/>
+      <c r="N39" s="167"/>
+      <c r="O39" s="167"/>
     </row>
     <row r="40" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>261</v>
       </c>
-      <c r="E40" s="164" t="s">
+      <c r="E40" s="167" t="s">
         <v>262</v>
       </c>
-      <c r="F40" s="164"/>
-      <c r="G40" s="164"/>
-      <c r="H40" s="164"/>
-      <c r="I40" s="164"/>
-      <c r="J40" s="164"/>
-      <c r="K40" s="164"/>
-      <c r="L40" s="164"/>
-      <c r="M40" s="164"/>
-      <c r="N40" s="164"/>
-      <c r="O40" s="164"/>
+      <c r="F40" s="167"/>
+      <c r="G40" s="167"/>
+      <c r="H40" s="167"/>
+      <c r="I40" s="167"/>
+      <c r="J40" s="167"/>
+      <c r="K40" s="167"/>
+      <c r="L40" s="167"/>
+      <c r="M40" s="167"/>
+      <c r="N40" s="167"/>
+      <c r="O40" s="167"/>
     </row>
     <row r="41" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
         <v>263</v>
       </c>
-      <c r="E41" s="164" t="s">
+      <c r="E41" s="167" t="s">
         <v>264</v>
       </c>
-      <c r="F41" s="164"/>
-      <c r="G41" s="164"/>
-      <c r="H41" s="164"/>
-      <c r="I41" s="164"/>
-      <c r="J41" s="164"/>
-      <c r="K41" s="164"/>
-      <c r="L41" s="164"/>
-      <c r="M41" s="164"/>
-      <c r="N41" s="164"/>
-      <c r="O41" s="164"/>
+      <c r="F41" s="167"/>
+      <c r="G41" s="167"/>
+      <c r="H41" s="167"/>
+      <c r="I41" s="167"/>
+      <c r="J41" s="167"/>
+      <c r="K41" s="167"/>
+      <c r="L41" s="167"/>
+      <c r="M41" s="167"/>
+      <c r="N41" s="167"/>
+      <c r="O41" s="167"/>
     </row>
     <row r="42" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>265</v>
       </c>
-      <c r="E42" s="164" t="s">
+      <c r="E42" s="167" t="s">
         <v>266</v>
       </c>
-      <c r="F42" s="164"/>
-      <c r="G42" s="164"/>
-      <c r="H42" s="164"/>
-      <c r="I42" s="164"/>
-      <c r="J42" s="164"/>
-      <c r="K42" s="164"/>
-      <c r="L42" s="164"/>
-      <c r="M42" s="164"/>
-      <c r="N42" s="164"/>
-      <c r="O42" s="164"/>
+      <c r="F42" s="167"/>
+      <c r="G42" s="167"/>
+      <c r="H42" s="167"/>
+      <c r="I42" s="167"/>
+      <c r="J42" s="167"/>
+      <c r="K42" s="167"/>
+      <c r="L42" s="167"/>
+      <c r="M42" s="167"/>
+      <c r="N42" s="167"/>
+      <c r="O42" s="167"/>
     </row>
     <row r="44" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
         <v>267</v>
       </c>
-      <c r="E44" s="164" t="s">
+      <c r="E44" s="167" t="s">
         <v>268</v>
       </c>
-      <c r="F44" s="164"/>
-      <c r="G44" s="164"/>
-      <c r="H44" s="164"/>
-      <c r="I44" s="164"/>
-      <c r="J44" s="164"/>
-      <c r="K44" s="164"/>
-      <c r="L44" s="164"/>
-      <c r="M44" s="164"/>
-      <c r="N44" s="164"/>
-      <c r="O44" s="164"/>
+      <c r="F44" s="167"/>
+      <c r="G44" s="167"/>
+      <c r="H44" s="167"/>
+      <c r="I44" s="167"/>
+      <c r="J44" s="167"/>
+      <c r="K44" s="167"/>
+      <c r="L44" s="167"/>
+      <c r="M44" s="167"/>
+      <c r="N44" s="167"/>
+      <c r="O44" s="167"/>
     </row>
     <row r="45" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
         <v>269</v>
       </c>
-      <c r="E45" s="164" t="s">
+      <c r="E45" s="167" t="s">
         <v>270</v>
       </c>
-      <c r="F45" s="164"/>
-      <c r="G45" s="164"/>
-      <c r="H45" s="164"/>
-      <c r="I45" s="164"/>
-      <c r="J45" s="164"/>
-      <c r="K45" s="164"/>
-      <c r="L45" s="164"/>
-      <c r="M45" s="164"/>
-      <c r="N45" s="164"/>
-      <c r="O45" s="164"/>
+      <c r="F45" s="167"/>
+      <c r="G45" s="167"/>
+      <c r="H45" s="167"/>
+      <c r="I45" s="167"/>
+      <c r="J45" s="167"/>
+      <c r="K45" s="167"/>
+      <c r="L45" s="167"/>
+      <c r="M45" s="167"/>
+      <c r="N45" s="167"/>
+      <c r="O45" s="167"/>
     </row>
     <row r="46" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C46" t="s">
         <v>271</v>
       </c>
-      <c r="E46" s="164" t="s">
+      <c r="E46" s="167" t="s">
         <v>272</v>
       </c>
-      <c r="F46" s="164"/>
-      <c r="G46" s="164"/>
-      <c r="H46" s="164"/>
-      <c r="I46" s="164"/>
-      <c r="J46" s="164"/>
-      <c r="K46" s="164"/>
-      <c r="L46" s="164"/>
-      <c r="M46" s="164"/>
-      <c r="N46" s="164"/>
-      <c r="O46" s="164"/>
+      <c r="F46" s="167"/>
+      <c r="G46" s="167"/>
+      <c r="H46" s="167"/>
+      <c r="I46" s="167"/>
+      <c r="J46" s="167"/>
+      <c r="K46" s="167"/>
+      <c r="L46" s="167"/>
+      <c r="M46" s="167"/>
+      <c r="N46" s="167"/>
+      <c r="O46" s="167"/>
     </row>
     <row r="47" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
         <v>273</v>
       </c>
-      <c r="E47" s="164" t="s">
+      <c r="E47" s="167" t="s">
         <v>274</v>
       </c>
-      <c r="F47" s="164"/>
-      <c r="G47" s="164"/>
-      <c r="H47" s="164"/>
-      <c r="I47" s="164"/>
-      <c r="J47" s="164"/>
-      <c r="K47" s="164"/>
-      <c r="L47" s="164"/>
-      <c r="M47" s="164"/>
-      <c r="N47" s="164"/>
-      <c r="O47" s="164"/>
+      <c r="F47" s="167"/>
+      <c r="G47" s="167"/>
+      <c r="H47" s="167"/>
+      <c r="I47" s="167"/>
+      <c r="J47" s="167"/>
+      <c r="K47" s="167"/>
+      <c r="L47" s="167"/>
+      <c r="M47" s="167"/>
+      <c r="N47" s="167"/>
+      <c r="O47" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="E5:O5"/>
+    <mergeCell ref="E6:O6"/>
+    <mergeCell ref="E7:O7"/>
+    <mergeCell ref="E8:O8"/>
+    <mergeCell ref="E9:O9"/>
+    <mergeCell ref="E10:O10"/>
+    <mergeCell ref="E17:O17"/>
+    <mergeCell ref="E18:O18"/>
+    <mergeCell ref="E19:O19"/>
+    <mergeCell ref="E20:O20"/>
+    <mergeCell ref="E36:O36"/>
+    <mergeCell ref="E21:O21"/>
+    <mergeCell ref="E22:O22"/>
+    <mergeCell ref="E23:O23"/>
+    <mergeCell ref="E24:O24"/>
+    <mergeCell ref="E25:O25"/>
     <mergeCell ref="E44:O44"/>
     <mergeCell ref="E45:O45"/>
     <mergeCell ref="E46:O46"/>
@@ -24098,22 +24114,6 @@
     <mergeCell ref="E33:O33"/>
     <mergeCell ref="E34:O34"/>
     <mergeCell ref="E35:O35"/>
-    <mergeCell ref="E36:O36"/>
-    <mergeCell ref="E21:O21"/>
-    <mergeCell ref="E22:O22"/>
-    <mergeCell ref="E23:O23"/>
-    <mergeCell ref="E24:O24"/>
-    <mergeCell ref="E25:O25"/>
-    <mergeCell ref="E10:O10"/>
-    <mergeCell ref="E17:O17"/>
-    <mergeCell ref="E18:O18"/>
-    <mergeCell ref="E19:O19"/>
-    <mergeCell ref="E20:O20"/>
-    <mergeCell ref="E5:O5"/>
-    <mergeCell ref="E6:O6"/>
-    <mergeCell ref="E7:O7"/>
-    <mergeCell ref="E8:O8"/>
-    <mergeCell ref="E9:O9"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24130,20 +24130,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C2" s="165" t="s">
+      <c r="C2" s="168" t="s">
         <v>275</v>
       </c>
-      <c r="D2" s="166"/>
-      <c r="E2" s="166"/>
-      <c r="F2" s="166"/>
-      <c r="G2" s="167"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="170"/>
     </row>
     <row r="3" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C3" s="168"/>
-      <c r="D3" s="169"/>
-      <c r="E3" s="169"/>
-      <c r="F3" s="169"/>
-      <c r="G3" s="170"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="173"/>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
@@ -24421,36 +24421,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="D2" s="163" t="s">
+      <c r="D2" s="143" t="s">
         <v>322</v>
       </c>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="163"/>
-      <c r="L2" s="163"/>
-      <c r="M2" s="163"/>
-      <c r="N2" s="163"/>
-      <c r="O2" s="163"/>
-      <c r="P2" s="163"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
+      <c r="K2" s="143"/>
+      <c r="L2" s="143"/>
+      <c r="M2" s="143"/>
+      <c r="N2" s="143"/>
+      <c r="O2" s="143"/>
+      <c r="P2" s="143"/>
     </row>
     <row r="3" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="163"/>
-      <c r="K3" s="163"/>
-      <c r="L3" s="163"/>
-      <c r="M3" s="163"/>
-      <c r="N3" s="163"/>
-      <c r="O3" s="163"/>
-      <c r="P3" s="163"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="143"/>
+      <c r="I3" s="143"/>
+      <c r="J3" s="143"/>
+      <c r="K3" s="143"/>
+      <c r="L3" s="143"/>
+      <c r="M3" s="143"/>
+      <c r="N3" s="143"/>
+      <c r="O3" s="143"/>
+      <c r="P3" s="143"/>
     </row>
     <row r="6" spans="4:16" x14ac:dyDescent="0.25">
       <c r="L6" t="s">
@@ -24628,248 +24628,248 @@
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="13" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E13" s="141" t="s">
+      <c r="E13" s="145" t="s">
         <v>350</v>
       </c>
-      <c r="F13" s="141"/>
-      <c r="G13" s="141"/>
-      <c r="H13" s="141"/>
-      <c r="I13" s="141"/>
-      <c r="J13" s="141"/>
-      <c r="K13" s="141"/>
-      <c r="L13" s="141"/>
-      <c r="M13" s="141"/>
-      <c r="N13" s="141"/>
-      <c r="O13" s="141"/>
-      <c r="P13" s="141"/>
-      <c r="Q13" s="141"/>
+      <c r="F13" s="145"/>
+      <c r="G13" s="145"/>
+      <c r="H13" s="145"/>
+      <c r="I13" s="145"/>
+      <c r="J13" s="145"/>
+      <c r="K13" s="145"/>
+      <c r="L13" s="145"/>
+      <c r="M13" s="145"/>
+      <c r="N13" s="145"/>
+      <c r="O13" s="145"/>
+      <c r="P13" s="145"/>
+      <c r="Q13" s="145"/>
     </row>
     <row r="14" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E14" s="141"/>
-      <c r="F14" s="141"/>
-      <c r="G14" s="141"/>
-      <c r="H14" s="141"/>
-      <c r="I14" s="141"/>
-      <c r="J14" s="141"/>
-      <c r="K14" s="141"/>
-      <c r="L14" s="141"/>
-      <c r="M14" s="141"/>
-      <c r="N14" s="141"/>
-      <c r="O14" s="141"/>
-      <c r="P14" s="141"/>
-      <c r="Q14" s="141"/>
+      <c r="E14" s="145"/>
+      <c r="F14" s="145"/>
+      <c r="G14" s="145"/>
+      <c r="H14" s="145"/>
+      <c r="I14" s="145"/>
+      <c r="J14" s="145"/>
+      <c r="K14" s="145"/>
+      <c r="L14" s="145"/>
+      <c r="M14" s="145"/>
+      <c r="N14" s="145"/>
+      <c r="O14" s="145"/>
+      <c r="P14" s="145"/>
+      <c r="Q14" s="145"/>
     </row>
     <row r="15" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E15" s="141"/>
-      <c r="F15" s="141"/>
-      <c r="G15" s="141"/>
-      <c r="H15" s="141"/>
-      <c r="I15" s="141"/>
-      <c r="J15" s="141"/>
-      <c r="K15" s="141"/>
-      <c r="L15" s="141"/>
-      <c r="M15" s="141"/>
-      <c r="N15" s="141"/>
-      <c r="O15" s="141"/>
-      <c r="P15" s="141"/>
-      <c r="Q15" s="141"/>
+      <c r="E15" s="145"/>
+      <c r="F15" s="145"/>
+      <c r="G15" s="145"/>
+      <c r="H15" s="145"/>
+      <c r="I15" s="145"/>
+      <c r="J15" s="145"/>
+      <c r="K15" s="145"/>
+      <c r="L15" s="145"/>
+      <c r="M15" s="145"/>
+      <c r="N15" s="145"/>
+      <c r="O15" s="145"/>
+      <c r="P15" s="145"/>
+      <c r="Q15" s="145"/>
     </row>
     <row r="16" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E16" s="141"/>
-      <c r="F16" s="141"/>
-      <c r="G16" s="141"/>
-      <c r="H16" s="141"/>
-      <c r="I16" s="141"/>
-      <c r="J16" s="141"/>
-      <c r="K16" s="141"/>
-      <c r="L16" s="141"/>
-      <c r="M16" s="141"/>
-      <c r="N16" s="141"/>
-      <c r="O16" s="141"/>
-      <c r="P16" s="141"/>
-      <c r="Q16" s="141"/>
+      <c r="E16" s="145"/>
+      <c r="F16" s="145"/>
+      <c r="G16" s="145"/>
+      <c r="H16" s="145"/>
+      <c r="I16" s="145"/>
+      <c r="J16" s="145"/>
+      <c r="K16" s="145"/>
+      <c r="L16" s="145"/>
+      <c r="M16" s="145"/>
+      <c r="N16" s="145"/>
+      <c r="O16" s="145"/>
+      <c r="P16" s="145"/>
+      <c r="Q16" s="145"/>
     </row>
     <row r="17" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E17" s="141"/>
-      <c r="F17" s="141"/>
-      <c r="G17" s="141"/>
-      <c r="H17" s="141"/>
-      <c r="I17" s="141"/>
-      <c r="J17" s="141"/>
-      <c r="K17" s="141"/>
-      <c r="L17" s="141"/>
-      <c r="M17" s="141"/>
-      <c r="N17" s="141"/>
-      <c r="O17" s="141"/>
-      <c r="P17" s="141"/>
-      <c r="Q17" s="141"/>
+      <c r="E17" s="145"/>
+      <c r="F17" s="145"/>
+      <c r="G17" s="145"/>
+      <c r="H17" s="145"/>
+      <c r="I17" s="145"/>
+      <c r="J17" s="145"/>
+      <c r="K17" s="145"/>
+      <c r="L17" s="145"/>
+      <c r="M17" s="145"/>
+      <c r="N17" s="145"/>
+      <c r="O17" s="145"/>
+      <c r="P17" s="145"/>
+      <c r="Q17" s="145"/>
     </row>
     <row r="18" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E18" s="141"/>
-      <c r="F18" s="141"/>
-      <c r="G18" s="141"/>
-      <c r="H18" s="141"/>
-      <c r="I18" s="141"/>
-      <c r="J18" s="141"/>
-      <c r="K18" s="141"/>
-      <c r="L18" s="141"/>
-      <c r="M18" s="141"/>
-      <c r="N18" s="141"/>
-      <c r="O18" s="141"/>
-      <c r="P18" s="141"/>
-      <c r="Q18" s="141"/>
+      <c r="E18" s="145"/>
+      <c r="F18" s="145"/>
+      <c r="G18" s="145"/>
+      <c r="H18" s="145"/>
+      <c r="I18" s="145"/>
+      <c r="J18" s="145"/>
+      <c r="K18" s="145"/>
+      <c r="L18" s="145"/>
+      <c r="M18" s="145"/>
+      <c r="N18" s="145"/>
+      <c r="O18" s="145"/>
+      <c r="P18" s="145"/>
+      <c r="Q18" s="145"/>
     </row>
     <row r="19" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E19" s="141"/>
-      <c r="F19" s="141"/>
-      <c r="G19" s="141"/>
-      <c r="H19" s="141"/>
-      <c r="I19" s="141"/>
-      <c r="J19" s="141"/>
-      <c r="K19" s="141"/>
-      <c r="L19" s="141"/>
-      <c r="M19" s="141"/>
-      <c r="N19" s="141"/>
-      <c r="O19" s="141"/>
-      <c r="P19" s="141"/>
-      <c r="Q19" s="141"/>
+      <c r="E19" s="145"/>
+      <c r="F19" s="145"/>
+      <c r="G19" s="145"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="145"/>
+      <c r="N19" s="145"/>
+      <c r="O19" s="145"/>
+      <c r="P19" s="145"/>
+      <c r="Q19" s="145"/>
     </row>
     <row r="20" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E20" s="141"/>
-      <c r="F20" s="141"/>
-      <c r="G20" s="141"/>
-      <c r="H20" s="141"/>
-      <c r="I20" s="141"/>
-      <c r="J20" s="141"/>
-      <c r="K20" s="141"/>
-      <c r="L20" s="141"/>
-      <c r="M20" s="141"/>
-      <c r="N20" s="141"/>
-      <c r="O20" s="141"/>
-      <c r="P20" s="141"/>
-      <c r="Q20" s="141"/>
+      <c r="E20" s="145"/>
+      <c r="F20" s="145"/>
+      <c r="G20" s="145"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="145"/>
+      <c r="O20" s="145"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="145"/>
     </row>
     <row r="23" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E23" s="141" t="s">
+      <c r="E23" s="145" t="s">
         <v>351</v>
       </c>
-      <c r="F23" s="141"/>
-      <c r="G23" s="141"/>
-      <c r="H23" s="141"/>
-      <c r="I23" s="141"/>
-      <c r="J23" s="141"/>
-      <c r="K23" s="141"/>
-      <c r="L23" s="141"/>
-      <c r="M23" s="141"/>
-      <c r="N23" s="141"/>
-      <c r="O23" s="141"/>
-      <c r="P23" s="141"/>
-      <c r="Q23" s="141"/>
+      <c r="F23" s="145"/>
+      <c r="G23" s="145"/>
+      <c r="H23" s="145"/>
+      <c r="I23" s="145"/>
+      <c r="J23" s="145"/>
+      <c r="K23" s="145"/>
+      <c r="L23" s="145"/>
+      <c r="M23" s="145"/>
+      <c r="N23" s="145"/>
+      <c r="O23" s="145"/>
+      <c r="P23" s="145"/>
+      <c r="Q23" s="145"/>
     </row>
     <row r="24" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E24" s="141"/>
-      <c r="F24" s="141"/>
-      <c r="G24" s="141"/>
-      <c r="H24" s="141"/>
-      <c r="I24" s="141"/>
-      <c r="J24" s="141"/>
-      <c r="K24" s="141"/>
-      <c r="L24" s="141"/>
-      <c r="M24" s="141"/>
-      <c r="N24" s="141"/>
-      <c r="O24" s="141"/>
-      <c r="P24" s="141"/>
-      <c r="Q24" s="141"/>
+      <c r="E24" s="145"/>
+      <c r="F24" s="145"/>
+      <c r="G24" s="145"/>
+      <c r="H24" s="145"/>
+      <c r="I24" s="145"/>
+      <c r="J24" s="145"/>
+      <c r="K24" s="145"/>
+      <c r="L24" s="145"/>
+      <c r="M24" s="145"/>
+      <c r="N24" s="145"/>
+      <c r="O24" s="145"/>
+      <c r="P24" s="145"/>
+      <c r="Q24" s="145"/>
     </row>
     <row r="25" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E25" s="141"/>
-      <c r="F25" s="141"/>
-      <c r="G25" s="141"/>
-      <c r="H25" s="141"/>
-      <c r="I25" s="141"/>
-      <c r="J25" s="141"/>
-      <c r="K25" s="141"/>
-      <c r="L25" s="141"/>
-      <c r="M25" s="141"/>
-      <c r="N25" s="141"/>
-      <c r="O25" s="141"/>
-      <c r="P25" s="141"/>
-      <c r="Q25" s="141"/>
+      <c r="E25" s="145"/>
+      <c r="F25" s="145"/>
+      <c r="G25" s="145"/>
+      <c r="H25" s="145"/>
+      <c r="I25" s="145"/>
+      <c r="J25" s="145"/>
+      <c r="K25" s="145"/>
+      <c r="L25" s="145"/>
+      <c r="M25" s="145"/>
+      <c r="N25" s="145"/>
+      <c r="O25" s="145"/>
+      <c r="P25" s="145"/>
+      <c r="Q25" s="145"/>
     </row>
     <row r="26" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E26" s="141"/>
-      <c r="F26" s="141"/>
-      <c r="G26" s="141"/>
-      <c r="H26" s="141"/>
-      <c r="I26" s="141"/>
-      <c r="J26" s="141"/>
-      <c r="K26" s="141"/>
-      <c r="L26" s="141"/>
-      <c r="M26" s="141"/>
-      <c r="N26" s="141"/>
-      <c r="O26" s="141"/>
-      <c r="P26" s="141"/>
-      <c r="Q26" s="141"/>
+      <c r="E26" s="145"/>
+      <c r="F26" s="145"/>
+      <c r="G26" s="145"/>
+      <c r="H26" s="145"/>
+      <c r="I26" s="145"/>
+      <c r="J26" s="145"/>
+      <c r="K26" s="145"/>
+      <c r="L26" s="145"/>
+      <c r="M26" s="145"/>
+      <c r="N26" s="145"/>
+      <c r="O26" s="145"/>
+      <c r="P26" s="145"/>
+      <c r="Q26" s="145"/>
     </row>
     <row r="27" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E27" s="141"/>
-      <c r="F27" s="141"/>
-      <c r="G27" s="141"/>
-      <c r="H27" s="141"/>
-      <c r="I27" s="141"/>
-      <c r="J27" s="141"/>
-      <c r="K27" s="141"/>
-      <c r="L27" s="141"/>
-      <c r="M27" s="141"/>
-      <c r="N27" s="141"/>
-      <c r="O27" s="141"/>
-      <c r="P27" s="141"/>
-      <c r="Q27" s="141"/>
+      <c r="E27" s="145"/>
+      <c r="F27" s="145"/>
+      <c r="G27" s="145"/>
+      <c r="H27" s="145"/>
+      <c r="I27" s="145"/>
+      <c r="J27" s="145"/>
+      <c r="K27" s="145"/>
+      <c r="L27" s="145"/>
+      <c r="M27" s="145"/>
+      <c r="N27" s="145"/>
+      <c r="O27" s="145"/>
+      <c r="P27" s="145"/>
+      <c r="Q27" s="145"/>
     </row>
     <row r="28" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E28" s="141"/>
-      <c r="F28" s="141"/>
-      <c r="G28" s="141"/>
-      <c r="H28" s="141"/>
-      <c r="I28" s="141"/>
-      <c r="J28" s="141"/>
-      <c r="K28" s="141"/>
-      <c r="L28" s="141"/>
-      <c r="M28" s="141"/>
-      <c r="N28" s="141"/>
-      <c r="O28" s="141"/>
-      <c r="P28" s="141"/>
-      <c r="Q28" s="141"/>
+      <c r="E28" s="145"/>
+      <c r="F28" s="145"/>
+      <c r="G28" s="145"/>
+      <c r="H28" s="145"/>
+      <c r="I28" s="145"/>
+      <c r="J28" s="145"/>
+      <c r="K28" s="145"/>
+      <c r="L28" s="145"/>
+      <c r="M28" s="145"/>
+      <c r="N28" s="145"/>
+      <c r="O28" s="145"/>
+      <c r="P28" s="145"/>
+      <c r="Q28" s="145"/>
     </row>
     <row r="29" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E29" s="141"/>
-      <c r="F29" s="141"/>
-      <c r="G29" s="141"/>
-      <c r="H29" s="141"/>
-      <c r="I29" s="141"/>
-      <c r="J29" s="141"/>
-      <c r="K29" s="141"/>
-      <c r="L29" s="141"/>
-      <c r="M29" s="141"/>
-      <c r="N29" s="141"/>
-      <c r="O29" s="141"/>
-      <c r="P29" s="141"/>
-      <c r="Q29" s="141"/>
+      <c r="E29" s="145"/>
+      <c r="F29" s="145"/>
+      <c r="G29" s="145"/>
+      <c r="H29" s="145"/>
+      <c r="I29" s="145"/>
+      <c r="J29" s="145"/>
+      <c r="K29" s="145"/>
+      <c r="L29" s="145"/>
+      <c r="M29" s="145"/>
+      <c r="N29" s="145"/>
+      <c r="O29" s="145"/>
+      <c r="P29" s="145"/>
+      <c r="Q29" s="145"/>
     </row>
     <row r="30" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E30" s="141"/>
-      <c r="F30" s="141"/>
-      <c r="G30" s="141"/>
-      <c r="H30" s="141"/>
-      <c r="I30" s="141"/>
-      <c r="J30" s="141"/>
-      <c r="K30" s="141"/>
-      <c r="L30" s="141"/>
-      <c r="M30" s="141"/>
-      <c r="N30" s="141"/>
-      <c r="O30" s="141"/>
-      <c r="P30" s="141"/>
-      <c r="Q30" s="141"/>
+      <c r="E30" s="145"/>
+      <c r="F30" s="145"/>
+      <c r="G30" s="145"/>
+      <c r="H30" s="145"/>
+      <c r="I30" s="145"/>
+      <c r="J30" s="145"/>
+      <c r="K30" s="145"/>
+      <c r="L30" s="145"/>
+      <c r="M30" s="145"/>
+      <c r="N30" s="145"/>
+      <c r="O30" s="145"/>
+      <c r="P30" s="145"/>
+      <c r="Q30" s="145"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -24894,60 +24894,60 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C3" s="163" t="s">
+      <c r="C3" s="143" t="s">
         <v>352</v>
       </c>
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="163"/>
-      <c r="K3" s="163"/>
-      <c r="L3" s="163"/>
-      <c r="M3" s="163"/>
-      <c r="N3" s="163"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="143"/>
+      <c r="I3" s="143"/>
+      <c r="J3" s="143"/>
+      <c r="K3" s="143"/>
+      <c r="L3" s="143"/>
+      <c r="M3" s="143"/>
+      <c r="N3" s="143"/>
     </row>
     <row r="4" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C4" s="163"/>
-      <c r="D4" s="163"/>
-      <c r="E4" s="163"/>
-      <c r="F4" s="163"/>
-      <c r="G4" s="163"/>
-      <c r="H4" s="163"/>
-      <c r="I4" s="163"/>
-      <c r="J4" s="163"/>
-      <c r="K4" s="163"/>
-      <c r="L4" s="163"/>
-      <c r="M4" s="163"/>
-      <c r="N4" s="163"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="143"/>
+      <c r="I4" s="143"/>
+      <c r="J4" s="143"/>
+      <c r="K4" s="143"/>
+      <c r="L4" s="143"/>
+      <c r="M4" s="143"/>
+      <c r="N4" s="143"/>
     </row>
     <row r="7" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="D7" s="163" t="s">
+      <c r="D7" s="143" t="s">
         <v>352</v>
       </c>
-      <c r="F7" s="163" t="s">
+      <c r="F7" s="143" t="s">
         <v>353</v>
       </c>
-      <c r="G7" s="163"/>
-      <c r="H7" s="163"/>
-      <c r="J7" s="163" t="s">
+      <c r="G7" s="143"/>
+      <c r="H7" s="143"/>
+      <c r="J7" s="143" t="s">
         <v>354</v>
       </c>
-      <c r="K7" s="163"/>
-      <c r="L7" s="163"/>
-      <c r="M7" s="163"/>
+      <c r="K7" s="143"/>
+      <c r="L7" s="143"/>
+      <c r="M7" s="143"/>
     </row>
     <row r="8" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="D8" s="163"/>
-      <c r="F8" s="163"/>
-      <c r="G8" s="163"/>
-      <c r="H8" s="163"/>
-      <c r="J8" s="163"/>
-      <c r="K8" s="163"/>
-      <c r="L8" s="163"/>
-      <c r="M8" s="163"/>
+      <c r="D8" s="143"/>
+      <c r="F8" s="143"/>
+      <c r="G8" s="143"/>
+      <c r="H8" s="143"/>
+      <c r="J8" s="143"/>
+      <c r="K8" s="143"/>
+      <c r="L8" s="143"/>
+      <c r="M8" s="143"/>
     </row>
     <row r="10" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D10" s="103" t="s">
@@ -24962,12 +24962,12 @@
       </c>
       <c r="H10" s="104"/>
       <c r="I10" s="104"/>
-      <c r="J10" s="171" t="s">
+      <c r="J10" s="174" t="s">
         <v>358</v>
       </c>
-      <c r="K10" s="171"/>
-      <c r="L10" s="171"/>
-      <c r="M10" s="172"/>
+      <c r="K10" s="174"/>
+      <c r="L10" s="174"/>
+      <c r="M10" s="175"/>
     </row>
     <row r="11" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D11" s="105" t="s">
@@ -24984,12 +24984,12 @@
         <v>362</v>
       </c>
       <c r="I11" s="106"/>
-      <c r="J11" s="173" t="s">
+      <c r="J11" s="176" t="s">
         <v>363</v>
       </c>
-      <c r="K11" s="173"/>
-      <c r="L11" s="173"/>
-      <c r="M11" s="174"/>
+      <c r="K11" s="176"/>
+      <c r="L11" s="176"/>
+      <c r="M11" s="177"/>
     </row>
     <row r="13" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D13" s="103" t="s">
@@ -25004,12 +25004,12 @@
       </c>
       <c r="H13" s="104"/>
       <c r="I13" s="104"/>
-      <c r="J13" s="171" t="s">
+      <c r="J13" s="174" t="s">
         <v>367</v>
       </c>
-      <c r="K13" s="171"/>
-      <c r="L13" s="171"/>
-      <c r="M13" s="172"/>
+      <c r="K13" s="174"/>
+      <c r="L13" s="174"/>
+      <c r="M13" s="175"/>
     </row>
     <row r="14" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D14" s="105" t="s">
@@ -25026,12 +25026,12 @@
         <v>371</v>
       </c>
       <c r="I14" s="106"/>
-      <c r="J14" s="173" t="s">
+      <c r="J14" s="176" t="s">
         <v>367</v>
       </c>
-      <c r="K14" s="173"/>
-      <c r="L14" s="173"/>
-      <c r="M14" s="174"/>
+      <c r="K14" s="176"/>
+      <c r="L14" s="176"/>
+      <c r="M14" s="177"/>
     </row>
     <row r="16" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D16" s="103" t="s">
@@ -25046,12 +25046,12 @@
       </c>
       <c r="H16" s="104"/>
       <c r="I16" s="104"/>
-      <c r="J16" s="171" t="s">
+      <c r="J16" s="174" t="s">
         <v>367</v>
       </c>
-      <c r="K16" s="171"/>
-      <c r="L16" s="171"/>
-      <c r="M16" s="172"/>
+      <c r="K16" s="174"/>
+      <c r="L16" s="174"/>
+      <c r="M16" s="175"/>
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D17" s="105" t="s">
@@ -25066,12 +25066,12 @@
       </c>
       <c r="H17" s="106"/>
       <c r="I17" s="106"/>
-      <c r="J17" s="173" t="s">
+      <c r="J17" s="176" t="s">
         <v>367</v>
       </c>
-      <c r="K17" s="173"/>
-      <c r="L17" s="173"/>
-      <c r="M17" s="174"/>
+      <c r="K17" s="176"/>
+      <c r="L17" s="176"/>
+      <c r="M17" s="177"/>
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D19" s="103" t="s">
@@ -25084,12 +25084,12 @@
       <c r="G19" s="104"/>
       <c r="H19" s="104"/>
       <c r="I19" s="104"/>
-      <c r="J19" s="171" t="s">
+      <c r="J19" s="174" t="s">
         <v>367</v>
       </c>
-      <c r="K19" s="171"/>
-      <c r="L19" s="171"/>
-      <c r="M19" s="172"/>
+      <c r="K19" s="174"/>
+      <c r="L19" s="174"/>
+      <c r="M19" s="175"/>
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D20" s="105" t="s">
@@ -25102,12 +25102,12 @@
       <c r="G20" s="106"/>
       <c r="H20" s="106"/>
       <c r="I20" s="106"/>
-      <c r="J20" s="173" t="s">
+      <c r="J20" s="176" t="s">
         <v>367</v>
       </c>
-      <c r="K20" s="173"/>
-      <c r="L20" s="173"/>
-      <c r="M20" s="174"/>
+      <c r="K20" s="176"/>
+      <c r="L20" s="176"/>
+      <c r="M20" s="177"/>
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D22" s="103" t="s">
@@ -25120,12 +25120,12 @@
       <c r="G22" s="104"/>
       <c r="H22" s="104"/>
       <c r="I22" s="104"/>
-      <c r="J22" s="171" t="s">
+      <c r="J22" s="174" t="s">
         <v>367</v>
       </c>
-      <c r="K22" s="171"/>
-      <c r="L22" s="171"/>
-      <c r="M22" s="172"/>
+      <c r="K22" s="174"/>
+      <c r="L22" s="174"/>
+      <c r="M22" s="175"/>
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D23" s="105" t="s">
@@ -25138,12 +25138,12 @@
       <c r="G23" s="106"/>
       <c r="H23" s="106"/>
       <c r="I23" s="106"/>
-      <c r="J23" s="173" t="s">
+      <c r="J23" s="176" t="s">
         <v>367</v>
       </c>
-      <c r="K23" s="173"/>
-      <c r="L23" s="173"/>
-      <c r="M23" s="174"/>
+      <c r="K23" s="176"/>
+      <c r="L23" s="176"/>
+      <c r="M23" s="177"/>
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D25" s="103" t="s">
@@ -25156,12 +25156,12 @@
       <c r="G25" s="104"/>
       <c r="H25" s="104"/>
       <c r="I25" s="104"/>
-      <c r="J25" s="171" t="s">
+      <c r="J25" s="174" t="s">
         <v>367</v>
       </c>
-      <c r="K25" s="171"/>
-      <c r="L25" s="171"/>
-      <c r="M25" s="172"/>
+      <c r="K25" s="174"/>
+      <c r="L25" s="174"/>
+      <c r="M25" s="175"/>
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D26" s="105" t="s">
@@ -25174,12 +25174,12 @@
       <c r="G26" s="106"/>
       <c r="H26" s="106"/>
       <c r="I26" s="106"/>
-      <c r="J26" s="173" t="s">
+      <c r="J26" s="176" t="s">
         <v>367</v>
       </c>
-      <c r="K26" s="173"/>
-      <c r="L26" s="173"/>
-      <c r="M26" s="174"/>
+      <c r="K26" s="176"/>
+      <c r="L26" s="176"/>
+      <c r="M26" s="177"/>
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D28" s="103" t="s">
@@ -25192,12 +25192,12 @@
       <c r="G28" s="104"/>
       <c r="H28" s="104"/>
       <c r="I28" s="104"/>
-      <c r="J28" s="171" t="s">
+      <c r="J28" s="174" t="s">
         <v>367</v>
       </c>
-      <c r="K28" s="171"/>
-      <c r="L28" s="171"/>
-      <c r="M28" s="172"/>
+      <c r="K28" s="174"/>
+      <c r="L28" s="174"/>
+      <c r="M28" s="175"/>
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D29" s="105" t="s">
@@ -25212,20 +25212,15 @@
       </c>
       <c r="H29" s="106"/>
       <c r="I29" s="106"/>
-      <c r="J29" s="173" t="s">
+      <c r="J29" s="176" t="s">
         <v>367</v>
       </c>
-      <c r="K29" s="173"/>
-      <c r="L29" s="173"/>
-      <c r="M29" s="174"/>
+      <c r="K29" s="176"/>
+      <c r="L29" s="176"/>
+      <c r="M29" s="177"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C3:N4"/>
-    <mergeCell ref="F7:H8"/>
-    <mergeCell ref="J7:M8"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="J26:M26"/>
     <mergeCell ref="J28:M28"/>
     <mergeCell ref="J29:M29"/>
     <mergeCell ref="D7:D8"/>
@@ -25239,6 +25234,11 @@
     <mergeCell ref="J13:M13"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="J16:M16"/>
+    <mergeCell ref="C3:N4"/>
+    <mergeCell ref="F7:H8"/>
+    <mergeCell ref="J7:M8"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="J26:M26"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/iridescent/src/main/resources/IridescentAlchemy3-TraceOfBattle/ReadMe.xlsx
+++ b/iridescent/src/main/resources/IridescentAlchemy3-TraceOfBattle/ReadMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace-idea\7daystodie\iridescent\src\main\resources\IridescentAlchemy3-TraceOfBattle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37F4BF0-BEEC-42E8-9F0E-926B968C4A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C6BA2C-F06C-49B9-86A9-9F838030ABA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3990" yWindow="1910" windowWidth="34300" windowHeight="17350" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4046" uniqueCount="1168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4044" uniqueCount="1167">
   <si>
     <t>FF1111</t>
   </si>
@@ -2888,28 +2888,6 @@
     <t>【极意】生命提升</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>贯星</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFF09457"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>■</t>
-    </r>
-  </si>
-  <si>
     <t>【极意】防御缓冲</t>
   </si>
   <si>
@@ -3482,119 +3460,119 @@
   </si>
   <si>
     <t>520</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>200</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>360</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>1500/150</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>5000/500</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2000/200</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>3500/350</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>600/60</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>1000/100</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>1000/15000</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>750/10000</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>500/5000</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>--</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>蓝蘑菇</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>战斧</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>流血异常</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>0</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>40</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>小石斧</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>150</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>210</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>240</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>110</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>130</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>10/20/30/40</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>90</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>180</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>280</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>320</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3614,191 +3592,191 @@
 文档版本：V3.0.26.816
 七日杀游戏版本：V3.0</t>
     </r>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>上位</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>中位</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>火烧地</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>废墟</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>雪地</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>沙漠</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>紧急任务（14-18、20）</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>紧急任务（20-24）</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>埋藏补给(19-20)</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>获取(19-21)</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>清理(20-24)</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>群聚(20-24)</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>超级群聚(20-24)</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>强攻据点(20-24)</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>讨伐目标（21-24）</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>潜入电力(21-24)</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>20</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>23</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>24</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>8</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>4</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>72</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>288</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>36</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>144</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>54</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>216</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>普通18</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>晶化</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>狂化</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>3</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>2</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>1</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>腐化装备</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>腐化</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>300</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>套装可与狂化联动</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>超会心</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>0</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>看破</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>体力提升</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>属性解放</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3808,7 +3786,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3861,13 +3839,6 @@
     <font>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFF09457"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -4809,55 +4780,55 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="30" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="30" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="36" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="36" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="36" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="36" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="30" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="30" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="49" fontId="9" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="49" fontId="9" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="49" fontId="9" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -4875,13 +4846,13 @@
     <xf numFmtId="49" fontId="1" fillId="37" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="61" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="61" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="61" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4941,19 +4912,19 @@
     <xf numFmtId="49" fontId="0" fillId="36" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="36" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="36" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="36" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="36" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="36" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="61" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="61" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="61" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="61" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="31" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5097,22 +5068,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="62" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="62" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="62" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="49" fontId="9" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="45" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="45" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="45" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5404,7 +5375,7 @@
   <sheetData>
     <row r="7" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C7" s="155" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="D7" s="156"/>
       <c r="E7" s="156"/>
@@ -6173,7 +6144,7 @@
   <mergeCells count="1">
     <mergeCell ref="C7:Q51"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7297,7 +7268,7 @@
         <v>205</v>
       </c>
       <c r="K32" s="133" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="L32" s="48" t="s">
         <v>460</v>
@@ -7312,10 +7283,10 @@
         <v>435</v>
       </c>
       <c r="P32" s="133" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="Q32" s="133" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.25">
@@ -7340,7 +7311,7 @@
         <v>435</v>
       </c>
       <c r="K33" s="133" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="L33" s="48" t="s">
         <v>460</v>
@@ -7355,10 +7326,10 @@
         <v>431</v>
       </c>
       <c r="P33" s="133" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="Q33" s="133" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
@@ -7513,31 +7484,31 @@
         <v>481</v>
       </c>
       <c r="G39" s="133" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H39" s="133" t="s">
+        <v>1102</v>
+      </c>
+      <c r="I39" s="133" t="s">
+        <v>1096</v>
+      </c>
+      <c r="J39" s="133" t="s">
         <v>1099</v>
       </c>
-      <c r="H39" s="133" t="s">
-        <v>1103</v>
-      </c>
-      <c r="I39" s="133" t="s">
+      <c r="K39" s="133" t="s">
+        <v>1101</v>
+      </c>
+      <c r="L39" s="133" t="s">
         <v>1097</v>
       </c>
-      <c r="J39" s="133" t="s">
+      <c r="M39" s="133" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N39" s="133" t="s">
         <v>1100</v>
       </c>
-      <c r="K39" s="133" t="s">
-        <v>1102</v>
-      </c>
-      <c r="L39" s="133" t="s">
-        <v>1098</v>
-      </c>
-      <c r="M39" s="133" t="s">
+      <c r="O39" s="133" t="s">
         <v>1095</v>
-      </c>
-      <c r="N39" s="133" t="s">
-        <v>1101</v>
-      </c>
-      <c r="O39" s="133" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
@@ -9307,10 +9278,10 @@
     </row>
     <row r="92" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B92" s="136" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C92" s="136" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D92" s="100" t="s">
         <v>435</v>
@@ -9319,45 +9290,45 @@
         <v>430</v>
       </c>
       <c r="F92" s="136" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G92" s="136" t="s">
+        <v>1113</v>
+      </c>
+      <c r="H92" s="136" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I92" s="136" t="s">
+        <v>1110</v>
+      </c>
+      <c r="J92" s="136" t="s">
         <v>1117</v>
       </c>
-      <c r="G92" s="136" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H92" s="136" t="s">
+      <c r="K92" s="136" t="s">
+        <v>1111</v>
+      </c>
+      <c r="L92" s="136" t="s">
+        <v>1112</v>
+      </c>
+      <c r="M92" s="136" t="s">
+        <v>1118</v>
+      </c>
+      <c r="N92" s="136" t="s">
+        <v>1119</v>
+      </c>
+      <c r="O92" s="136" t="s">
+        <v>1093</v>
+      </c>
+      <c r="P92" s="136" t="s">
         <v>1115</v>
-      </c>
-      <c r="I92" s="136" t="s">
-        <v>1111</v>
-      </c>
-      <c r="J92" s="136" t="s">
-        <v>1118</v>
-      </c>
-      <c r="K92" s="136" t="s">
-        <v>1112</v>
-      </c>
-      <c r="L92" s="136" t="s">
-        <v>1113</v>
-      </c>
-      <c r="M92" s="136" t="s">
-        <v>1119</v>
-      </c>
-      <c r="N92" s="136" t="s">
-        <v>1120</v>
-      </c>
-      <c r="O92" s="136" t="s">
-        <v>1094</v>
-      </c>
-      <c r="P92" s="136" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="93" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D93" s="138" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="E93" s="138" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="F93" s="138" t="s">
         <v>426</v>
@@ -9390,10 +9361,10 @@
         <v>426</v>
       </c>
       <c r="P93" s="138" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="Q93" s="137" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
   </sheetData>
@@ -9403,7 +9374,7 @@
     <mergeCell ref="B43:P44"/>
     <mergeCell ref="B2:N3"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -10271,7 +10242,7 @@
     <mergeCell ref="H40:H43"/>
     <mergeCell ref="H46:H49"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -10353,13 +10324,13 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="133" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B4" s="133" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C4" s="133" t="s">
         <v>1148</v>
-      </c>
-      <c r="C4" s="133" t="s">
-        <v>1149</v>
       </c>
       <c r="D4" s="48" t="s">
         <v>714</v>
@@ -10377,13 +10348,13 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="133" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B5" s="133" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C5" s="133" t="s">
         <v>1150</v>
-      </c>
-      <c r="C5" s="133" t="s">
-        <v>1151</v>
       </c>
       <c r="D5" s="48" t="s">
         <v>716</v>
@@ -10401,13 +10372,13 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="133" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B6" s="133" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C6" s="133" t="s">
         <v>1146</v>
-      </c>
-      <c r="C6" s="133" t="s">
-        <v>1147</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>718</v>
@@ -10428,13 +10399,13 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="133" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B7" s="133" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C7" s="133" t="s">
         <v>1160</v>
-      </c>
-      <c r="C7" s="133" t="s">
-        <v>1161</v>
       </c>
       <c r="D7" s="48" t="s">
         <v>718</v>
@@ -10536,7 +10507,7 @@
         <v>722</v>
       </c>
       <c r="B12" s="147" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C12" s="49" t="s">
         <v>723</v>
@@ -10625,25 +10596,25 @@
         <v>1155</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>735</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>736</v>
+        <v>763</v>
+      </c>
+      <c r="H14" s="143" t="s">
+        <v>1156</v>
       </c>
       <c r="I14" s="146" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>737</v>
       </c>
       <c r="K14" s="143" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>763</v>
-      </c>
-      <c r="M14" s="143" t="s">
-        <v>1157</v>
+        <v>735</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>736</v>
       </c>
       <c r="N14" s="50">
         <v>1</v>
@@ -10652,7 +10623,7 @@
         <v>763</v>
       </c>
       <c r="P14" s="143" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>738</v>
@@ -10661,13 +10632,13 @@
         <v>1</v>
       </c>
       <c r="S14" s="146" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="T14" s="5" t="s">
         <v>749</v>
       </c>
       <c r="U14" s="143" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="V14" s="5" t="s">
         <v>739</v>
@@ -10690,10 +10661,10 @@
         <v>1</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="F15" s="143" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>735</v>
@@ -10702,19 +10673,19 @@
         <v>736</v>
       </c>
       <c r="I15" s="146" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>284</v>
       </c>
       <c r="K15" s="143" t="s">
+        <v>1155</v>
+      </c>
+      <c r="L15" s="143" t="s">
+        <v>1162</v>
+      </c>
+      <c r="M15" s="143" t="s">
         <v>1156</v>
-      </c>
-      <c r="L15" s="143" t="s">
-        <v>1163</v>
-      </c>
-      <c r="M15" s="143" t="s">
-        <v>1157</v>
       </c>
       <c r="N15" s="50">
         <v>1</v>
@@ -10723,7 +10694,7 @@
         <v>276</v>
       </c>
       <c r="P15" s="143" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>735</v>
@@ -10735,10 +10706,10 @@
         <v>1</v>
       </c>
       <c r="T15" s="143" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="U15" s="143" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="V15" s="5" t="s">
         <v>735</v>
@@ -10758,13 +10729,13 @@
         <v>743</v>
       </c>
       <c r="D16" s="146" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="E16" s="143" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="F16" s="143" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>744</v>
@@ -10773,13 +10744,13 @@
         <v>1</v>
       </c>
       <c r="I16" s="146" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>272</v>
       </c>
       <c r="K16" s="143" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>735</v>
@@ -10788,13 +10759,13 @@
         <v>736</v>
       </c>
       <c r="N16" s="146" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="O16" s="5" t="s">
         <v>272</v>
       </c>
       <c r="P16" s="143" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>735</v>
@@ -10806,10 +10777,10 @@
         <v>1</v>
       </c>
       <c r="T16" s="143" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="U16" s="143" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="V16" s="5" t="s">
         <v>735</v>
@@ -13311,7 +13282,7 @@
         <v>885</v>
       </c>
       <c r="B57" s="148" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="C57" s="57" t="s">
         <v>723</v>
@@ -15908,7 +15879,7 @@
         <v>885</v>
       </c>
       <c r="B98" s="149" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C98" s="59" t="s">
         <v>723</v>
@@ -17913,9 +17884,6 @@
       <c r="X125" s="52" t="s">
         <v>888</v>
       </c>
-      <c r="Y125" s="5" t="s">
-        <v>901</v>
-      </c>
     </row>
     <row r="126" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
@@ -17991,7 +17959,7 @@
         <v>888</v>
       </c>
       <c r="Y126" s="5" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="127" spans="1:25" x14ac:dyDescent="0.25">
@@ -18068,7 +18036,7 @@
         <v>888</v>
       </c>
       <c r="Y127" s="5" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="128" spans="1:25" x14ac:dyDescent="0.25">
@@ -18145,7 +18113,7 @@
         <v>888</v>
       </c>
       <c r="Y128" s="5" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="129" spans="1:25" x14ac:dyDescent="0.25">
@@ -18222,7 +18190,7 @@
         <v>888</v>
       </c>
       <c r="Y129" s="5" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="130" spans="1:25" x14ac:dyDescent="0.25">
@@ -18299,7 +18267,7 @@
         <v>888</v>
       </c>
       <c r="Y130" s="5" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="131" spans="1:25" x14ac:dyDescent="0.25">
@@ -18447,7 +18415,7 @@
         <v>888</v>
       </c>
       <c r="Y132" s="5" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.25">
@@ -18612,7 +18580,7 @@
     </row>
     <row r="137" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A137" s="231" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B137" s="230"/>
       <c r="C137" s="230"/>
@@ -18677,7 +18645,7 @@
       <c r="L139" s="4"/>
       <c r="M139" s="4"/>
       <c r="X139" s="234" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="Y139" s="235"/>
     </row>
@@ -18686,7 +18654,7 @@
         <v>885</v>
       </c>
       <c r="B140" s="232" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C140" s="233" t="s">
         <v>723</v>
@@ -20691,9 +20659,6 @@
       <c r="X167" s="52" t="s">
         <v>888</v>
       </c>
-      <c r="Y167" s="5" t="s">
-        <v>901</v>
-      </c>
     </row>
     <row r="168" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A168" s="5">
@@ -20769,7 +20734,7 @@
         <v>888</v>
       </c>
       <c r="Y168" s="5" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="169" spans="1:25" x14ac:dyDescent="0.25">
@@ -20846,7 +20811,7 @@
         <v>888</v>
       </c>
       <c r="Y169" s="5" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="170" spans="1:25" x14ac:dyDescent="0.25">
@@ -20923,7 +20888,7 @@
         <v>888</v>
       </c>
       <c r="Y170" s="5" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="171" spans="1:25" x14ac:dyDescent="0.25">
@@ -21000,7 +20965,7 @@
         <v>888</v>
       </c>
       <c r="Y171" s="5" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="172" spans="1:25" x14ac:dyDescent="0.25">
@@ -21077,7 +21042,7 @@
         <v>888</v>
       </c>
       <c r="Y172" s="5" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="173" spans="1:25" x14ac:dyDescent="0.25">
@@ -21225,7 +21190,7 @@
         <v>888</v>
       </c>
       <c r="Y174" s="5" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="175" spans="1:25" x14ac:dyDescent="0.25">
@@ -21312,7 +21277,7 @@
     <mergeCell ref="A54:Y55"/>
     <mergeCell ref="A95:Y96"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -21356,7 +21321,7 @@
   <sheetData>
     <row r="3" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C3" s="207" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D3" s="207"/>
       <c r="E3" s="207"/>
@@ -21369,14 +21334,14 @@
       <c r="L3" s="207"/>
       <c r="M3" s="207"/>
       <c r="P3" s="207" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="Q3" s="207"/>
       <c r="R3" s="207"/>
       <c r="S3" s="207"/>
       <c r="T3" s="207"/>
       <c r="W3" s="207" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="X3" s="207"/>
       <c r="Y3" s="207"/>
@@ -21407,24 +21372,24 @@
     <row r="7" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C7" s="4"/>
       <c r="E7" s="5" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="L7" s="4"/>
       <c r="M7" s="5" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="Q7" s="4"/>
       <c r="T7" s="4"/>
       <c r="Z7" s="4" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="8" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C8" s="32" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>741</v>
@@ -21433,7 +21398,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>813</v>
@@ -21442,7 +21407,7 @@
         <v>2</v>
       </c>
       <c r="K8" s="34" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>314</v>
@@ -21451,19 +21416,19 @@
         <v>5</v>
       </c>
       <c r="P8" s="35" t="s">
+        <v>915</v>
+      </c>
+      <c r="Q8" s="4" t="s">
         <v>916</v>
       </c>
-      <c r="Q8" s="4" t="s">
+      <c r="S8" s="36" t="s">
         <v>917</v>
       </c>
-      <c r="S8" s="36" t="s">
+      <c r="T8" s="37" t="s">
         <v>918</v>
       </c>
-      <c r="T8" s="37" t="s">
+      <c r="W8" s="38" t="s">
         <v>919</v>
-      </c>
-      <c r="W8" s="38" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="9" spans="3:26" x14ac:dyDescent="0.25">
@@ -21487,16 +21452,16 @@
         <v>5</v>
       </c>
       <c r="Q9" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="T9" s="37" t="s">
         <v>921</v>
-      </c>
-      <c r="T9" s="37" t="s">
-        <v>922</v>
       </c>
       <c r="X9" s="4" t="s">
         <v>846</v>
       </c>
       <c r="Z9" s="4" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="10" spans="3:26" x14ac:dyDescent="0.25">
@@ -21520,16 +21485,16 @@
         <v>3</v>
       </c>
       <c r="Q10" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="T10" s="4" t="s">
         <v>924</v>
       </c>
-      <c r="T10" s="4" t="s">
+      <c r="X10" s="4" t="s">
         <v>925</v>
       </c>
-      <c r="X10" s="4" t="s">
+      <c r="Z10" s="4" t="s">
         <v>926</v>
-      </c>
-      <c r="Z10" s="4" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="11" spans="3:26" x14ac:dyDescent="0.25">
@@ -21557,7 +21522,7 @@
         <v>280</v>
       </c>
       <c r="Z11" s="4" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="12" spans="3:26" x14ac:dyDescent="0.25">
@@ -21586,7 +21551,7 @@
         <v>879</v>
       </c>
       <c r="Z12" s="4" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="13" spans="3:26" x14ac:dyDescent="0.25">
@@ -21610,16 +21575,16 @@
         <v>61</v>
       </c>
       <c r="P13" s="39" t="s">
+        <v>929</v>
+      </c>
+      <c r="Q13" s="4" t="s">
         <v>930</v>
       </c>
-      <c r="Q13" s="4" t="s">
+      <c r="S13" s="40" t="s">
         <v>931</v>
       </c>
-      <c r="S13" s="40" t="s">
+      <c r="T13" s="37" t="s">
         <v>932</v>
-      </c>
-      <c r="T13" s="37" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="14" spans="3:26" x14ac:dyDescent="0.25">
@@ -21637,10 +21602,10 @@
         <v>5</v>
       </c>
       <c r="Q14" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="T14" s="37" t="s">
         <v>934</v>
-      </c>
-      <c r="T14" s="37" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="15" spans="3:26" x14ac:dyDescent="0.25">
@@ -21658,16 +21623,16 @@
         <v>3</v>
       </c>
       <c r="Q15" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="T15" s="4" t="s">
         <v>936</v>
-      </c>
-      <c r="T15" s="4" t="s">
-        <v>937</v>
       </c>
       <c r="X15" s="4" t="s">
         <v>741</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="16" spans="3:26" x14ac:dyDescent="0.25">
@@ -21690,13 +21655,13 @@
         <v>734</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="17" spans="2:27" x14ac:dyDescent="0.25">
       <c r="C17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I17" s="5">
         <v>5</v>
@@ -21713,7 +21678,7 @@
         <v>755</v>
       </c>
       <c r="Z17" s="4" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="18" spans="2:27" x14ac:dyDescent="0.25">
@@ -21733,10 +21698,10 @@
       <c r="Q18" s="4"/>
       <c r="T18" s="4"/>
       <c r="X18" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="Z18" s="4" t="s">
         <v>941</v>
-      </c>
-      <c r="Z18" s="4" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="19" spans="2:27" x14ac:dyDescent="0.25">
@@ -21761,7 +21726,7 @@
         <v>816</v>
       </c>
       <c r="Z19" s="4" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="20" spans="2:27" x14ac:dyDescent="0.25">
@@ -21784,7 +21749,7 @@
         <v>272</v>
       </c>
       <c r="Z20" s="4" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="21" spans="2:27" x14ac:dyDescent="0.25">
@@ -21807,7 +21772,7 @@
         <v>294</v>
       </c>
       <c r="Z21" s="4" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="AA21" s="5"/>
     </row>
@@ -21831,7 +21796,7 @@
         <v>290</v>
       </c>
       <c r="Z22" s="4" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="23" spans="2:27" x14ac:dyDescent="0.25">
@@ -21854,7 +21819,7 @@
         <v>300</v>
       </c>
       <c r="Z23" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="24" spans="2:27" x14ac:dyDescent="0.25">
@@ -21877,7 +21842,7 @@
         <v>742</v>
       </c>
       <c r="Z24" s="4" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="25" spans="2:27" x14ac:dyDescent="0.25">
@@ -21900,7 +21865,7 @@
         <v>296</v>
       </c>
       <c r="Z25" s="4" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="26" spans="2:27" x14ac:dyDescent="0.25">
@@ -21917,7 +21882,7 @@
         <v>298</v>
       </c>
       <c r="Z26" s="4" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="27" spans="2:27" x14ac:dyDescent="0.25">
@@ -21931,7 +21896,7 @@
         <v>800</v>
       </c>
       <c r="Z27" s="4" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="28" spans="2:27" customFormat="1" x14ac:dyDescent="0.25">
@@ -21948,7 +21913,7 @@
       </c>
       <c r="Y28" s="4"/>
       <c r="Z28" s="4" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="AA28" s="4"/>
     </row>
@@ -21957,12 +21922,12 @@
         <v>314</v>
       </c>
       <c r="Z29" s="4" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="30" spans="2:27" x14ac:dyDescent="0.25">
       <c r="C30" s="41" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>749</v>
@@ -21971,7 +21936,7 @@
         <v>4</v>
       </c>
       <c r="G30" s="42" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>759</v>
@@ -21980,7 +21945,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="43" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="L30" s="4" t="s">
         <v>799</v>
@@ -22132,7 +22097,7 @@
     <row r="37" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C37" s="4"/>
       <c r="D37" s="4" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>63</v>
@@ -22169,7 +22134,7 @@
       <c r="Q38" s="4"/>
       <c r="T38" s="4"/>
       <c r="W38" s="207" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="X38" s="207"/>
       <c r="Y38" s="207"/>
@@ -22213,7 +22178,7 @@
       <c r="Q40" s="4"/>
       <c r="T40" s="4"/>
       <c r="W40" s="208" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="X40" s="208"/>
       <c r="Y40" s="208"/>
@@ -22440,7 +22405,7 @@
     <mergeCell ref="W38:Z39"/>
     <mergeCell ref="W40:Z41"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22462,35 +22427,35 @@
   <sheetData>
     <row r="2" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C2" s="9" t="s">
+        <v>959</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>960</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>961</v>
       </c>
       <c r="F2" s="11"/>
     </row>
     <row r="3" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C3" s="12" t="s">
+        <v>961</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>962</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>963</v>
       </c>
       <c r="F3" s="13"/>
     </row>
     <row r="4" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C4" s="12" t="s">
+        <v>963</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>964</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>965</v>
       </c>
       <c r="F4" s="14"/>
       <c r="N4" s="10" t="s">
+        <v>965</v>
+      </c>
+      <c r="P4" s="10" t="s">
         <v>966</v>
-      </c>
-      <c r="P4" s="10" t="s">
-        <v>967</v>
       </c>
       <c r="Q4" s="15"/>
       <c r="R4" s="10">
@@ -22499,17 +22464,17 @@
     </row>
     <row r="5" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C5" s="16" t="s">
+        <v>967</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>968</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>969</v>
       </c>
       <c r="F5" s="17"/>
       <c r="N5" s="10" t="s">
+        <v>969</v>
+      </c>
+      <c r="P5" s="10" t="s">
         <v>970</v>
-      </c>
-      <c r="P5" s="10" t="s">
-        <v>971</v>
       </c>
       <c r="Q5" s="18"/>
       <c r="R5" s="10">
@@ -22518,17 +22483,17 @@
     </row>
     <row r="6" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C6" s="12" t="s">
+        <v>971</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>972</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>973</v>
       </c>
       <c r="F6" s="19"/>
       <c r="N6" s="10" t="s">
+        <v>973</v>
+      </c>
+      <c r="P6" s="10" t="s">
         <v>974</v>
-      </c>
-      <c r="P6" s="10" t="s">
-        <v>975</v>
       </c>
       <c r="Q6" s="20"/>
       <c r="R6" s="10">
@@ -22537,7 +22502,7 @@
     </row>
     <row r="10" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C10" s="207" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D10" s="207"/>
       <c r="E10" s="207"/>
@@ -22547,7 +22512,7 @@
       <c r="I10" s="207"/>
       <c r="J10" s="207"/>
       <c r="N10" s="207" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="O10" s="207"/>
       <c r="P10" s="207"/>
@@ -22589,10 +22554,10 @@
     </row>
     <row r="13" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C13" s="210" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E13" s="22">
         <f>E14/SUM(E14:H14)</f>
@@ -22603,10 +22568,10 @@
         <v>0.30769230769230799</v>
       </c>
       <c r="N13" s="210" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="O13" s="21" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="P13" s="22">
         <f>P14/SUM(P14:S14)</f>
@@ -22628,7 +22593,7 @@
     <row r="14" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C14" s="211"/>
       <c r="D14" s="21" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E14" s="23">
         <f>E16*E15</f>
@@ -22640,7 +22605,7 @@
       </c>
       <c r="N14" s="211"/>
       <c r="O14" s="21" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P14" s="23">
         <f t="shared" ref="P14:S14" si="0">P16*P15</f>
@@ -22662,7 +22627,7 @@
     <row r="15" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C15" s="211"/>
       <c r="D15" s="24" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E15" s="25">
         <v>3</v>
@@ -22672,7 +22637,7 @@
       </c>
       <c r="N15" s="211"/>
       <c r="O15" s="26" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P15" s="25">
         <v>50</v>
@@ -22690,7 +22655,7 @@
     <row r="16" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C16" s="211"/>
       <c r="D16" s="24" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E16" s="25">
         <v>6</v>
@@ -22700,7 +22665,7 @@
       </c>
       <c r="N16" s="211"/>
       <c r="O16" s="24" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="P16" s="25">
         <v>6</v>
@@ -22718,26 +22683,26 @@
     <row r="17" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C17" s="212"/>
       <c r="D17" s="27" t="s">
+        <v>981</v>
+      </c>
+      <c r="E17" s="28" t="s">
         <v>982</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>983</v>
       </c>
       <c r="F17" s="28" t="s">
         <v>321</v>
       </c>
       <c r="N17" s="212"/>
       <c r="O17" s="28" t="s">
+        <v>981</v>
+      </c>
+      <c r="P17" s="28" t="s">
         <v>982</v>
-      </c>
-      <c r="P17" s="28" t="s">
-        <v>983</v>
       </c>
       <c r="Q17" s="28" t="s">
         <v>321</v>
       </c>
       <c r="R17" s="28" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="S17" s="28" t="s">
         <v>326</v>
@@ -22759,10 +22724,10 @@
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C19" s="210" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E19" s="22">
         <f>E20/SUM(E20:H20)</f>
@@ -22777,10 +22742,10 @@
         <v>0.11764705882352899</v>
       </c>
       <c r="N19" s="210" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="O19" s="21" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="P19" s="22">
         <f>P20/SUM(P20:S20)</f>
@@ -22802,7 +22767,7 @@
     <row r="20" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C20" s="211"/>
       <c r="D20" s="21" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E20" s="23">
         <f t="shared" ref="E20:G20" si="1">E22*E21</f>
@@ -22818,7 +22783,7 @@
       </c>
       <c r="N20" s="211"/>
       <c r="O20" s="21" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P20" s="23">
         <f t="shared" ref="P20:S20" si="2">P22*P21</f>
@@ -22840,7 +22805,7 @@
     <row r="21" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C21" s="211"/>
       <c r="D21" s="24" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E21" s="25">
         <v>30</v>
@@ -22853,7 +22818,7 @@
       </c>
       <c r="N21" s="211"/>
       <c r="O21" s="26" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P21" s="25">
         <v>15</v>
@@ -22871,7 +22836,7 @@
     <row r="22" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C22" s="211"/>
       <c r="D22" s="24" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E22" s="25">
         <v>8</v>
@@ -22884,7 +22849,7 @@
       </c>
       <c r="N22" s="211"/>
       <c r="O22" s="24" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="P22" s="25">
         <v>18</v>
@@ -22902,32 +22867,32 @@
     <row r="23" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C23" s="212"/>
       <c r="D23" s="27" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E23" s="28" t="s">
         <v>321</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="G23" s="28" t="s">
         <v>326</v>
       </c>
       <c r="N23" s="212"/>
       <c r="O23" s="28" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="P23" s="28" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="Q23" s="28" t="s">
         <v>326</v>
       </c>
       <c r="R23" s="28" t="s">
+        <v>984</v>
+      </c>
+      <c r="S23" s="28" t="s">
         <v>985</v>
-      </c>
-      <c r="S23" s="28" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="24" spans="3:19" x14ac:dyDescent="0.25">
@@ -22946,10 +22911,10 @@
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C25" s="210" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E25" s="22">
         <f>E26/SUM(E26:H26)</f>
@@ -22968,10 +22933,10 @@
         <v>3.7267080745341602E-2</v>
       </c>
       <c r="N25" s="209" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="O25" s="21" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="P25" s="22">
         <f>P26/SUM(P26:S26)</f>
@@ -22993,7 +22958,7 @@
     <row r="26" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C26" s="211"/>
       <c r="D26" s="21" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E26" s="23">
         <f t="shared" ref="E26:H26" si="3">E28*E27</f>
@@ -23013,7 +22978,7 @@
       </c>
       <c r="N26" s="209"/>
       <c r="O26" s="21" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="P26" s="23">
         <f t="shared" ref="P26:S26" si="4">(P28*P27)+(P30*P29)</f>
@@ -23035,7 +23000,7 @@
     <row r="27" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C27" s="211"/>
       <c r="D27" s="24" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E27" s="25">
         <v>20</v>
@@ -23051,7 +23016,7 @@
       </c>
       <c r="N27" s="209"/>
       <c r="O27" s="26" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P27" s="25">
         <v>2</v>
@@ -23069,7 +23034,7 @@
     <row r="28" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C28" s="211"/>
       <c r="D28" s="24" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E28" s="25">
         <v>18</v>
@@ -23085,7 +23050,7 @@
       </c>
       <c r="N28" s="209"/>
       <c r="O28" s="24" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="P28" s="25">
         <v>792</v>
@@ -23103,23 +23068,23 @@
     <row r="29" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C29" s="212"/>
       <c r="D29" s="27" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F29" s="28" t="s">
         <v>326</v>
       </c>
       <c r="G29" s="28" t="s">
+        <v>984</v>
+      </c>
+      <c r="H29" s="28" t="s">
         <v>985</v>
-      </c>
-      <c r="H29" s="28" t="s">
-        <v>986</v>
       </c>
       <c r="N29" s="209"/>
       <c r="O29" s="29" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="P29" s="30">
         <v>50</v>
@@ -23143,7 +23108,7 @@
       <c r="H30" s="9"/>
       <c r="N30" s="209"/>
       <c r="O30" s="31" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="P30" s="31" t="s">
         <v>66</v>
@@ -23152,7 +23117,7 @@
         <v>209</v>
       </c>
       <c r="R30" s="31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="S30" s="31" t="s">
         <v>563</v>
@@ -23160,10 +23125,10 @@
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C31" s="209" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E31" s="22">
         <f>E32/SUM(E32:H32)</f>
@@ -23187,25 +23152,25 @@
       </c>
       <c r="N31" s="209"/>
       <c r="O31" s="28" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="P31" s="28" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="Q31" s="28" t="s">
         <v>330</v>
       </c>
       <c r="R31" s="28" t="s">
+        <v>990</v>
+      </c>
+      <c r="S31" s="28" t="s">
         <v>991</v>
-      </c>
-      <c r="S31" s="28" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C32" s="209"/>
       <c r="D32" s="21" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E32" s="23">
         <f t="shared" ref="E32:I32" si="5">(E34*E33)+(E36*E35)</f>
@@ -23231,7 +23196,7 @@
     <row r="33" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C33" s="209"/>
       <c r="D33" s="26" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E33" s="25">
         <v>200</v>
@@ -23252,7 +23217,7 @@
     <row r="34" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C34" s="209"/>
       <c r="D34" s="24" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E34" s="25">
         <v>22</v>
@@ -23273,7 +23238,7 @@
     <row r="35" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C35" s="209"/>
       <c r="D35" s="29" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E35" s="30">
         <v>0</v>
@@ -23294,7 +23259,7 @@
     <row r="36" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C36" s="209"/>
       <c r="D36" s="31" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="E36" s="31" t="s">
         <v>570</v>
@@ -23315,19 +23280,19 @@
     <row r="37" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C37" s="209"/>
       <c r="D37" s="28" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E37" s="28" t="s">
         <v>326</v>
       </c>
       <c r="F37" s="28" t="s">
+        <v>984</v>
+      </c>
+      <c r="G37" s="28" t="s">
         <v>985</v>
       </c>
-      <c r="G37" s="28" t="s">
-        <v>986</v>
-      </c>
       <c r="H37" s="28" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="I37" s="28" t="s">
         <v>330</v>
@@ -23335,10 +23300,10 @@
     </row>
     <row r="39" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C39" s="209" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E39" s="22">
         <f>E40/SUM(E40:H40)</f>
@@ -23368,7 +23333,7 @@
     <row r="40" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C40" s="209"/>
       <c r="D40" s="21" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E40" s="23">
         <f t="shared" ref="E40:J40" si="7">(E42*E41)+(E44*E43)</f>
@@ -23398,7 +23363,7 @@
     <row r="41" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C41" s="209"/>
       <c r="D41" s="26" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E41" s="25">
         <v>100</v>
@@ -23422,7 +23387,7 @@
     <row r="42" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C42" s="209"/>
       <c r="D42" s="24" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E42" s="25">
         <v>20</v>
@@ -23446,7 +23411,7 @@
     <row r="43" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C43" s="209"/>
       <c r="D43" s="29" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E43" s="30">
         <v>0</v>
@@ -23470,7 +23435,7 @@
     <row r="44" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C44" s="209"/>
       <c r="D44" s="31" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="E44" s="31" t="s">
         <v>570</v>
@@ -23485,7 +23450,7 @@
         <v>209</v>
       </c>
       <c r="I44" s="31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="J44" s="31" t="s">
         <v>563</v>
@@ -23494,25 +23459,25 @@
     <row r="45" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C45" s="209"/>
       <c r="D45" s="28" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E45" s="28" t="s">
+        <v>984</v>
+      </c>
+      <c r="F45" s="28" t="s">
         <v>985</v>
       </c>
-      <c r="F45" s="28" t="s">
-        <v>986</v>
-      </c>
       <c r="G45" s="28" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H45" s="28" t="s">
         <v>330</v>
       </c>
       <c r="I45" s="28" t="s">
+        <v>990</v>
+      </c>
+      <c r="J45" s="28" t="s">
         <v>991</v>
-      </c>
-      <c r="J45" s="28" t="s">
-        <v>992</v>
       </c>
     </row>
   </sheetData>
@@ -23528,7 +23493,7 @@
     <mergeCell ref="C25:C29"/>
     <mergeCell ref="C31:C37"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23557,7 +23522,7 @@
   <sheetData>
     <row r="2" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C2" s="219" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D2" s="220"/>
       <c r="E2" s="220"/>
@@ -23605,34 +23570,34 @@
         <v>723</v>
       </c>
       <c r="D6" s="216" t="s">
+        <v>993</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>994</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="216" t="s">
         <v>995</v>
       </c>
-      <c r="F6" s="216" t="s">
+      <c r="G6" s="6" t="s">
         <v>996</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="216" t="s">
         <v>997</v>
       </c>
-      <c r="H6" s="216" t="s">
+      <c r="I6" s="6" t="s">
         <v>998</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>999</v>
       </c>
       <c r="J6" s="216" t="s">
         <v>100</v>
       </c>
       <c r="K6" s="6" t="s">
+        <v>999</v>
+      </c>
+      <c r="L6" s="216" t="s">
         <v>1000</v>
       </c>
-      <c r="L6" s="216" t="s">
+      <c r="M6" s="6" t="s">
         <v>1001</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="7" spans="3:16" x14ac:dyDescent="0.25">
@@ -23664,34 +23629,34 @@
     <row r="9" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C9" s="214"/>
       <c r="D9" s="216" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>1003</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="F9" s="216" t="s">
         <v>1004</v>
       </c>
-      <c r="F9" s="216" t="s">
+      <c r="G9" s="6" t="s">
         <v>1005</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="H9" s="216" t="s">
         <v>1006</v>
       </c>
-      <c r="H9" s="216" t="s">
+      <c r="I9" s="6" t="s">
         <v>1007</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="J9" s="216" t="s">
         <v>1008</v>
       </c>
-      <c r="J9" s="216" t="s">
+      <c r="K9" s="6" t="s">
         <v>1009</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="L9" s="216" t="s">
         <v>1010</v>
       </c>
-      <c r="L9" s="216" t="s">
+      <c r="M9" s="6" t="s">
         <v>1011</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="10" spans="3:16" x14ac:dyDescent="0.25">
@@ -23723,34 +23688,34 @@
     <row r="12" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C12" s="214"/>
       <c r="D12" s="216" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>1013</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="F12" s="216" t="s">
         <v>1014</v>
       </c>
-      <c r="F12" s="216" t="s">
+      <c r="G12" s="6" t="s">
         <v>1015</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="H12" s="216" t="s">
         <v>1016</v>
       </c>
-      <c r="H12" s="216" t="s">
+      <c r="I12" s="6" t="s">
         <v>1017</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="J12" s="216" t="s">
         <v>1018</v>
       </c>
-      <c r="J12" s="216" t="s">
+      <c r="K12" s="6" t="s">
         <v>1019</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="L12" s="216" t="s">
         <v>1020</v>
       </c>
-      <c r="L12" s="216" t="s">
+      <c r="M12" s="6" t="s">
         <v>1021</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="13" spans="3:16" x14ac:dyDescent="0.25">
@@ -23784,10 +23749,10 @@
         <v>492</v>
       </c>
       <c r="D16" s="216" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>1023</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="17" spans="3:11" x14ac:dyDescent="0.25">
@@ -23803,10 +23768,10 @@
     <row r="19" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C19" s="214"/>
       <c r="D19" s="216" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>1025</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="20" spans="3:11" x14ac:dyDescent="0.25">
@@ -23822,35 +23787,35 @@
     <row r="22" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C22" s="214"/>
       <c r="D22" s="216" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F22" s="216" t="s">
         <v>1027</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>1026</v>
-      </c>
-      <c r="F22" s="216" t="s">
+      <c r="G22" s="6" t="s">
         <v>1028</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="H22" s="216" t="s">
         <v>1029</v>
       </c>
-      <c r="H22" s="216" t="s">
+      <c r="I22" s="6" t="s">
         <v>1030</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="J22" s="216" t="s">
         <v>1031</v>
       </c>
-      <c r="J22" s="216" t="s">
+      <c r="K22" s="6" t="s">
         <v>1032</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="23" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C23" s="214"/>
       <c r="D23" s="217"/>
       <c r="E23" s="7" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="F23" s="217"/>
       <c r="G23" s="7"/>
@@ -23858,7 +23823,7 @@
       <c r="I23" s="7"/>
       <c r="J23" s="217"/>
       <c r="K23" s="7" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="24" spans="3:11" x14ac:dyDescent="0.25">
@@ -23874,13 +23839,13 @@
     </row>
     <row r="26" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C26" s="213" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D26" s="216" t="s">
         <v>1036</v>
       </c>
-      <c r="D26" s="216" t="s">
+      <c r="E26" s="6" t="s">
         <v>1037</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="27" spans="3:11" x14ac:dyDescent="0.25">
@@ -23896,17 +23861,17 @@
     <row r="29" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C29" s="214"/>
       <c r="D29" s="216" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="30" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C30" s="214"/>
       <c r="D30" s="217"/>
       <c r="E30" s="7" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="31" spans="3:11" x14ac:dyDescent="0.25">
@@ -23920,14 +23885,14 @@
         <v>49</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="33" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C33" s="214"/>
       <c r="D33" s="217"/>
       <c r="E33" s="7" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="34" spans="3:15" x14ac:dyDescent="0.25">
@@ -23975,7 +23940,7 @@
     <mergeCell ref="D29:D31"/>
     <mergeCell ref="D32:D34"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23991,7 +23956,7 @@
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="190" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B2" s="191"/>
       <c r="C2" s="191"/>
@@ -24007,89 +23972,89 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D6" t="s">
         <v>1043</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D7" t="s">
         <v>1045</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D8" t="s">
         <v>1047</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D9" t="s">
         <v>1049</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D10" t="s">
         <v>1051</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D11" t="s">
         <v>1053</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D12" t="s">
         <v>1055</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D13" t="s">
         <v>1057</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D14" t="s">
         <v>1059</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D15" t="s">
         <v>1061</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1062</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E3"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -24109,33 +24074,33 @@
   <sheetData>
     <row r="4" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J4" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="5" spans="10:13" x14ac:dyDescent="0.25">
       <c r="K5" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="9" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J9" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="10" spans="10:13" x14ac:dyDescent="0.25">
       <c r="K10" t="s">
+        <v>1065</v>
+      </c>
+      <c r="L10" t="s">
         <v>1066</v>
-      </c>
-      <c r="L10" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="11" spans="10:13" x14ac:dyDescent="0.25">
       <c r="K11" t="s">
+        <v>1067</v>
+      </c>
+      <c r="L11" t="s">
         <v>1068</v>
-      </c>
-      <c r="L11" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="12" spans="10:13" x14ac:dyDescent="0.25">
@@ -24145,13 +24110,13 @@
     </row>
     <row r="13" spans="10:13" x14ac:dyDescent="0.25">
       <c r="K13" t="s">
+        <v>1069</v>
+      </c>
+      <c r="L13" t="s">
         <v>1070</v>
       </c>
-      <c r="L13" t="s">
+      <c r="M13" t="s">
         <v>1071</v>
-      </c>
-      <c r="M13" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="14" spans="10:13" x14ac:dyDescent="0.25">
@@ -24166,39 +24131,39 @@
     </row>
     <row r="16" spans="10:13" x14ac:dyDescent="0.25">
       <c r="K16" t="s">
+        <v>1072</v>
+      </c>
+      <c r="L16" t="s">
         <v>1073</v>
-      </c>
-      <c r="L16" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="17" spans="4:14" x14ac:dyDescent="0.25">
       <c r="K17" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="18" spans="4:14" x14ac:dyDescent="0.25">
       <c r="K18" t="s">
+        <v>1075</v>
+      </c>
+      <c r="M18" t="s">
         <v>1076</v>
-      </c>
-      <c r="M18" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="19" spans="4:14" x14ac:dyDescent="0.25">
       <c r="K19" t="s">
+        <v>1077</v>
+      </c>
+      <c r="L19" t="s">
         <v>1078</v>
-      </c>
-      <c r="L19" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="20" spans="4:14" x14ac:dyDescent="0.25">
       <c r="K20" t="s">
+        <v>1079</v>
+      </c>
+      <c r="L20" t="s">
         <v>1080</v>
-      </c>
-      <c r="L20" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="21" spans="4:14" ht="43" customHeight="1" x14ac:dyDescent="0.25">
@@ -24206,32 +24171,32 @@
         <v>873</v>
       </c>
       <c r="L21" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M21" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="N21" t="s">
         <v>1083</v>
-      </c>
-      <c r="N21" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="23" spans="4:14" x14ac:dyDescent="0.25">
       <c r="K23" t="s">
+        <v>1084</v>
+      </c>
+      <c r="L23" t="s">
         <v>1085</v>
-      </c>
-      <c r="L23" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="29" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D29" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="189" t="s">
         <v>1088</v>
-      </c>
-      <c r="F29" s="189" t="s">
-        <v>1089</v>
       </c>
       <c r="G29" s="189"/>
       <c r="H29" s="189"/>
@@ -24244,10 +24209,10 @@
     </row>
     <row r="31" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D31" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E31" s="228" t="s">
         <v>1090</v>
-      </c>
-      <c r="E31" s="228" t="s">
-        <v>1091</v>
       </c>
       <c r="F31" s="228"/>
       <c r="G31" s="228"/>
@@ -24258,7 +24223,7 @@
     <mergeCell ref="F29:N29"/>
     <mergeCell ref="E31:H31"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -24576,13 +24541,13 @@
     </row>
     <row r="28" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C28" s="157" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D28" s="180" t="s">
         <v>1123</v>
       </c>
-      <c r="D28" s="180" t="s">
-        <v>1124</v>
-      </c>
       <c r="E28" s="180" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="F28" s="158" t="s">
         <v>39</v>
@@ -24632,19 +24597,19 @@
     </row>
     <row r="30" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C30" s="139" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="D30" s="139" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="E30" s="139" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="F30" s="129" t="s">
         <v>50</v>
       </c>
       <c r="G30" s="142" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H30" s="129" t="s">
         <v>51</v>
@@ -24676,49 +24641,49 @@
         <v>49</v>
       </c>
       <c r="D31" s="140" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E31" s="140" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="F31" s="175" t="s">
         <v>39</v>
       </c>
       <c r="G31" s="177" t="s">
+        <v>1128</v>
+      </c>
+      <c r="H31" s="179" t="s">
         <v>1129</v>
       </c>
-      <c r="H31" s="179" t="s">
+      <c r="I31" s="179" t="s">
         <v>1130</v>
       </c>
-      <c r="I31" s="179" t="s">
+      <c r="J31" s="179" t="s">
         <v>1131</v>
       </c>
-      <c r="J31" s="179" t="s">
+      <c r="K31" s="179" t="s">
         <v>1132</v>
       </c>
-      <c r="K31" s="179" t="s">
+      <c r="L31" s="179" t="s">
         <v>1133</v>
       </c>
-      <c r="L31" s="179" t="s">
+      <c r="M31" s="179" t="s">
         <v>1134</v>
       </c>
-      <c r="M31" s="179" t="s">
+      <c r="N31" s="177" t="s">
         <v>1135</v>
       </c>
-      <c r="N31" s="177" t="s">
+      <c r="O31" s="179" t="s">
         <v>1136</v>
-      </c>
-      <c r="O31" s="179" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="32" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C32" s="176"/>
       <c r="D32" s="140" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="E32" s="141" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F32" s="176"/>
       <c r="G32" s="178"/>
@@ -24809,22 +24774,22 @@
     </row>
     <row r="41" spans="7:12" x14ac:dyDescent="0.25">
       <c r="G41" s="143" t="s">
+        <v>1137</v>
+      </c>
+      <c r="H41" s="144" t="s">
         <v>1138</v>
       </c>
-      <c r="H41" s="144" t="s">
+      <c r="I41" s="144" t="s">
         <v>1139</v>
       </c>
-      <c r="I41" s="144" t="s">
+      <c r="J41" s="144" t="s">
         <v>1140</v>
       </c>
-      <c r="J41" s="144" t="s">
+      <c r="K41" s="144" t="s">
         <v>1141</v>
       </c>
-      <c r="K41" s="144" t="s">
+      <c r="L41" s="144" t="s">
         <v>1142</v>
-      </c>
-      <c r="L41" s="144" t="s">
-        <v>1143</v>
       </c>
     </row>
   </sheetData>
@@ -24875,7 +24840,7 @@
     <mergeCell ref="G26:G27"/>
     <mergeCell ref="G28:G29"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -25480,7 +25445,7 @@
     <mergeCell ref="D25:D27"/>
     <mergeCell ref="D28:D30"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -26294,7 +26259,7 @@
     <mergeCell ref="E8:O8"/>
     <mergeCell ref="E15:O15"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -26341,7 +26306,7 @@
     </row>
     <row r="5" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C5" s="135" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="E5" s="189" t="s">
         <v>215</v>
@@ -26986,7 +26951,7 @@
     <mergeCell ref="E8:O8"/>
     <mergeCell ref="E9:O9"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27021,7 +26986,7 @@
         <v>271</v>
       </c>
       <c r="E6" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F6" t="s">
         <v>272</v>
@@ -27032,7 +26997,7 @@
         <v>273</v>
       </c>
       <c r="E7" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F7" t="s">
         <v>274</v>
@@ -27043,7 +27008,7 @@
         <v>275</v>
       </c>
       <c r="E8" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F8" t="s">
         <v>276</v>
@@ -27054,7 +27019,7 @@
         <v>277</v>
       </c>
       <c r="E9" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F9" t="s">
         <v>278</v>
@@ -27065,7 +27030,7 @@
         <v>279</v>
       </c>
       <c r="E10" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F10" t="s">
         <v>280</v>
@@ -27076,7 +27041,7 @@
         <v>281</v>
       </c>
       <c r="E11" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F11" t="s">
         <v>282</v>
@@ -27087,7 +27052,7 @@
         <v>283</v>
       </c>
       <c r="E12" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F12" t="s">
         <v>284</v>
@@ -27098,7 +27063,7 @@
         <v>285</v>
       </c>
       <c r="E13" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F13" t="s">
         <v>286</v>
@@ -27109,7 +27074,7 @@
         <v>287</v>
       </c>
       <c r="E14" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F14" t="s">
         <v>288</v>
@@ -27120,7 +27085,7 @@
         <v>289</v>
       </c>
       <c r="E15" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F15" t="s">
         <v>290</v>
@@ -27131,7 +27096,7 @@
         <v>291</v>
       </c>
       <c r="E16" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F16" t="s">
         <v>292</v>
@@ -27142,7 +27107,7 @@
         <v>293</v>
       </c>
       <c r="E17" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F17" t="s">
         <v>294</v>
@@ -27153,7 +27118,7 @@
         <v>295</v>
       </c>
       <c r="E18" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F18" t="s">
         <v>296</v>
@@ -27164,7 +27129,7 @@
         <v>297</v>
       </c>
       <c r="E19" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F19" t="s">
         <v>298</v>
@@ -27175,7 +27140,7 @@
         <v>299</v>
       </c>
       <c r="E20" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F20" t="s">
         <v>300</v>
@@ -27186,7 +27151,7 @@
         <v>301</v>
       </c>
       <c r="E21" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F21" t="s">
         <v>302</v>
@@ -27197,7 +27162,7 @@
         <v>303</v>
       </c>
       <c r="E22" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F22" t="s">
         <v>304</v>
@@ -27208,7 +27173,7 @@
         <v>305</v>
       </c>
       <c r="E23" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F23" t="s">
         <v>306</v>
@@ -27219,7 +27184,7 @@
         <v>307</v>
       </c>
       <c r="E24" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F24" t="s">
         <v>308</v>
@@ -27230,7 +27195,7 @@
         <v>309</v>
       </c>
       <c r="E25" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F25" t="s">
         <v>310</v>
@@ -27241,7 +27206,7 @@
         <v>311</v>
       </c>
       <c r="E26" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F26" t="s">
         <v>312</v>
@@ -27252,7 +27217,7 @@
         <v>313</v>
       </c>
       <c r="E27" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F27" t="s">
         <v>314</v>
@@ -27263,7 +27228,7 @@
         <v>315</v>
       </c>
       <c r="E28" s="134" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F28" t="s">
         <v>316</v>
@@ -27273,7 +27238,7 @@
   <mergeCells count="1">
     <mergeCell ref="C2:G3"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27488,7 +27453,7 @@
   <mergeCells count="1">
     <mergeCell ref="D2:P3"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27747,7 +27712,7 @@
     <mergeCell ref="E13:Q20"/>
     <mergeCell ref="E23:Q30"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28111,7 +28076,7 @@
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="J16:M16"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/iridescent/src/main/resources/IridescentAlchemy3-TraceOfBattle/ReadMe.xlsx
+++ b/iridescent/src/main/resources/IridescentAlchemy3-TraceOfBattle/ReadMe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace-idea\7daystodie\iridescent\src\main\resources\IridescentAlchemy3-TraceOfBattle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C6BA2C-F06C-49B9-86A9-9F838030ABA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4456797B-2202-4C98-BB86-870E70C55348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3990" yWindow="1910" windowWidth="34300" windowHeight="17350" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3990" yWindow="1910" windowWidth="34300" windowHeight="17350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="首页" sheetId="15" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4044" uniqueCount="1167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4044" uniqueCount="1168">
   <si>
     <t>FF1111</t>
   </si>
@@ -3575,6 +3575,194 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>上位</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>火烧地</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>废墟</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪地</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙漠</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>紧急任务（14-18、20）</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>紧急任务（20-24）</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>埋藏补给(19-20)</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取(19-21)</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>清理(20-24)</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>群聚(20-24)</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>超级群聚(20-24)</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>强攻据点(20-24)</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>讨伐目标（21-24）</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜入电力(21-24)</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>19</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>20</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>21</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>22</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>23</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>24</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>72</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>288</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>36</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>144</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>54</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>216</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通18</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>晶化</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>狂化</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>腐化装备</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>腐化</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>300</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>套装可与狂化联动</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>超会心</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>看破</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力提升</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性解放</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>超位</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>G位</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">虹彩炼金3-战痕
 </t>
@@ -3589,193 +3777,9 @@
       </rPr>
       <t xml:space="preserve">
 作者：整洁的魔理沙
-文档版本：V3.0.26.816
+文档版本：V3.0.26.865
 七日杀游戏版本：V3.0</t>
     </r>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>上位</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>中位</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>火烧地</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>废墟</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>雪地</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>沙漠</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>紧急任务（14-18、20）</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>紧急任务（20-24）</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>埋藏补给(19-20)</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>获取(19-21)</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>清理(20-24)</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>群聚(20-24)</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>超级群聚(20-24)</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>强攻据点(20-24)</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>讨伐目标（21-24）</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>潜入电力(21-24)</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>19</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>20</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>21</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>22</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>23</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>24</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>4</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>72</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>288</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>36</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>144</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>54</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>216</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通18</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>晶化</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>狂化</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>3</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>2</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>腐化装备</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>腐化</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>300</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>套装可与狂化联动</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>超会心</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>看破</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>体力提升</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>属性解放</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -5375,7 +5379,7 @@
   <sheetData>
     <row r="7" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C7" s="155" t="s">
-        <v>1120</v>
+        <v>1167</v>
       </c>
       <c r="D7" s="156"/>
       <c r="E7" s="156"/>
@@ -10324,13 +10328,13 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="133" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="B4" s="133" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="C4" s="133" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="D4" s="48" t="s">
         <v>714</v>
@@ -10348,13 +10352,13 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="133" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="B5" s="133" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="C5" s="133" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="D5" s="48" t="s">
         <v>716</v>
@@ -10372,13 +10376,13 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="133" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B6" s="133" t="s">
         <v>1143</v>
       </c>
-      <c r="B6" s="133" t="s">
-        <v>1145</v>
-      </c>
       <c r="C6" s="133" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>718</v>
@@ -10399,13 +10403,13 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="133" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B7" s="133" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="C7" s="133" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="D7" s="48" t="s">
         <v>718</v>
@@ -10507,7 +10511,7 @@
         <v>722</v>
       </c>
       <c r="B12" s="147" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C12" s="49" t="s">
         <v>723</v>
@@ -10593,22 +10597,22 @@
         <v>737</v>
       </c>
       <c r="F14" s="143" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>763</v>
       </c>
       <c r="H14" s="143" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="I14" s="146" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>737</v>
       </c>
       <c r="K14" s="143" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="L14" s="5" t="s">
         <v>735</v>
@@ -10623,7 +10627,7 @@
         <v>763</v>
       </c>
       <c r="P14" s="143" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>738</v>
@@ -10632,13 +10636,13 @@
         <v>1</v>
       </c>
       <c r="S14" s="146" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="T14" s="5" t="s">
         <v>749</v>
       </c>
       <c r="U14" s="143" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="V14" s="5" t="s">
         <v>739</v>
@@ -10661,10 +10665,10 @@
         <v>1</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="F15" s="143" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>735</v>
@@ -10673,19 +10677,19 @@
         <v>736</v>
       </c>
       <c r="I15" s="146" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>284</v>
       </c>
       <c r="K15" s="143" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="L15" s="143" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="M15" s="143" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="N15" s="50">
         <v>1</v>
@@ -10694,7 +10698,7 @@
         <v>276</v>
       </c>
       <c r="P15" s="143" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>735</v>
@@ -10706,10 +10710,10 @@
         <v>1</v>
       </c>
       <c r="T15" s="143" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="U15" s="143" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="V15" s="5" t="s">
         <v>735</v>
@@ -10729,13 +10733,13 @@
         <v>743</v>
       </c>
       <c r="D16" s="146" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="E16" s="143" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="F16" s="143" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>744</v>
@@ -10744,13 +10748,13 @@
         <v>1</v>
       </c>
       <c r="I16" s="146" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>272</v>
       </c>
       <c r="K16" s="143" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>735</v>
@@ -10759,13 +10763,13 @@
         <v>736</v>
       </c>
       <c r="N16" s="146" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="O16" s="5" t="s">
         <v>272</v>
       </c>
       <c r="P16" s="143" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>735</v>
@@ -10777,10 +10781,10 @@
         <v>1</v>
       </c>
       <c r="T16" s="143" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="U16" s="143" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="V16" s="5" t="s">
         <v>735</v>
@@ -13282,7 +13286,7 @@
         <v>885</v>
       </c>
       <c r="B57" s="148" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="C57" s="57" t="s">
         <v>723</v>
@@ -15879,7 +15883,7 @@
         <v>885</v>
       </c>
       <c r="B98" s="149" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="C98" s="59" t="s">
         <v>723</v>
@@ -18580,7 +18584,7 @@
     </row>
     <row r="137" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A137" s="231" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B137" s="230"/>
       <c r="C137" s="230"/>
@@ -18645,7 +18649,7 @@
       <c r="L139" s="4"/>
       <c r="M139" s="4"/>
       <c r="X139" s="234" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="Y139" s="235"/>
     </row>
@@ -18654,7 +18658,7 @@
         <v>885</v>
       </c>
       <c r="B140" s="232" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="C140" s="233" t="s">
         <v>723</v>
@@ -24541,13 +24545,13 @@
     </row>
     <row r="28" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C28" s="157" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="D28" s="180" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="E28" s="180" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="F28" s="158" t="s">
         <v>39</v>
@@ -24597,19 +24601,19 @@
     </row>
     <row r="30" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C30" s="139" t="s">
-        <v>1121</v>
+        <v>1166</v>
       </c>
       <c r="D30" s="139" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="E30" s="139" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="F30" s="129" t="s">
         <v>50</v>
       </c>
       <c r="G30" s="142" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="H30" s="129" t="s">
         <v>51</v>
@@ -24637,50 +24641,50 @@
       </c>
     </row>
     <row r="31" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C31" s="175" t="s">
-        <v>49</v>
+      <c r="C31" s="179" t="s">
+        <v>1165</v>
       </c>
       <c r="D31" s="140" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="E31" s="140" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="F31" s="175" t="s">
         <v>39</v>
       </c>
       <c r="G31" s="177" t="s">
+        <v>1126</v>
+      </c>
+      <c r="H31" s="179" t="s">
+        <v>1127</v>
+      </c>
+      <c r="I31" s="179" t="s">
         <v>1128</v>
       </c>
-      <c r="H31" s="179" t="s">
+      <c r="J31" s="179" t="s">
         <v>1129</v>
       </c>
-      <c r="I31" s="179" t="s">
+      <c r="K31" s="179" t="s">
         <v>1130</v>
       </c>
-      <c r="J31" s="179" t="s">
+      <c r="L31" s="179" t="s">
         <v>1131</v>
       </c>
-      <c r="K31" s="179" t="s">
+      <c r="M31" s="179" t="s">
         <v>1132</v>
       </c>
-      <c r="L31" s="179" t="s">
+      <c r="N31" s="177" t="s">
         <v>1133</v>
       </c>
-      <c r="M31" s="179" t="s">
+      <c r="O31" s="179" t="s">
         <v>1134</v>
-      </c>
-      <c r="N31" s="177" t="s">
-        <v>1135</v>
-      </c>
-      <c r="O31" s="179" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="32" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C32" s="176"/>
       <c r="D32" s="140" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="E32" s="141" t="s">
         <v>1103</v>
@@ -24774,22 +24778,22 @@
     </row>
     <row r="41" spans="7:12" x14ac:dyDescent="0.25">
       <c r="G41" s="143" t="s">
+        <v>1135</v>
+      </c>
+      <c r="H41" s="144" t="s">
+        <v>1136</v>
+      </c>
+      <c r="I41" s="144" t="s">
         <v>1137</v>
       </c>
-      <c r="H41" s="144" t="s">
+      <c r="J41" s="144" t="s">
         <v>1138</v>
       </c>
-      <c r="I41" s="144" t="s">
+      <c r="K41" s="144" t="s">
         <v>1139</v>
       </c>
-      <c r="J41" s="144" t="s">
+      <c r="L41" s="144" t="s">
         <v>1140</v>
-      </c>
-      <c r="K41" s="144" t="s">
-        <v>1141</v>
-      </c>
-      <c r="L41" s="144" t="s">
-        <v>1142</v>
       </c>
     </row>
   </sheetData>
@@ -24842,6 +24846,7 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
